--- a/data/import/MuscuGuide_Base_Produits.xlsx
+++ b/data/import/MuscuGuide_Base_Produits.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rfc1457e6c9c941ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produits" sheetId="2" r:id="Rb65f86ea3de24f9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notation" sheetId="3" r:id="R5e25b3bbe1754b39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Claude" sheetId="4" r:id="Rc0a76878b93943da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="5" r:id="Rb401f7a14e464a17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="6" r:id="R9032eecde86345ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rd2e18a93e3fb434d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produits" sheetId="2" r:id="Rf761825655804eb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notation" sheetId="3" r:id="R1657e877bbcd4e3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Claude" sheetId="4" r:id="Rf3cff52f8837413f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="5" r:id="R7bd93243be6b450a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="6" r:id="Rf9dadfb54df84384"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,12 +18,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="5">
+  <x:numFmts count="6">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0"/>
     <x:numFmt numFmtId="203" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="204" formatCode="0%"/>
+    <x:numFmt numFmtId="205" formatCode="dd/mm/yyyy"/>
   </x:numFmts>
   <x:fonts count="5">
     <x:font>
@@ -90,7 +91,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="54">
+  <x:cellXfs count="56">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -209,6 +210,10 @@
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="205" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -220,7 +225,7 @@
         <x:color rgb="FF155724"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD4EDDA"/>
         </x:patternFill>
       </x:fill>
@@ -230,7 +235,7 @@
         <x:color rgb="FF856404"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF3CD"/>
         </x:patternFill>
       </x:fill>
@@ -240,7 +245,7 @@
         <x:color rgb="FF721C24"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF8D7DA"/>
         </x:patternFill>
       </x:fill>
@@ -430,7 +435,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R565b0a56faf14e65"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1d6af66b31564bd4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -742,7 +747,7 @@
       </x:c>
       <x:c r="B6" s="12" t="n">
         <x:f>COUNTIF(Produits!AG4:AG250,"Validé")</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C6" s="12"/>
       <x:c r="D6" s="12" t="str">
@@ -772,7 +777,7 @@
       </x:c>
       <x:c r="B7" s="12" t="n">
         <x:f>COUNTIF(Produits!AG4:AG250,"À rechercher")</x:f>
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C7" s="12"/>
       <x:c r="D7" s="12" t="str">
@@ -802,7 +807,7 @@
       </x:c>
       <x:c r="B8" s="38" t="n">
         <x:f>IFERROR(AVERAGE(Produits!U4:U250),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C8" s="12"/>
       <x:c r="D8" s="12" t="str">
@@ -849,7 +854,7 @@
       </x:c>
       <x:c r="G9" s="12" t="n">
         <x:f>COUNTIFS(Produits!B:B,D9,Produits!AG:AG,"Validé")</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H9" s="46" t="n">
         <x:f>IFERROR(F9/E9,0)</x:f>
@@ -1254,7 +1259,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff64c95332a5436f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a8e9b9a759245ef"/>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -1496,9 +1501,8 @@
       <x:c r="R4" s="12" t="str"/>
       <x:c r="S4" s="12" t="str"/>
       <x:c r="T4" s="12" t="str"/>
-      <x:c r="U4" s="12" t="n">
+      <x:c r="U4" s="12" t="str">
         <x:f>IF(COUNTA(O4:T4)=0,"",SUM(O4:T4))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="V4" s="12" t="str">
         <x:f>IF(U4="","",IF(U4&gt;=95,"Exceptionnel",IF(U4&gt;=90,"Excellent",IF(U4&gt;=85,"Très bon",IF(U4&gt;=80,"Bon",IF(U4&gt;=70,"Correct","À revoir"))))))</x:f>
@@ -1572,9 +1576,8 @@
       <x:c r="R5" s="12" t="str"/>
       <x:c r="S5" s="12" t="str"/>
       <x:c r="T5" s="12" t="str"/>
-      <x:c r="U5" s="12" t="n">
+      <x:c r="U5" s="12" t="str">
         <x:f>IF(COUNTA(O5:T5)=0,"",SUM(O5:T5))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="V5" s="12" t="str">
         <x:f>IF(U5="","",IF(U5&gt;=95,"Exceptionnel",IF(U5&gt;=90,"Excellent",IF(U5&gt;=85,"Très bon",IF(U5&gt;=80,"Bon",IF(U5&gt;=70,"Correct","À revoir"))))))</x:f>
@@ -1646,9 +1649,8 @@
       <x:c r="R6" s="12" t="str"/>
       <x:c r="S6" s="12" t="str"/>
       <x:c r="T6" s="12" t="str"/>
-      <x:c r="U6" s="12" t="n">
+      <x:c r="U6" s="12" t="str">
         <x:f>IF(COUNTA(O6:T6)=0,"",SUM(O6:T6))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="V6" s="12" t="str">
         <x:f>IF(U6="","",IF(U6&gt;=95,"Exceptionnel",IF(U6&gt;=90,"Excellent",IF(U6&gt;=85,"Très bon",IF(U6&gt;=80,"Bon",IF(U6&gt;=70,"Correct","À revoir"))))))</x:f>
@@ -1720,9 +1722,8 @@
       <x:c r="R7" s="12" t="str"/>
       <x:c r="S7" s="12" t="str"/>
       <x:c r="T7" s="12" t="str"/>
-      <x:c r="U7" s="12" t="n">
+      <x:c r="U7" s="12" t="str">
         <x:f>IF(COUNTA(O7:T7)=0,"",SUM(O7:T7))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="V7" s="12" t="str">
         <x:f>IF(U7="","",IF(U7&gt;=95,"Exceptionnel",IF(U7&gt;=90,"Excellent",IF(U7&gt;=85,"Très bon",IF(U7&gt;=80,"Bon",IF(U7&gt;=70,"Correct","À revoir"))))))</x:f>
@@ -1796,9 +1797,8 @@
       <x:c r="R8" s="12" t="str"/>
       <x:c r="S8" s="12" t="str"/>
       <x:c r="T8" s="12" t="str"/>
-      <x:c r="U8" s="12" t="n">
+      <x:c r="U8" s="12" t="str">
         <x:f>IF(COUNTA(O8:T8)=0,"",SUM(O8:T8))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="V8" s="12" t="str">
         <x:f>IF(U8="","",IF(U8&gt;=95,"Exceptionnel",IF(U8&gt;=90,"Excellent",IF(U8&gt;=85,"Très bon",IF(U8&gt;=80,"Bon",IF(U8&gt;=70,"Correct","À revoir"))))))</x:f>
@@ -1872,9 +1872,8 @@
       <x:c r="R9" s="12" t="str"/>
       <x:c r="S9" s="12" t="str"/>
       <x:c r="T9" s="12" t="str"/>
-      <x:c r="U9" s="12" t="n">
+      <x:c r="U9" s="12" t="str">
         <x:f>IF(COUNTA(O9:T9)=0,"",SUM(O9:T9))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="V9" s="12" t="str">
         <x:f>IF(U9="","",IF(U9&gt;=95,"Exceptionnel",IF(U9&gt;=90,"Excellent",IF(U9&gt;=85,"Très bon",IF(U9&gt;=80,"Bon",IF(U9&gt;=70,"Correct","À revoir"))))))</x:f>
@@ -1946,9 +1945,8 @@
       <x:c r="R10" s="12" t="str"/>
       <x:c r="S10" s="12" t="str"/>
       <x:c r="T10" s="12" t="str"/>
-      <x:c r="U10" s="12" t="n">
+      <x:c r="U10" s="12" t="str">
         <x:f>IF(COUNTA(O10:T10)=0,"",SUM(O10:T10))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="V10" s="12" t="str">
         <x:f>IF(U10="","",IF(U10&gt;=95,"Exceptionnel",IF(U10&gt;=90,"Excellent",IF(U10&gt;=85,"Très bon",IF(U10&gt;=80,"Bon",IF(U10&gt;=70,"Correct","À revoir"))))))</x:f>
@@ -2022,9 +2020,8 @@
       <x:c r="R11" s="12" t="str"/>
       <x:c r="S11" s="12" t="str"/>
       <x:c r="T11" s="12" t="str"/>
-      <x:c r="U11" s="12" t="n">
+      <x:c r="U11" s="12" t="str">
         <x:f>IF(COUNTA(O11:T11)=0,"",SUM(O11:T11))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="V11" s="12" t="str">
         <x:f>IF(U11="","",IF(U11&gt;=95,"Exceptionnel",IF(U11&gt;=90,"Excellent",IF(U11&gt;=85,"Très bon",IF(U11&gt;=80,"Bon",IF(U11&gt;=70,"Correct","À revoir"))))))</x:f>
@@ -2096,9 +2093,8 @@
       <x:c r="R12" s="12" t="str"/>
       <x:c r="S12" s="12" t="str"/>
       <x:c r="T12" s="12" t="str"/>
-      <x:c r="U12" s="12" t="n">
+      <x:c r="U12" s="12" t="str">
         <x:f>IF(COUNTA(O12:T12)=0,"",SUM(O12:T12))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="V12" s="12" t="str">
         <x:f>IF(U12="","",IF(U12&gt;=95,"Exceptionnel",IF(U12&gt;=90,"Excellent",IF(U12&gt;=85,"Très bon",IF(U12&gt;=80,"Bon",IF(U12&gt;=70,"Correct","À revoir"))))))</x:f>
@@ -2147,14 +2143,20 @@
         <x:v>Choix MuscuGuide</x:v>
       </x:c>
       <x:c r="E13" s="12" t="str">
-        <x:v>Adjustable Weight Bench</x:v>
+        <x:v>Banc de musculation réglable et pliable</x:v>
       </x:c>
       <x:c r="F13" s="12" t="str">
         <x:v>FLYBIRD</x:v>
       </x:c>
-      <x:c r="G13" s="12" t="str"/>
-      <x:c r="H13" s="12" t="str"/>
-      <x:c r="I13" s="12" t="str"/>
+      <x:c r="G13" s="12" t="str">
+        <x:v>Version entraînement complet — B09MQYP1BG</x:v>
+      </x:c>
+      <x:c r="H13" s="12" t="str">
+        <x:v>B09MQYP1BG</x:v>
+      </x:c>
+      <x:c r="I13" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B09MQYP1BG</x:v>
+      </x:c>
       <x:c r="J13" s="12" t="str"/>
       <x:c r="K13" s="12" t="str">
         <x:f>IF(OR(H13="",J13=""),"", "https://www.amazon.fr/dp/"&amp;H13&amp;"?tag="&amp;J13)</x:f>
@@ -2164,18 +2166,31 @@
       <x:c r="N13" s="12" t="str">
         <x:v>Performance</x:v>
       </x:c>
-      <x:c r="O13" s="12" t="str"/>
-      <x:c r="P13" s="12" t="str"/>
-      <x:c r="Q13" s="12" t="str"/>
-      <x:c r="R13" s="12" t="str"/>
-      <x:c r="S13" s="12" t="str"/>
-      <x:c r="T13" s="12" t="str"/>
+      <x:c r="O13" s="12" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P13" s="12" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q13" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="R13" s="12" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="S13" s="12" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="T13" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="U13" s="12" t="n">
         <x:f>IF(COUNTA(O13:T13)=0,"",SUM(O13:T13))</x:f>
-        <x:v>0</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="V13" s="12" t="str">
         <x:f>IF(U13="","",IF(U13&gt;=95,"Exceptionnel",IF(U13&gt;=90,"Excellent",IF(U13&gt;=85,"Très bon",IF(U13&gt;=80,"Bon",IF(U13&gt;=70,"Correct","À revoir"))))))</x:f>
+        <x:v>Très bon</x:v>
       </x:c>
       <x:c r="W13" s="12" t="str">
         <x:v>Oui</x:v>
@@ -2187,26 +2202,30 @@
         <x:v>Oui</x:v>
       </x:c>
       <x:c r="Z13" s="12" t="str">
-        <x:v>Banc réglable et pliable adapté au home gym.</x:v>
+        <x:v>Banc réglable et pliable très polyvalent pour équiper un home gym sans prendre trop de place.</x:v>
       </x:c>
       <x:c r="AA13" s="12" t="str">
-        <x:v>Pliable | Polyvalent | Populaire</x:v>
+        <x:v>Pliable | Réglages polyvalents | Bon rapport qualité/prix | Adapté au home gym</x:v>
       </x:c>
       <x:c r="AB13" s="12" t="str">
-        <x:v>Stabilité à vérifier selon version</x:v>
+        <x:v>Moins adapté à un usage professionnel intensif | Stabilité dépendante du bon verrouillage</x:v>
       </x:c>
       <x:c r="AC13" s="12" t="str">
-        <x:v>Débutant à confirmé</x:v>
-      </x:c>
-      <x:c r="AD13" s="12" t="str"/>
-      <x:c r="AE13" s="38" t="str"/>
-      <x:c r="AF13" s="40" t="str"/>
+        <x:v>Débutant à confirmé recherchant un banc compact</x:v>
+      </x:c>
+      <x:c r="AD13" s="12"/>
+      <x:c r="AE13" s="38"/>
+      <x:c r="AF13" s="55" t="n">
+        <x:v>46238</x:v>
+      </x:c>
       <x:c r="AG13" s="12" t="str">
-        <x:v>À rechercher</x:v>
-      </x:c>
-      <x:c r="AH13" s="12" t="str"/>
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH13" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B09MQYP1BG</x:v>
+      </x:c>
       <x:c r="AI13" s="12" t="str">
-        <x:v>Identifier la version exacte Amazon FR.</x:v>
+        <x:v>ASIN Amazon FR vérifié le 04/08/2026. Note et nombre d'avis laissés vides faute de lecture FR suffisamment fiable.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2223,14 +2242,20 @@
         <x:v>Meilleur rapport qualité/prix</x:v>
       </x:c>
       <x:c r="E14" s="12" t="str">
-        <x:v>Adjustable Weight Bench</x:v>
+        <x:v>Banc de musculation réglable 375 kg</x:v>
       </x:c>
       <x:c r="F14" s="12" t="str">
         <x:v>YOLEO</x:v>
       </x:c>
-      <x:c r="G14" s="12" t="str"/>
-      <x:c r="H14" s="12" t="str"/>
-      <x:c r="I14" s="12" t="str"/>
+      <x:c r="G14" s="12" t="str">
+        <x:v>Préassemblé à 98 % — 84 positions</x:v>
+      </x:c>
+      <x:c r="H14" s="12" t="str">
+        <x:v>B08GLYDMSF</x:v>
+      </x:c>
+      <x:c r="I14" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B08GLYDMSF</x:v>
+      </x:c>
       <x:c r="J14" s="12" t="str"/>
       <x:c r="K14" s="12" t="str">
         <x:f>IF(OR(H14="",J14=""),"", "https://www.amazon.fr/dp/"&amp;H14&amp;"?tag="&amp;J14)</x:f>
@@ -2240,18 +2265,31 @@
       <x:c r="N14" s="12" t="str">
         <x:v>Essentials</x:v>
       </x:c>
-      <x:c r="O14" s="12" t="str"/>
-      <x:c r="P14" s="12" t="str"/>
-      <x:c r="Q14" s="12" t="str"/>
-      <x:c r="R14" s="12" t="str"/>
-      <x:c r="S14" s="12" t="str"/>
-      <x:c r="T14" s="12" t="str"/>
+      <x:c r="O14" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P14" s="12" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q14" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="R14" s="12" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="S14" s="12" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="T14" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="U14" s="12" t="n">
         <x:f>IF(COUNTA(O14:T14)=0,"",SUM(O14:T14))</x:f>
-        <x:v>0</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="V14" s="12" t="str">
         <x:f>IF(U14="","",IF(U14&gt;=95,"Exceptionnel",IF(U14&gt;=90,"Excellent",IF(U14&gt;=85,"Très bon",IF(U14&gt;=80,"Bon",IF(U14&gt;=70,"Correct","À revoir"))))))</x:f>
+        <x:v>Très bon</x:v>
       </x:c>
       <x:c r="W14" s="12" t="str">
         <x:v>Oui</x:v>
@@ -2261,26 +2299,34 @@
       </x:c>
       <x:c r="Y14" s="12" t="str"/>
       <x:c r="Z14" s="12" t="str">
-        <x:v>Banc abordable pour débuter à domicile.</x:v>
+        <x:v>Banc pliable et accessible, particulièrement intéressant pour débuter et varier les angles à domicile.</x:v>
       </x:c>
       <x:c r="AA14" s="12" t="str">
-        <x:v>Prix | Pliable | Plusieurs inclinaisons</x:v>
+        <x:v>Excellent rapport qualité/prix | Charge annoncée élevée | Pliable | Nombreux réglages</x:v>
       </x:c>
       <x:c r="AB14" s="12" t="str">
-        <x:v>Charge et dimensions à vérifier</x:v>
+        <x:v>Finitions moins premium | SAV et disponibilité à surveiller</x:v>
       </x:c>
       <x:c r="AC14" s="12" t="str">
-        <x:v>Débutant / intermédiaire</x:v>
-      </x:c>
-      <x:c r="AD14" s="12" t="str"/>
-      <x:c r="AE14" s="38" t="str"/>
-      <x:c r="AF14" s="40" t="str"/>
+        <x:v>Débutant ou intermédiaire avec budget maîtrisé</x:v>
+      </x:c>
+      <x:c r="AD14" s="12" t="n">
+        <x:v>6094</x:v>
+      </x:c>
+      <x:c r="AE14" s="38" t="n">
+        <x:v>4.6</x:v>
+      </x:c>
+      <x:c r="AF14" s="55" t="n">
+        <x:v>46238</x:v>
+      </x:c>
       <x:c r="AG14" s="12" t="str">
-        <x:v>À rechercher</x:v>
-      </x:c>
-      <x:c r="AH14" s="12" t="str"/>
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH14" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B08GLYDMSF</x:v>
+      </x:c>
       <x:c r="AI14" s="12" t="str">
-        <x:v>Identifier modèle exact.</x:v>
+        <x:v>ASIN, note Amazon et nombre d'évaluations vérifiés le 04/08/2026. Ces données évoluent dans le temps.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -2297,14 +2343,20 @@
         <x:v>Premium</x:v>
       </x:c>
       <x:c r="E15" s="12" t="str">
-        <x:v>5.1S Stowable Bench</x:v>
+        <x:v>Banc de musculation 5.1S</x:v>
       </x:c>
       <x:c r="F15" s="12" t="str">
         <x:v>Bowflex</x:v>
       </x:c>
-      <x:c r="G15" s="12" t="str"/>
-      <x:c r="H15" s="12" t="str"/>
-      <x:c r="I15" s="12" t="str"/>
+      <x:c r="G15" s="12" t="str">
+        <x:v>SelectTech 5.1S Stowable Bench</x:v>
+      </x:c>
+      <x:c r="H15" s="12" t="str">
+        <x:v>B0BKW8ZBCT</x:v>
+      </x:c>
+      <x:c r="I15" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0BKW8ZBCT</x:v>
+      </x:c>
       <x:c r="J15" s="12" t="str"/>
       <x:c r="K15" s="12" t="str">
         <x:f>IF(OR(H15="",J15=""),"", "https://www.amazon.fr/dp/"&amp;H15&amp;"?tag="&amp;J15)</x:f>
@@ -2314,18 +2366,31 @@
       <x:c r="N15" s="12" t="str">
         <x:v>Elite</x:v>
       </x:c>
-      <x:c r="O15" s="12" t="str"/>
-      <x:c r="P15" s="12" t="str"/>
-      <x:c r="Q15" s="12" t="str"/>
-      <x:c r="R15" s="12" t="str"/>
-      <x:c r="S15" s="12" t="str"/>
-      <x:c r="T15" s="12" t="str"/>
+      <x:c r="O15" s="12" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P15" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="Q15" s="12" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R15" s="12" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="S15" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="T15" s="12" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="U15" s="12" t="n">
         <x:f>IF(COUNTA(O15:T15)=0,"",SUM(O15:T15))</x:f>
-        <x:v>0</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="V15" s="12" t="str">
         <x:f>IF(U15="","",IF(U15&gt;=95,"Exceptionnel",IF(U15&gt;=90,"Excellent",IF(U15&gt;=85,"Très bon",IF(U15&gt;=80,"Bon",IF(U15&gt;=70,"Correct","À revoir"))))))</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="W15" s="12" t="str"/>
       <x:c r="X15" s="12" t="str">
@@ -2335,26 +2400,30 @@
         <x:v>Oui</x:v>
       </x:c>
       <x:c r="Z15" s="12" t="str">
-        <x:v>Banc premium stable et rangeable verticalement.</x:v>
+        <x:v>Banc premium robuste et confortable, conçu pour les pratiquants exigeants et le rangement vertical.</x:v>
       </x:c>
       <x:c r="AA15" s="12" t="str">
-        <x:v>Finition | Stabilité | Rangement</x:v>
+        <x:v>Construction premium | Très bonne stabilité | Plusieurs angles | Rangement vertical</x:v>
       </x:c>
       <x:c r="AB15" s="12" t="str">
-        <x:v>Prix élevé | Lourd</x:v>
+        <x:v>Prix élevé | Plus lourd et encombrant que les modèles pliables légers</x:v>
       </x:c>
       <x:c r="AC15" s="12" t="str">
-        <x:v>Home gym premium</x:v>
-      </x:c>
-      <x:c r="AD15" s="12" t="str"/>
-      <x:c r="AE15" s="38" t="str"/>
-      <x:c r="AF15" s="40" t="str"/>
+        <x:v>Intermédiaire ou confirmé recherchant un banc premium</x:v>
+      </x:c>
+      <x:c r="AD15" s="12"/>
+      <x:c r="AE15" s="38"/>
+      <x:c r="AF15" s="55" t="n">
+        <x:v>46238</x:v>
+      </x:c>
       <x:c r="AG15" s="12" t="str">
-        <x:v>À rechercher</x:v>
-      </x:c>
-      <x:c r="AH15" s="12" t="str"/>
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH15" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0BKW8ZBCT</x:v>
+      </x:c>
       <x:c r="AI15" s="12" t="str">
-        <x:v>Vérifier disponibilité Amazon FR.</x:v>
+        <x:v>ASIN Amazon FR et modèle 5.1S vérifiés le 04/08/2026. Note et nombre d'avis laissés vides faute de valeur FR précisément vérifiable.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2394,9 +2463,8 @@
       <x:c r="R16" s="12" t="str"/>
       <x:c r="S16" s="12" t="str"/>
       <x:c r="T16" s="12" t="str"/>
-      <x:c r="U16" s="12" t="n">
+      <x:c r="U16" s="12" t="str">
         <x:f>IF(COUNTA(O16:T16)=0,"",SUM(O16:T16))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="V16" s="12" t="str">
         <x:f>IF(U16="","",IF(U16&gt;=95,"Exceptionnel",IF(U16&gt;=90,"Excellent",IF(U16&gt;=85,"Très bon",IF(U16&gt;=80,"Bon",IF(U16&gt;=70,"Correct","À revoir"))))))</x:f>
@@ -2470,9 +2538,8 @@
       <x:c r="R17" s="12" t="str"/>
       <x:c r="S17" s="12" t="str"/>
       <x:c r="T17" s="12" t="str"/>
-      <x:c r="U17" s="12" t="n">
+      <x:c r="U17" s="12" t="str">
         <x:f>IF(COUNTA(O17:T17)=0,"",SUM(O17:T17))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="V17" s="12" t="str">
         <x:f>IF(U17="","",IF(U17&gt;=95,"Exceptionnel",IF(U17&gt;=90,"Excellent",IF(U17&gt;=85,"Très bon",IF(U17&gt;=80,"Bon",IF(U17&gt;=70,"Correct","À revoir"))))))</x:f>
@@ -2544,9 +2611,8 @@
       <x:c r="R18" s="12" t="str"/>
       <x:c r="S18" s="12" t="str"/>
       <x:c r="T18" s="12" t="str"/>
-      <x:c r="U18" s="12" t="n">
+      <x:c r="U18" s="12" t="str">
         <x:f>IF(COUNTA(O18:T18)=0,"",SUM(O18:T18))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="V18" s="12" t="str">
         <x:f>IF(U18="","",IF(U18&gt;=95,"Exceptionnel",IF(U18&gt;=90,"Excellent",IF(U18&gt;=85,"Très bon",IF(U18&gt;=80,"Bon",IF(U18&gt;=70,"Correct","À revoir"))))))</x:f>
@@ -2618,9 +2684,8 @@
       <x:c r="R19" s="12" t="str"/>
       <x:c r="S19" s="12" t="str"/>
       <x:c r="T19" s="12" t="str"/>
-      <x:c r="U19" s="12" t="n">
+      <x:c r="U19" s="12" t="str">
         <x:f>IF(COUNTA(O19:T19)=0,"",SUM(O19:T19))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="V19" s="12" t="str">
         <x:f>IF(U19="","",IF(U19&gt;=95,"Exceptionnel",IF(U19&gt;=90,"Excellent",IF(U19&gt;=85,"Très bon",IF(U19&gt;=80,"Bon",IF(U19&gt;=70,"Correct","À revoir"))))))</x:f>
@@ -2692,9 +2757,8 @@
       <x:c r="R20" s="12" t="str"/>
       <x:c r="S20" s="12" t="str"/>
       <x:c r="T20" s="12" t="str"/>
-      <x:c r="U20" s="12" t="n">
+      <x:c r="U20" s="12" t="str">
         <x:f>IF(COUNTA(O20:T20)=0,"",SUM(O20:T20))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="V20" s="12" t="str">
         <x:f>IF(U20="","",IF(U20&gt;=95,"Exceptionnel",IF(U20&gt;=90,"Excellent",IF(U20&gt;=85,"Très bon",IF(U20&gt;=80,"Bon",IF(U20&gt;=70,"Correct","À revoir"))))))</x:f>
@@ -2766,9 +2830,8 @@
       <x:c r="R21" s="12" t="str"/>
       <x:c r="S21" s="12" t="str"/>
       <x:c r="T21" s="12" t="str"/>
-      <x:c r="U21" s="12" t="n">
+      <x:c r="U21" s="12" t="str">
         <x:f>IF(COUNTA(O21:T21)=0,"",SUM(O21:T21))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="V21" s="12" t="str">
         <x:f>IF(U21="","",IF(U21&gt;=95,"Exceptionnel",IF(U21&gt;=90,"Excellent",IF(U21&gt;=85,"Très bon",IF(U21&gt;=80,"Bon",IF(U21&gt;=70,"Correct","À revoir"))))))</x:f>
@@ -2840,9 +2903,8 @@
       <x:c r="R22" s="12" t="str"/>
       <x:c r="S22" s="12" t="str"/>
       <x:c r="T22" s="12" t="str"/>
-      <x:c r="U22" s="12" t="n">
+      <x:c r="U22" s="12" t="str">
         <x:f>IF(COUNTA(O22:T22)=0,"",SUM(O22:T22))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="V22" s="12" t="str">
         <x:f>IF(U22="","",IF(U22&gt;=95,"Exceptionnel",IF(U22&gt;=90,"Excellent",IF(U22&gt;=85,"Très bon",IF(U22&gt;=80,"Bon",IF(U22&gt;=70,"Correct","À revoir"))))))</x:f>
@@ -2916,9 +2978,8 @@
       <x:c r="R23" s="12" t="str"/>
       <x:c r="S23" s="12" t="str"/>
       <x:c r="T23" s="12" t="str"/>
-      <x:c r="U23" s="12" t="n">
+      <x:c r="U23" s="12" t="str">
         <x:f>IF(COUNTA(O23:T23)=0,"",SUM(O23:T23))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="V23" s="12" t="str">
         <x:f>IF(U23="","",IF(U23&gt;=95,"Exceptionnel",IF(U23&gt;=90,"Excellent",IF(U23&gt;=85,"Très bon",IF(U23&gt;=80,"Bon",IF(U23&gt;=70,"Correct","À revoir"))))))</x:f>
@@ -2990,9 +3051,8 @@
       <x:c r="R24" s="12" t="str"/>
       <x:c r="S24" s="12" t="str"/>
       <x:c r="T24" s="12" t="str"/>
-      <x:c r="U24" s="12" t="n">
+      <x:c r="U24" s="12" t="str">
         <x:f>IF(COUNTA(O24:T24)=0,"",SUM(O24:T24))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="V24" s="12" t="str">
         <x:f>IF(U24="","",IF(U24&gt;=95,"Exceptionnel",IF(U24&gt;=90,"Excellent",IF(U24&gt;=85,"Très bon",IF(U24&gt;=80,"Bon",IF(U24&gt;=70,"Correct","À revoir"))))))</x:f>
@@ -3064,9 +3124,8 @@
       <x:c r="R25" s="12" t="str"/>
       <x:c r="S25" s="12" t="str"/>
       <x:c r="T25" s="12" t="str"/>
-      <x:c r="U25" s="12" t="n">
+      <x:c r="U25" s="12" t="str">
         <x:f>IF(COUNTA(O25:T25)=0,"",SUM(O25:T25))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="V25" s="12" t="str">
         <x:f>IF(U25="","",IF(U25&gt;=95,"Exceptionnel",IF(U25&gt;=90,"Excellent",IF(U25&gt;=85,"Très bon",IF(U25&gt;=80,"Bon",IF(U25&gt;=70,"Correct","À revoir"))))))</x:f>
@@ -3140,9 +3199,8 @@
       <x:c r="R26" s="12" t="str"/>
       <x:c r="S26" s="12" t="str"/>
       <x:c r="T26" s="12" t="str"/>
-      <x:c r="U26" s="12" t="n">
+      <x:c r="U26" s="12" t="str">
         <x:f>IF(COUNTA(O26:T26)=0,"",SUM(O26:T26))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="V26" s="12" t="str">
         <x:f>IF(U26="","",IF(U26&gt;=95,"Exceptionnel",IF(U26&gt;=90,"Excellent",IF(U26&gt;=85,"Très bon",IF(U26&gt;=80,"Bon",IF(U26&gt;=70,"Correct","À revoir"))))))</x:f>
@@ -3216,9 +3274,8 @@
       <x:c r="R27" s="12" t="str"/>
       <x:c r="S27" s="12" t="str"/>
       <x:c r="T27" s="12" t="str"/>
-      <x:c r="U27" s="12" t="n">
+      <x:c r="U27" s="12" t="str">
         <x:f>IF(COUNTA(O27:T27)=0,"",SUM(O27:T27))</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="V27" s="12" t="str">
         <x:f>IF(U27="","",IF(U27&gt;=95,"Exceptionnel",IF(U27&gt;=90,"Excellent",IF(U27&gt;=85,"Très bon",IF(U27&gt;=80,"Bon",IF(U27&gt;=70,"Correct","À revoir"))))))</x:f>
@@ -12912,7 +12969,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d206decd1424a68"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95fec52e65ac4803"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13974,19 +14031,19 @@
       </x:c>
       <x:c r="E13" s="12" t="str">
         <x:f>Produits!E13</x:f>
-        <x:v>Adjustable Weight Bench</x:v>
+        <x:v>Banc de musculation réglable et pliable</x:v>
       </x:c>
       <x:c r="F13" s="12" t="str">
         <x:f>Produits!F13</x:f>
         <x:v>FLYBIRD</x:v>
       </x:c>
-      <x:c r="G13" s="12" t="n">
+      <x:c r="G13" s="12" t="str">
         <x:f>Produits!H13</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H13" s="12" t="n">
+        <x:v>B09MQYP1BG</x:v>
+      </x:c>
+      <x:c r="H13" s="12" t="str">
         <x:f>Produits!I13</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B09MQYP1BG</x:v>
       </x:c>
       <x:c r="I13" s="12" t="n">
         <x:f>Produits!K13</x:f>
@@ -13998,30 +14055,31 @@
       </x:c>
       <x:c r="K13" s="12" t="n">
         <x:f>Produits!U13</x:f>
-        <x:v>0</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="L13" s="12" t="str">
         <x:f>Produits!V13</x:f>
+        <x:v>Très bon</x:v>
       </x:c>
       <x:c r="M13" s="12" t="str">
         <x:f>Produits!Z13</x:f>
-        <x:v>Banc réglable et pliable adapté au home gym.</x:v>
+        <x:v>Banc réglable et pliable très polyvalent pour équiper un home gym sans prendre trop de place.</x:v>
       </x:c>
       <x:c r="N13" s="12" t="str">
         <x:f>Produits!AA13</x:f>
-        <x:v>Pliable | Polyvalent | Populaire</x:v>
+        <x:v>Pliable | Réglages polyvalents | Bon rapport qualité/prix | Adapté au home gym</x:v>
       </x:c>
       <x:c r="O13" s="12" t="str">
         <x:f>Produits!AB13</x:f>
-        <x:v>Stabilité à vérifier selon version</x:v>
+        <x:v>Moins adapté à un usage professionnel intensif | Stabilité dépendante du bon verrouillage</x:v>
       </x:c>
       <x:c r="P13" s="12" t="str">
         <x:f>Produits!AC13</x:f>
-        <x:v>Débutant à confirmé</x:v>
+        <x:v>Débutant à confirmé recherchant un banc compact</x:v>
       </x:c>
       <x:c r="Q13" s="12" t="str">
         <x:f>Produits!AG13</x:f>
-        <x:v>À rechercher</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -14043,19 +14101,19 @@
       </x:c>
       <x:c r="E14" s="12" t="str">
         <x:f>Produits!E14</x:f>
-        <x:v>Adjustable Weight Bench</x:v>
+        <x:v>Banc de musculation réglable 375 kg</x:v>
       </x:c>
       <x:c r="F14" s="12" t="str">
         <x:f>Produits!F14</x:f>
         <x:v>YOLEO</x:v>
       </x:c>
-      <x:c r="G14" s="12" t="n">
+      <x:c r="G14" s="12" t="str">
         <x:f>Produits!H14</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H14" s="12" t="n">
+        <x:v>B08GLYDMSF</x:v>
+      </x:c>
+      <x:c r="H14" s="12" t="str">
         <x:f>Produits!I14</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B08GLYDMSF</x:v>
       </x:c>
       <x:c r="I14" s="12" t="n">
         <x:f>Produits!K14</x:f>
@@ -14067,31 +14125,31 @@
       </x:c>
       <x:c r="K14" s="12" t="n">
         <x:f>Produits!U14</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L14" s="12" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="L14" s="12" t="str">
         <x:f>Produits!V14</x:f>
-        <x:v>0</x:v>
+        <x:v>Très bon</x:v>
       </x:c>
       <x:c r="M14" s="12" t="str">
         <x:f>Produits!Z14</x:f>
-        <x:v>Banc abordable pour débuter à domicile.</x:v>
+        <x:v>Banc pliable et accessible, particulièrement intéressant pour débuter et varier les angles à domicile.</x:v>
       </x:c>
       <x:c r="N14" s="12" t="str">
         <x:f>Produits!AA14</x:f>
-        <x:v>Prix | Pliable | Plusieurs inclinaisons</x:v>
+        <x:v>Excellent rapport qualité/prix | Charge annoncée élevée | Pliable | Nombreux réglages</x:v>
       </x:c>
       <x:c r="O14" s="12" t="str">
         <x:f>Produits!AB14</x:f>
-        <x:v>Charge et dimensions à vérifier</x:v>
+        <x:v>Finitions moins premium | SAV et disponibilité à surveiller</x:v>
       </x:c>
       <x:c r="P14" s="12" t="str">
         <x:f>Produits!AC14</x:f>
-        <x:v>Débutant / intermédiaire</x:v>
+        <x:v>Débutant ou intermédiaire avec budget maîtrisé</x:v>
       </x:c>
       <x:c r="Q14" s="12" t="str">
         <x:f>Produits!AG14</x:f>
-        <x:v>À rechercher</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -14113,19 +14171,19 @@
       </x:c>
       <x:c r="E15" s="12" t="str">
         <x:f>Produits!E15</x:f>
-        <x:v>5.1S Stowable Bench</x:v>
+        <x:v>Banc de musculation 5.1S</x:v>
       </x:c>
       <x:c r="F15" s="12" t="str">
         <x:f>Produits!F15</x:f>
         <x:v>Bowflex</x:v>
       </x:c>
-      <x:c r="G15" s="12" t="n">
+      <x:c r="G15" s="12" t="str">
         <x:f>Produits!H15</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H15" s="12" t="n">
+        <x:v>B0BKW8ZBCT</x:v>
+      </x:c>
+      <x:c r="H15" s="12" t="str">
         <x:f>Produits!I15</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B0BKW8ZBCT</x:v>
       </x:c>
       <x:c r="I15" s="12" t="n">
         <x:f>Produits!K15</x:f>
@@ -14137,30 +14195,31 @@
       </x:c>
       <x:c r="K15" s="12" t="n">
         <x:f>Produits!U15</x:f>
-        <x:v>0</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="L15" s="12" t="str">
         <x:f>Produits!V15</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="M15" s="12" t="str">
         <x:f>Produits!Z15</x:f>
-        <x:v>Banc premium stable et rangeable verticalement.</x:v>
+        <x:v>Banc premium robuste et confortable, conçu pour les pratiquants exigeants et le rangement vertical.</x:v>
       </x:c>
       <x:c r="N15" s="12" t="str">
         <x:f>Produits!AA15</x:f>
-        <x:v>Finition | Stabilité | Rangement</x:v>
+        <x:v>Construction premium | Très bonne stabilité | Plusieurs angles | Rangement vertical</x:v>
       </x:c>
       <x:c r="O15" s="12" t="str">
         <x:f>Produits!AB15</x:f>
-        <x:v>Prix élevé | Lourd</x:v>
+        <x:v>Prix élevé | Plus lourd et encombrant que les modèles pliables légers</x:v>
       </x:c>
       <x:c r="P15" s="12" t="str">
         <x:f>Produits!AC15</x:f>
-        <x:v>Home gym premium</x:v>
+        <x:v>Intermédiaire ou confirmé recherchant un banc premium</x:v>
       </x:c>
       <x:c r="Q15" s="12" t="str">
         <x:f>Produits!AG15</x:f>
-        <x:v>À rechercher</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -15037,8 +15096,9 @@
         <x:f>Produits!L28</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K28" s="12" t="str">
+      <x:c r="K28" s="12" t="n">
         <x:f>Produits!U28</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L28" s="12" t="n">
         <x:f>Produits!V28</x:f>
@@ -15106,8 +15166,9 @@
         <x:f>Produits!L29</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K29" s="12" t="str">
+      <x:c r="K29" s="12" t="n">
         <x:f>Produits!U29</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L29" s="12" t="n">
         <x:f>Produits!V29</x:f>
@@ -15175,8 +15236,9 @@
         <x:f>Produits!L30</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K30" s="12" t="str">
+      <x:c r="K30" s="12" t="n">
         <x:f>Produits!U30</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L30" s="12" t="n">
         <x:f>Produits!V30</x:f>
@@ -15244,8 +15306,9 @@
         <x:f>Produits!L31</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K31" s="12" t="str">
+      <x:c r="K31" s="12" t="n">
         <x:f>Produits!U31</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L31" s="12" t="n">
         <x:f>Produits!V31</x:f>
@@ -15313,8 +15376,9 @@
         <x:f>Produits!L32</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K32" s="12" t="str">
+      <x:c r="K32" s="12" t="n">
         <x:f>Produits!U32</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L32" s="12" t="n">
         <x:f>Produits!V32</x:f>
@@ -15382,8 +15446,9 @@
         <x:f>Produits!L33</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K33" s="12" t="str">
+      <x:c r="K33" s="12" t="n">
         <x:f>Produits!U33</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L33" s="12" t="n">
         <x:f>Produits!V33</x:f>
@@ -15451,8 +15516,9 @@
         <x:f>Produits!L34</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K34" s="12" t="str">
+      <x:c r="K34" s="12" t="n">
         <x:f>Produits!U34</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L34" s="12" t="n">
         <x:f>Produits!V34</x:f>
@@ -15520,8 +15586,9 @@
         <x:f>Produits!L35</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K35" s="12" t="str">
+      <x:c r="K35" s="12" t="n">
         <x:f>Produits!U35</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L35" s="12" t="n">
         <x:f>Produits!V35</x:f>
@@ -15589,8 +15656,9 @@
         <x:f>Produits!L36</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K36" s="12" t="str">
+      <x:c r="K36" s="12" t="n">
         <x:f>Produits!U36</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L36" s="12" t="n">
         <x:f>Produits!V36</x:f>
@@ -15658,8 +15726,9 @@
         <x:f>Produits!L37</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K37" s="12" t="str">
+      <x:c r="K37" s="12" t="n">
         <x:f>Produits!U37</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L37" s="12" t="n">
         <x:f>Produits!V37</x:f>
@@ -15727,8 +15796,9 @@
         <x:f>Produits!L38</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K38" s="12" t="str">
+      <x:c r="K38" s="12" t="n">
         <x:f>Produits!U38</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L38" s="12" t="n">
         <x:f>Produits!V38</x:f>
@@ -15796,8 +15866,9 @@
         <x:f>Produits!L39</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K39" s="12" t="str">
+      <x:c r="K39" s="12" t="n">
         <x:f>Produits!U39</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L39" s="12" t="n">
         <x:f>Produits!V39</x:f>
@@ -15865,8 +15936,9 @@
         <x:f>Produits!L40</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K40" s="12" t="str">
+      <x:c r="K40" s="12" t="n">
         <x:f>Produits!U40</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L40" s="12" t="n">
         <x:f>Produits!V40</x:f>
@@ -15934,8 +16006,9 @@
         <x:f>Produits!L41</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K41" s="12" t="str">
+      <x:c r="K41" s="12" t="n">
         <x:f>Produits!U41</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L41" s="12" t="n">
         <x:f>Produits!V41</x:f>
@@ -16003,8 +16076,9 @@
         <x:f>Produits!L42</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K42" s="12" t="str">
+      <x:c r="K42" s="12" t="n">
         <x:f>Produits!U42</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L42" s="12" t="n">
         <x:f>Produits!V42</x:f>
@@ -16072,8 +16146,9 @@
         <x:f>Produits!L43</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K43" s="12" t="str">
+      <x:c r="K43" s="12" t="n">
         <x:f>Produits!U43</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L43" s="12" t="n">
         <x:f>Produits!V43</x:f>
@@ -16141,8 +16216,9 @@
         <x:f>Produits!L44</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K44" s="12" t="str">
+      <x:c r="K44" s="12" t="n">
         <x:f>Produits!U44</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L44" s="12" t="n">
         <x:f>Produits!V44</x:f>
@@ -16210,8 +16286,9 @@
         <x:f>Produits!L45</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K45" s="12" t="str">
+      <x:c r="K45" s="12" t="n">
         <x:f>Produits!U45</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L45" s="12" t="n">
         <x:f>Produits!V45</x:f>
@@ -16279,8 +16356,9 @@
         <x:f>Produits!L46</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K46" s="12" t="str">
+      <x:c r="K46" s="12" t="n">
         <x:f>Produits!U46</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L46" s="12" t="n">
         <x:f>Produits!V46</x:f>
@@ -16348,8 +16426,9 @@
         <x:f>Produits!L47</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K47" s="12" t="str">
+      <x:c r="K47" s="12" t="n">
         <x:f>Produits!U47</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L47" s="12" t="n">
         <x:f>Produits!V47</x:f>
@@ -16417,8 +16496,9 @@
         <x:f>Produits!L48</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K48" s="12" t="str">
+      <x:c r="K48" s="12" t="n">
         <x:f>Produits!U48</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L48" s="12" t="n">
         <x:f>Produits!V48</x:f>
@@ -16486,8 +16566,9 @@
         <x:f>Produits!L49</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K49" s="12" t="str">
+      <x:c r="K49" s="12" t="n">
         <x:f>Produits!U49</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L49" s="12" t="n">
         <x:f>Produits!V49</x:f>
@@ -16555,8 +16636,9 @@
         <x:f>Produits!L50</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K50" s="12" t="str">
+      <x:c r="K50" s="12" t="n">
         <x:f>Produits!U50</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L50" s="12" t="n">
         <x:f>Produits!V50</x:f>
@@ -16624,8 +16706,9 @@
         <x:f>Produits!L51</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K51" s="12" t="str">
+      <x:c r="K51" s="12" t="n">
         <x:f>Produits!U51</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L51" s="12" t="n">
         <x:f>Produits!V51</x:f>
@@ -16693,8 +16776,9 @@
         <x:f>Produits!L52</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K52" s="12" t="str">
+      <x:c r="K52" s="12" t="n">
         <x:f>Produits!U52</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L52" s="12" t="n">
         <x:f>Produits!V52</x:f>
@@ -16762,8 +16846,9 @@
         <x:f>Produits!L53</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K53" s="12" t="str">
+      <x:c r="K53" s="12" t="n">
         <x:f>Produits!U53</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L53" s="12" t="n">
         <x:f>Produits!V53</x:f>
@@ -16831,8 +16916,9 @@
         <x:f>Produits!L54</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K54" s="12" t="str">
+      <x:c r="K54" s="12" t="n">
         <x:f>Produits!U54</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L54" s="12" t="n">
         <x:f>Produits!V54</x:f>
@@ -16900,8 +16986,9 @@
         <x:f>Produits!L55</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K55" s="12" t="str">
+      <x:c r="K55" s="12" t="n">
         <x:f>Produits!U55</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L55" s="12" t="n">
         <x:f>Produits!V55</x:f>
@@ -16969,8 +17056,9 @@
         <x:f>Produits!L56</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K56" s="12" t="str">
+      <x:c r="K56" s="12" t="n">
         <x:f>Produits!U56</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L56" s="12" t="n">
         <x:f>Produits!V56</x:f>
@@ -17038,8 +17126,9 @@
         <x:f>Produits!L57</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K57" s="12" t="str">
+      <x:c r="K57" s="12" t="n">
         <x:f>Produits!U57</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L57" s="12" t="n">
         <x:f>Produits!V57</x:f>
@@ -17107,8 +17196,9 @@
         <x:f>Produits!L58</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K58" s="12" t="str">
+      <x:c r="K58" s="12" t="n">
         <x:f>Produits!U58</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L58" s="12" t="n">
         <x:f>Produits!V58</x:f>
@@ -17176,8 +17266,9 @@
         <x:f>Produits!L59</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K59" s="12" t="str">
+      <x:c r="K59" s="12" t="n">
         <x:f>Produits!U59</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L59" s="12" t="n">
         <x:f>Produits!V59</x:f>
@@ -17245,8 +17336,9 @@
         <x:f>Produits!L60</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K60" s="12" t="str">
+      <x:c r="K60" s="12" t="n">
         <x:f>Produits!U60</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L60" s="12" t="n">
         <x:f>Produits!V60</x:f>
@@ -17314,8 +17406,9 @@
         <x:f>Produits!L61</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K61" s="12" t="str">
+      <x:c r="K61" s="12" t="n">
         <x:f>Produits!U61</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L61" s="12" t="n">
         <x:f>Produits!V61</x:f>
@@ -17383,8 +17476,9 @@
         <x:f>Produits!L62</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K62" s="12" t="str">
+      <x:c r="K62" s="12" t="n">
         <x:f>Produits!U62</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L62" s="12" t="n">
         <x:f>Produits!V62</x:f>
@@ -17452,8 +17546,9 @@
         <x:f>Produits!L63</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K63" s="12" t="str">
+      <x:c r="K63" s="12" t="n">
         <x:f>Produits!U63</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L63" s="12" t="n">
         <x:f>Produits!V63</x:f>
@@ -17521,8 +17616,9 @@
         <x:f>Produits!L64</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K64" s="12" t="str">
+      <x:c r="K64" s="12" t="n">
         <x:f>Produits!U64</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L64" s="12" t="n">
         <x:f>Produits!V64</x:f>
@@ -17590,8 +17686,9 @@
         <x:f>Produits!L65</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K65" s="12" t="str">
+      <x:c r="K65" s="12" t="n">
         <x:f>Produits!U65</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L65" s="12" t="n">
         <x:f>Produits!V65</x:f>
@@ -17659,8 +17756,9 @@
         <x:f>Produits!L66</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K66" s="12" t="str">
+      <x:c r="K66" s="12" t="n">
         <x:f>Produits!U66</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L66" s="12" t="n">
         <x:f>Produits!V66</x:f>
@@ -17728,8 +17826,9 @@
         <x:f>Produits!L67</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K67" s="12" t="str">
+      <x:c r="K67" s="12" t="n">
         <x:f>Produits!U67</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L67" s="12" t="n">
         <x:f>Produits!V67</x:f>
@@ -17797,8 +17896,9 @@
         <x:f>Produits!L68</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K68" s="12" t="str">
+      <x:c r="K68" s="12" t="n">
         <x:f>Produits!U68</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L68" s="12" t="n">
         <x:f>Produits!V68</x:f>
@@ -17866,8 +17966,9 @@
         <x:f>Produits!L69</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K69" s="12" t="str">
+      <x:c r="K69" s="12" t="n">
         <x:f>Produits!U69</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L69" s="12" t="n">
         <x:f>Produits!V69</x:f>
@@ -17935,8 +18036,9 @@
         <x:f>Produits!L70</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K70" s="12" t="str">
+      <x:c r="K70" s="12" t="n">
         <x:f>Produits!U70</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L70" s="12" t="n">
         <x:f>Produits!V70</x:f>
@@ -18004,8 +18106,9 @@
         <x:f>Produits!L71</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K71" s="12" t="str">
+      <x:c r="K71" s="12" t="n">
         <x:f>Produits!U71</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L71" s="12" t="n">
         <x:f>Produits!V71</x:f>
@@ -18073,8 +18176,9 @@
         <x:f>Produits!L72</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K72" s="12" t="str">
+      <x:c r="K72" s="12" t="n">
         <x:f>Produits!U72</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L72" s="12" t="n">
         <x:f>Produits!V72</x:f>
@@ -18142,8 +18246,9 @@
         <x:f>Produits!L73</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K73" s="12" t="str">
+      <x:c r="K73" s="12" t="n">
         <x:f>Produits!U73</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L73" s="12" t="n">
         <x:f>Produits!V73</x:f>
@@ -18211,8 +18316,9 @@
         <x:f>Produits!L74</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K74" s="12" t="str">
+      <x:c r="K74" s="12" t="n">
         <x:f>Produits!U74</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L74" s="12" t="n">
         <x:f>Produits!V74</x:f>
@@ -18280,8 +18386,9 @@
         <x:f>Produits!L75</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K75" s="12" t="str">
+      <x:c r="K75" s="12" t="n">
         <x:f>Produits!U75</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L75" s="12" t="n">
         <x:f>Produits!V75</x:f>
@@ -18349,8 +18456,9 @@
         <x:f>Produits!L76</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K76" s="12" t="str">
+      <x:c r="K76" s="12" t="n">
         <x:f>Produits!U76</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L76" s="12" t="n">
         <x:f>Produits!V76</x:f>
@@ -18418,8 +18526,9 @@
         <x:f>Produits!L77</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K77" s="12" t="str">
+      <x:c r="K77" s="12" t="n">
         <x:f>Produits!U77</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L77" s="12" t="n">
         <x:f>Produits!V77</x:f>
@@ -18487,8 +18596,9 @@
         <x:f>Produits!L78</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K78" s="12" t="str">
+      <x:c r="K78" s="12" t="n">
         <x:f>Produits!U78</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L78" s="12" t="n">
         <x:f>Produits!V78</x:f>
@@ -18556,8 +18666,9 @@
         <x:f>Produits!L79</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K79" s="12" t="str">
+      <x:c r="K79" s="12" t="n">
         <x:f>Produits!U79</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L79" s="12" t="n">
         <x:f>Produits!V79</x:f>
@@ -18625,8 +18736,9 @@
         <x:f>Produits!L80</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K80" s="12" t="str">
+      <x:c r="K80" s="12" t="n">
         <x:f>Produits!U80</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L80" s="12" t="n">
         <x:f>Produits!V80</x:f>
@@ -18694,8 +18806,9 @@
         <x:f>Produits!L81</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K81" s="12" t="str">
+      <x:c r="K81" s="12" t="n">
         <x:f>Produits!U81</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L81" s="12" t="n">
         <x:f>Produits!V81</x:f>
@@ -18763,8 +18876,9 @@
         <x:f>Produits!L82</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K82" s="12" t="str">
+      <x:c r="K82" s="12" t="n">
         <x:f>Produits!U82</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L82" s="12" t="n">
         <x:f>Produits!V82</x:f>
@@ -18832,8 +18946,9 @@
         <x:f>Produits!L83</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K83" s="12" t="str">
+      <x:c r="K83" s="12" t="n">
         <x:f>Produits!U83</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L83" s="12" t="n">
         <x:f>Produits!V83</x:f>
@@ -18901,8 +19016,9 @@
         <x:f>Produits!L84</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K84" s="12" t="str">
+      <x:c r="K84" s="12" t="n">
         <x:f>Produits!U84</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L84" s="12" t="n">
         <x:f>Produits!V84</x:f>
@@ -18970,8 +19086,9 @@
         <x:f>Produits!L85</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K85" s="12" t="str">
+      <x:c r="K85" s="12" t="n">
         <x:f>Produits!U85</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L85" s="12" t="n">
         <x:f>Produits!V85</x:f>
@@ -19039,8 +19156,9 @@
         <x:f>Produits!L86</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K86" s="12" t="str">
+      <x:c r="K86" s="12" t="n">
         <x:f>Produits!U86</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L86" s="12" t="n">
         <x:f>Produits!V86</x:f>
@@ -19108,8 +19226,9 @@
         <x:f>Produits!L87</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K87" s="12" t="str">
+      <x:c r="K87" s="12" t="n">
         <x:f>Produits!U87</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L87" s="12" t="n">
         <x:f>Produits!V87</x:f>
@@ -19177,8 +19296,9 @@
         <x:f>Produits!L88</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K88" s="12" t="str">
+      <x:c r="K88" s="12" t="n">
         <x:f>Produits!U88</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L88" s="12" t="n">
         <x:f>Produits!V88</x:f>
@@ -19246,8 +19366,9 @@
         <x:f>Produits!L89</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K89" s="12" t="str">
+      <x:c r="K89" s="12" t="n">
         <x:f>Produits!U89</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L89" s="12" t="n">
         <x:f>Produits!V89</x:f>
@@ -19315,8 +19436,9 @@
         <x:f>Produits!L90</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K90" s="12" t="str">
+      <x:c r="K90" s="12" t="n">
         <x:f>Produits!U90</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L90" s="12" t="n">
         <x:f>Produits!V90</x:f>
@@ -19384,8 +19506,9 @@
         <x:f>Produits!L91</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K91" s="12" t="str">
+      <x:c r="K91" s="12" t="n">
         <x:f>Produits!U91</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L91" s="12" t="n">
         <x:f>Produits!V91</x:f>
@@ -19453,8 +19576,9 @@
         <x:f>Produits!L92</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K92" s="12" t="str">
+      <x:c r="K92" s="12" t="n">
         <x:f>Produits!U92</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L92" s="12" t="n">
         <x:f>Produits!V92</x:f>
@@ -19522,8 +19646,9 @@
         <x:f>Produits!L93</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K93" s="12" t="str">
+      <x:c r="K93" s="12" t="n">
         <x:f>Produits!U93</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L93" s="12" t="n">
         <x:f>Produits!V93</x:f>
@@ -19591,8 +19716,9 @@
         <x:f>Produits!L94</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K94" s="12" t="str">
+      <x:c r="K94" s="12" t="n">
         <x:f>Produits!U94</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L94" s="12" t="n">
         <x:f>Produits!V94</x:f>
@@ -19660,8 +19786,9 @@
         <x:f>Produits!L95</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K95" s="12" t="str">
+      <x:c r="K95" s="12" t="n">
         <x:f>Produits!U95</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L95" s="12" t="n">
         <x:f>Produits!V95</x:f>
@@ -19729,8 +19856,9 @@
         <x:f>Produits!L96</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K96" s="12" t="str">
+      <x:c r="K96" s="12" t="n">
         <x:f>Produits!U96</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L96" s="12" t="n">
         <x:f>Produits!V96</x:f>
@@ -19798,8 +19926,9 @@
         <x:f>Produits!L97</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K97" s="12" t="str">
+      <x:c r="K97" s="12" t="n">
         <x:f>Produits!U97</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L97" s="12" t="n">
         <x:f>Produits!V97</x:f>
@@ -19867,8 +19996,9 @@
         <x:f>Produits!L98</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K98" s="12" t="str">
+      <x:c r="K98" s="12" t="n">
         <x:f>Produits!U98</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L98" s="12" t="n">
         <x:f>Produits!V98</x:f>
@@ -19936,8 +20066,9 @@
         <x:f>Produits!L99</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K99" s="12" t="str">
+      <x:c r="K99" s="12" t="n">
         <x:f>Produits!U99</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L99" s="12" t="n">
         <x:f>Produits!V99</x:f>
@@ -20005,8 +20136,9 @@
         <x:f>Produits!L100</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K100" s="12" t="str">
+      <x:c r="K100" s="12" t="n">
         <x:f>Produits!U100</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L100" s="12" t="n">
         <x:f>Produits!V100</x:f>
@@ -20074,8 +20206,9 @@
         <x:f>Produits!L101</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K101" s="12" t="str">
+      <x:c r="K101" s="12" t="n">
         <x:f>Produits!U101</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L101" s="12" t="n">
         <x:f>Produits!V101</x:f>
@@ -20143,8 +20276,9 @@
         <x:f>Produits!L102</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K102" s="12" t="str">
+      <x:c r="K102" s="12" t="n">
         <x:f>Produits!U102</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L102" s="12" t="n">
         <x:f>Produits!V102</x:f>
@@ -20212,8 +20346,9 @@
         <x:f>Produits!L103</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K103" s="12" t="str">
+      <x:c r="K103" s="12" t="n">
         <x:f>Produits!U103</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L103" s="12" t="n">
         <x:f>Produits!V103</x:f>

--- a/data/import/MuscuGuide_Base_Produits.xlsx
+++ b/data/import/MuscuGuide_Base_Produits.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rd2e18a93e3fb434d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produits" sheetId="2" r:id="Rf761825655804eb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notation" sheetId="3" r:id="R1657e877bbcd4e3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Claude" sheetId="4" r:id="Rf3cff52f8837413f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="5" r:id="R7bd93243be6b450a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="6" r:id="Rf9dadfb54df84384"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R522bf75483b04886"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produits" sheetId="2" r:id="R34840a6fb0594569"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notation" sheetId="3" r:id="R401ff5e0443743be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Claude" sheetId="4" r:id="Rd16a4a0e530e4800"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="5" r:id="R73bbdd50b8fe41e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="6" r:id="R4c621db2a7974146"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -435,7 +435,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1d6af66b31564bd4"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R52766ea4b689480e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -687,7 +687,7 @@
       </x:c>
       <x:c r="B4" s="12" t="n">
         <x:f>COUNTA(Produits!E4:E250)</x:f>
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C4" s="12"/>
       <x:c r="D4" s="12" t="str">
@@ -747,7 +747,7 @@
       </x:c>
       <x:c r="B6" s="12" t="n">
         <x:f>COUNTIF(Produits!AG4:AG250,"Validé")</x:f>
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C6" s="12"/>
       <x:c r="D6" s="12" t="str">
@@ -777,7 +777,7 @@
       </x:c>
       <x:c r="B7" s="12" t="n">
         <x:f>COUNTIF(Produits!AG4:AG250,"À rechercher")</x:f>
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="12"/>
       <x:c r="D7" s="12" t="str">
@@ -807,7 +807,7 @@
       </x:c>
       <x:c r="B8" s="38" t="n">
         <x:f>IFERROR(AVERAGE(Produits!U4:U250),0)</x:f>
-        <x:v>88</x:v>
+        <x:v>87.77777777777777</x:v>
       </x:c>
       <x:c r="C8" s="12"/>
       <x:c r="D8" s="12" t="str">
@@ -824,7 +824,7 @@
       </x:c>
       <x:c r="G8" s="12" t="n">
         <x:f>COUNTIFS(Produits!B:B,D8,Produits!AG:AG,"Validé")</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H8" s="46" t="n">
         <x:f>IFERROR(F8/E8,0)</x:f>
@@ -901,7 +901,7 @@
       </x:c>
       <x:c r="E11" s="12" t="n">
         <x:f>COUNTIF(Produits!B:B,D11)</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F11" s="12" t="n">
         <x:f>COUNTIFS(Produits!B:B,D11,Produits!H:H,"??????????")</x:f>
@@ -909,7 +909,7 @@
       </x:c>
       <x:c r="G11" s="12" t="n">
         <x:f>COUNTIFS(Produits!B:B,D11,Produits!AG:AG,"Validé")</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H11" s="46" t="n">
         <x:f>IFERROR(F11/E11,0)</x:f>
@@ -1259,7 +1259,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a8e9b9a759245ef"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3a2d5f181e24d1c"/>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -1922,14 +1922,20 @@
         <x:v>Choix MuscuGuide</x:v>
       </x:c>
       <x:c r="E10" s="12" t="str">
-        <x:v>SelectTech 552</x:v>
+        <x:v>Bowflex SelectTech 552</x:v>
       </x:c>
       <x:c r="F10" s="12" t="str">
         <x:v>Bowflex</x:v>
       </x:c>
-      <x:c r="G10" s="12" t="str"/>
-      <x:c r="H10" s="12" t="str"/>
-      <x:c r="I10" s="12" t="str"/>
+      <x:c r="G10" s="12" t="str">
+        <x:v>15 niveaux — jusqu’à 23,9 kg par haltère</x:v>
+      </x:c>
+      <x:c r="H10" s="12" t="str">
+        <x:v>B09MT5C8VB</x:v>
+      </x:c>
+      <x:c r="I10" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B09MT5C8VB</x:v>
+      </x:c>
       <x:c r="J10" s="12" t="str"/>
       <x:c r="K10" s="12" t="str">
         <x:f>IF(OR(H10="",J10=""),"", "https://www.amazon.fr/dp/"&amp;H10&amp;"?tag="&amp;J10)</x:f>
@@ -1939,17 +1945,31 @@
       <x:c r="N10" s="12" t="str">
         <x:v>Performance</x:v>
       </x:c>
-      <x:c r="O10" s="12" t="str"/>
-      <x:c r="P10" s="12" t="str"/>
-      <x:c r="Q10" s="12" t="str"/>
-      <x:c r="R10" s="12" t="str"/>
-      <x:c r="S10" s="12" t="str"/>
-      <x:c r="T10" s="12" t="str"/>
-      <x:c r="U10" s="12" t="str">
+      <x:c r="O10" s="12" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P10" s="12" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="Q10" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="R10" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="S10" s="12" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="T10" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="U10" s="12" t="n">
         <x:f>IF(COUNTA(O10:T10)=0,"",SUM(O10:T10))</x:f>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="V10" s="12" t="str">
         <x:f>IF(U10="","",IF(U10&gt;=95,"Exceptionnel",IF(U10&gt;=90,"Excellent",IF(U10&gt;=85,"Très bon",IF(U10&gt;=80,"Bon",IF(U10&gt;=70,"Correct","À revoir"))))))</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="W10" s="12" t="str">
         <x:v>Oui</x:v>
@@ -1961,26 +1981,30 @@
         <x:v>Oui</x:v>
       </x:c>
       <x:c r="Z10" s="12" t="str">
-        <x:v>Paire réglable iconique pour home gym compact.</x:v>
+        <x:v>Une référence fiable et compacte pour s’entraîner à domicile, avec un réglage rapide et une large plage de charges.</x:v>
       </x:c>
       <x:c r="AA10" s="12" t="str">
-        <x:v>Réglage rapide | Gain de place | Marque connue</x:v>
+        <x:v>15 niveaux de charge | Réglage rapide | Gain de place important | Marque reconnue | Polyvalent</x:v>
       </x:c>
       <x:c r="AB10" s="12" t="str">
-        <x:v>Amplitude encombrante | Prix</x:v>
+        <x:v>Format assez long aux faibles charges | Mécanisme à manipuler avec soin | Tarif supérieur aux modèles d’entrée de gamme</x:v>
       </x:c>
       <x:c r="AC10" s="12" t="str">
-        <x:v>Home gym polyvalent</x:v>
-      </x:c>
-      <x:c r="AD10" s="12" t="str"/>
-      <x:c r="AE10" s="38" t="str"/>
-      <x:c r="AF10" s="40" t="str"/>
+        <x:v>Débutant à confirmé recherchant une solution polyvalente et éprouvée</x:v>
+      </x:c>
+      <x:c r="AD10" s="12"/>
+      <x:c r="AE10" s="38"/>
+      <x:c r="AF10" s="55" t="n">
+        <x:v>46238</x:v>
+      </x:c>
       <x:c r="AG10" s="12" t="str">
-        <x:v>À rechercher</x:v>
-      </x:c>
-      <x:c r="AH10" s="12" t="str"/>
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH10" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B09MT5C8VB</x:v>
+      </x:c>
       <x:c r="AI10" s="12" t="str">
-        <x:v>Vérifier si l'offre est à l'unité ou en paire.</x:v>
+        <x:v>ASIN Amazon FR vérifié le 04/08/2026. Plage et 15 réglages confirmés par la documentation Bowflex. Note et nombre d’avis Amazon laissés vides.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1997,14 +2021,20 @@
         <x:v>Meilleur rapport qualité/prix</x:v>
       </x:c>
       <x:c r="E11" s="12" t="str">
-        <x:v>Haltères réglables</x:v>
+        <x:v>Paire d’haltères réglables 2 × 12 kg</x:v>
       </x:c>
       <x:c r="F11" s="12" t="str">
         <x:v>DH FitLife</x:v>
       </x:c>
-      <x:c r="G11" s="12" t="str"/>
-      <x:c r="H11" s="12" t="str"/>
-      <x:c r="I11" s="12" t="str"/>
+      <x:c r="G11" s="12" t="str">
+        <x:v>5 niveaux — sélection rapide à une main</x:v>
+      </x:c>
+      <x:c r="H11" s="12" t="str">
+        <x:v>B0D1HJLJLD</x:v>
+      </x:c>
+      <x:c r="I11" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0D1HJLJLD</x:v>
+      </x:c>
       <x:c r="J11" s="12" t="str"/>
       <x:c r="K11" s="12" t="str">
         <x:f>IF(OR(H11="",J11=""),"", "https://www.amazon.fr/dp/"&amp;H11&amp;"?tag="&amp;J11)</x:f>
@@ -2014,17 +2044,31 @@
       <x:c r="N11" s="12" t="str">
         <x:v>Essentials</x:v>
       </x:c>
-      <x:c r="O11" s="12" t="str"/>
-      <x:c r="P11" s="12" t="str"/>
-      <x:c r="Q11" s="12" t="str"/>
-      <x:c r="R11" s="12" t="str"/>
-      <x:c r="S11" s="12" t="str"/>
-      <x:c r="T11" s="12" t="str"/>
-      <x:c r="U11" s="12" t="str">
+      <x:c r="O11" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P11" s="12" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q11" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="R11" s="12" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="S11" s="12" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="T11" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="U11" s="12" t="n">
         <x:f>IF(COUNTA(O11:T11)=0,"",SUM(O11:T11))</x:f>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="V11" s="12" t="str">
         <x:f>IF(U11="","",IF(U11&gt;=95,"Exceptionnel",IF(U11&gt;=90,"Excellent",IF(U11&gt;=85,"Très bon",IF(U11&gt;=80,"Bon",IF(U11&gt;=70,"Correct","À revoir"))))))</x:f>
+        <x:v>Très bon</x:v>
       </x:c>
       <x:c r="W11" s="12" t="str">
         <x:v>Oui</x:v>
@@ -2034,26 +2078,34 @@
       </x:c>
       <x:c r="Y11" s="12" t="str"/>
       <x:c r="Z11" s="12" t="str">
-        <x:v>Alternative plus accessible pour débuter.</x:v>
+        <x:v>Une paire accessible et facile à utiliser, particulièrement adaptée aux débutants et aux entraînements légers à modérés.</x:v>
       </x:c>
       <x:c r="AA11" s="12" t="str">
-        <x:v>Prix | Polyvalence | Gain de place</x:v>
+        <x:v>Paire complète | Excellent rapport qualité/prix | Réglage rapide | Format compact | Poignée antidérapante</x:v>
       </x:c>
       <x:c r="AB11" s="12" t="str">
-        <x:v>Disponibilité et SAV à vérifier</x:v>
+        <x:v>Charge maximale limitée à 12 kg par haltère | Seulement 5 niveaux | Moins évolutif pour les pratiquants confirmés</x:v>
       </x:c>
       <x:c r="AC11" s="12" t="str">
-        <x:v>Débutant / intermédiaire</x:v>
-      </x:c>
-      <x:c r="AD11" s="12" t="str"/>
-      <x:c r="AE11" s="38" t="str"/>
-      <x:c r="AF11" s="40" t="str"/>
+        <x:v>Débutant ou utilisateur fitness avec budget maîtrisé</x:v>
+      </x:c>
+      <x:c r="AD11" s="12" t="n">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="AE11" s="38" t="n">
+        <x:v>4.6</x:v>
+      </x:c>
+      <x:c r="AF11" s="55" t="n">
+        <x:v>46238</x:v>
+      </x:c>
       <x:c r="AG11" s="12" t="str">
-        <x:v>À rechercher</x:v>
-      </x:c>
-      <x:c r="AH11" s="12" t="str"/>
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH11" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0D1HJLJLD</x:v>
+      </x:c>
       <x:c r="AI11" s="12" t="str">
-        <x:v>Sélection à confirmer selon offre Amazon FR.</x:v>
+        <x:v>ASIN, note Amazon 4,6/5 et 340 évaluations vérifiés le 04/08/2026. Les données Amazon peuvent évoluer.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -2070,14 +2122,20 @@
         <x:v>Premium</x:v>
       </x:c>
       <x:c r="E12" s="12" t="str">
-        <x:v>NÜOBELL</x:v>
+        <x:v>NÜOBELL 232</x:v>
       </x:c>
       <x:c r="F12" s="12" t="str">
         <x:v>NÜO Athletics</x:v>
       </x:c>
-      <x:c r="G12" s="12" t="str"/>
-      <x:c r="H12" s="12" t="str"/>
-      <x:c r="I12" s="12" t="str"/>
+      <x:c r="G12" s="12" t="str">
+        <x:v>Paire 2 à 32 kg — incréments de 2 kg</x:v>
+      </x:c>
+      <x:c r="H12" s="12" t="str">
+        <x:v>B0FGSRYX7C</x:v>
+      </x:c>
+      <x:c r="I12" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0FGSRYX7C</x:v>
+      </x:c>
       <x:c r="J12" s="12" t="str"/>
       <x:c r="K12" s="12" t="str">
         <x:f>IF(OR(H12="",J12=""),"", "https://www.amazon.fr/dp/"&amp;H12&amp;"?tag="&amp;J12)</x:f>
@@ -2087,17 +2145,31 @@
       <x:c r="N12" s="12" t="str">
         <x:v>Elite</x:v>
       </x:c>
-      <x:c r="O12" s="12" t="str"/>
-      <x:c r="P12" s="12" t="str"/>
-      <x:c r="Q12" s="12" t="str"/>
-      <x:c r="R12" s="12" t="str"/>
-      <x:c r="S12" s="12" t="str"/>
-      <x:c r="T12" s="12" t="str"/>
-      <x:c r="U12" s="12" t="str">
+      <x:c r="O12" s="12" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="P12" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="Q12" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="R12" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="S12" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="T12" s="12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="U12" s="12" t="n">
         <x:f>IF(COUNTA(O12:T12)=0,"",SUM(O12:T12))</x:f>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="V12" s="12" t="str">
         <x:f>IF(U12="","",IF(U12&gt;=95,"Exceptionnel",IF(U12&gt;=90,"Excellent",IF(U12&gt;=85,"Très bon",IF(U12&gt;=80,"Bon",IF(U12&gt;=70,"Correct","À revoir"))))))</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="W12" s="12" t="str"/>
       <x:c r="X12" s="12" t="str">
@@ -2107,26 +2179,30 @@
         <x:v>Oui</x:v>
       </x:c>
       <x:c r="Z12" s="12" t="str">
-        <x:v>Solution premium avec changement de charge fluide.</x:v>
+        <x:v>Une solution premium très fluide, proche de la sensation d’un haltère classique, destinée aux home gyms exigeants.</x:v>
       </x:c>
       <x:c r="AA12" s="12" t="str">
-        <x:v>Finition | Ergonomie | Réglage rapide</x:v>
+        <x:v>Plage 2 à 32 kg | Réglage par rotation | Poignée en aluminium | Équilibre proche d’un haltère fixe | Paire compacte</x:v>
       </x:c>
       <x:c r="AB12" s="12" t="str">
-        <x:v>Très cher | Disponibilité</x:v>
+        <x:v>Prix très élevé | Ne doit pas être lâché au sol | Encombrement et poids importants au réglage maximal</x:v>
       </x:c>
       <x:c r="AC12" s="12" t="str">
-        <x:v>Home gym premium</x:v>
-      </x:c>
-      <x:c r="AD12" s="12" t="str"/>
-      <x:c r="AE12" s="38" t="str"/>
-      <x:c r="AF12" s="40" t="str"/>
+        <x:v>Intermédiaire ou confirmé recherchant une solution premium et durable</x:v>
+      </x:c>
+      <x:c r="AD12" s="12"/>
+      <x:c r="AE12" s="38"/>
+      <x:c r="AF12" s="55" t="n">
+        <x:v>46238</x:v>
+      </x:c>
       <x:c r="AG12" s="12" t="str">
-        <x:v>À rechercher</x:v>
-      </x:c>
-      <x:c r="AH12" s="12" t="str"/>
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH12" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0FGSRYX7C</x:v>
+      </x:c>
       <x:c r="AI12" s="12" t="str">
-        <x:v>Vérifier distributeur officiel.</x:v>
+        <x:v>ASIN Amazon FR vérifié le 04/08/2026. Caractéristiques 2–32 kg, incréments de 2 kg et vente par paire confirmées par NÜO Athletics. Note Amazon laissée vide.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -3311,133 +3387,309 @@
       </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="12"/>
-      <x:c r="B28" s="12"/>
-      <x:c r="C28" s="12"/>
-      <x:c r="D28" s="12"/>
-      <x:c r="E28" s="12"/>
-      <x:c r="F28" s="12"/>
-      <x:c r="G28" s="12"/>
-      <x:c r="H28" s="12"/>
-      <x:c r="I28" s="12"/>
+      <x:c r="A28" s="12" t="str">
+        <x:v>MG-HOME-001</x:v>
+      </x:c>
+      <x:c r="B28" s="12" t="str">
+        <x:v>Station Home Gym</x:v>
+      </x:c>
+      <x:c r="C28" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D28" s="12" t="str">
+        <x:v>Choix MuscuGuide</x:v>
+      </x:c>
+      <x:c r="E28" s="12" t="str">
+        <x:v>Sportstech HGX100</x:v>
+      </x:c>
+      <x:c r="F28" s="12" t="str">
+        <x:v>Sportstech</x:v>
+      </x:c>
+      <x:c r="G28" s="12" t="str">
+        <x:v>30+ exercices — 12 poids pour un total de 70 kg</x:v>
+      </x:c>
+      <x:c r="H28" s="12" t="str">
+        <x:v>B07FCHL7TL</x:v>
+      </x:c>
+      <x:c r="I28" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B07FCHL7TL</x:v>
+      </x:c>
       <x:c r="J28" s="12"/>
       <x:c r="K28" s="12" t="str">
         <x:f>IF(OR(H28="",J28=""),"", "https://www.amazon.fr/dp/"&amp;H28&amp;"?tag="&amp;J28)</x:f>
       </x:c>
       <x:c r="L28" s="12"/>
       <x:c r="M28" s="36"/>
-      <x:c r="N28" s="12"/>
-      <x:c r="O28" s="12"/>
-      <x:c r="P28" s="12"/>
-      <x:c r="Q28" s="12"/>
-      <x:c r="R28" s="12"/>
-      <x:c r="S28" s="12"/>
-      <x:c r="T28" s="12"/>
-      <x:c r="U28" s="12" t="str">
+      <x:c r="N28" s="12" t="str">
+        <x:v>Performance</x:v>
+      </x:c>
+      <x:c r="O28" s="12" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P28" s="12" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="Q28" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="R28" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="S28" s="12" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="T28" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="U28" s="12" t="n">
         <x:f>IF(COUNTA(O28:T28)=0,"",SUM(O28:T28))</x:f>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="V28" s="12" t="str">
         <x:f>IF(U28="","",IF(U28&gt;=95,"Exceptionnel",IF(U28&gt;=90,"Excellent",IF(U28&gt;=85,"Très bon",IF(U28&gt;=80,"Bon",IF(U28&gt;=70,"Correct","À revoir"))))))</x:f>
-      </x:c>
-      <x:c r="W28" s="12"/>
-      <x:c r="X28" s="12"/>
-      <x:c r="Y28" s="12"/>
-      <x:c r="Z28" s="12"/>
-      <x:c r="AA28" s="12"/>
-      <x:c r="AB28" s="12"/>
-      <x:c r="AC28" s="12"/>
-      <x:c r="AD28" s="12"/>
-      <x:c r="AE28" s="38"/>
-      <x:c r="AF28" s="40"/>
-      <x:c r="AG28" s="12"/>
-      <x:c r="AH28" s="12"/>
-      <x:c r="AI28" s="12"/>
+        <x:v>Excellent</x:v>
+      </x:c>
+      <x:c r="W28" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="X28" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="Y28" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="Z28" s="12" t="str">
+        <x:v>Une station complète et robuste pour entraîner l’ensemble du corps à domicile, avec une large variété d’exercices guidés.</x:v>
+      </x:c>
+      <x:c r="AA28" s="12" t="str">
+        <x:v>Plus de 30 exercices | Bloc de 70 kg | Construction stable | Nombreux accessoires | Bonne réputation client</x:v>
+      </x:c>
+      <x:c r="AB28" s="12" t="str">
+        <x:v>Montage long | Encombrement important | Charge limitée pour certains pratiquants très avancés</x:v>
+      </x:c>
+      <x:c r="AC28" s="12" t="str">
+        <x:v>Débutant à confirmé disposant d’un espace dédié au home gym</x:v>
+      </x:c>
+      <x:c r="AD28" s="12" t="n">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="AE28" s="38" t="n">
+        <x:v>4.4</x:v>
+      </x:c>
+      <x:c r="AF28" s="55" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="AG28" s="12" t="str">
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH28" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B07FCHL7TL</x:v>
+      </x:c>
+      <x:c r="AI28" s="12" t="str">
+        <x:v>ASIN, note Amazon 4,4/5 et 103 évaluations vérifiés le 04/08/2026. Les 30+ exercices et les 70 kg sont confirmés par Sportstech.</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="12"/>
-      <x:c r="B29" s="12"/>
-      <x:c r="C29" s="12"/>
-      <x:c r="D29" s="12"/>
-      <x:c r="E29" s="12"/>
-      <x:c r="F29" s="12"/>
-      <x:c r="G29" s="12"/>
-      <x:c r="H29" s="12"/>
-      <x:c r="I29" s="12"/>
+      <x:c r="A29" s="12" t="str">
+        <x:v>MG-HOME-002</x:v>
+      </x:c>
+      <x:c r="B29" s="12" t="str">
+        <x:v>Station Home Gym</x:v>
+      </x:c>
+      <x:c r="C29" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D29" s="12" t="str">
+        <x:v>Meilleur rapport qualité/prix</x:v>
+      </x:c>
+      <x:c r="E29" s="12" t="str">
+        <x:v>ISE SY-4009 50-en-1</x:v>
+      </x:c>
+      <x:c r="F29" s="12" t="str">
+        <x:v>ISE</x:v>
+      </x:c>
+      <x:c r="G29" s="12" t="str">
+        <x:v>Station multifonction pour entraînement complet du corps</x:v>
+      </x:c>
+      <x:c r="H29" s="12" t="str">
+        <x:v>B07B7QN69F</x:v>
+      </x:c>
+      <x:c r="I29" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B07B7QN69F</x:v>
+      </x:c>
       <x:c r="J29" s="12"/>
       <x:c r="K29" s="12" t="str">
         <x:f>IF(OR(H29="",J29=""),"", "https://www.amazon.fr/dp/"&amp;H29&amp;"?tag="&amp;J29)</x:f>
       </x:c>
       <x:c r="L29" s="12"/>
       <x:c r="M29" s="36"/>
-      <x:c r="N29" s="12"/>
-      <x:c r="O29" s="12"/>
-      <x:c r="P29" s="12"/>
-      <x:c r="Q29" s="12"/>
-      <x:c r="R29" s="12"/>
-      <x:c r="S29" s="12"/>
-      <x:c r="T29" s="12"/>
-      <x:c r="U29" s="12" t="str">
+      <x:c r="N29" s="12" t="str">
+        <x:v>Essentials</x:v>
+      </x:c>
+      <x:c r="O29" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P29" s="12" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q29" s="12" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="R29" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="S29" s="12" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="T29" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="U29" s="12" t="n">
         <x:f>IF(COUNTA(O29:T29)=0,"",SUM(O29:T29))</x:f>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="V29" s="12" t="str">
         <x:f>IF(U29="","",IF(U29&gt;=95,"Exceptionnel",IF(U29&gt;=90,"Excellent",IF(U29&gt;=85,"Très bon",IF(U29&gt;=80,"Bon",IF(U29&gt;=70,"Correct","À revoir"))))))</x:f>
-      </x:c>
-      <x:c r="W29" s="12"/>
-      <x:c r="X29" s="12"/>
+        <x:v>Bon</x:v>
+      </x:c>
+      <x:c r="W29" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="X29" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
       <x:c r="Y29" s="12"/>
-      <x:c r="Z29" s="12"/>
-      <x:c r="AA29" s="12"/>
-      <x:c r="AB29" s="12"/>
-      <x:c r="AC29" s="12"/>
-      <x:c r="AD29" s="12"/>
-      <x:c r="AE29" s="38"/>
-      <x:c r="AF29" s="40"/>
-      <x:c r="AG29" s="12"/>
-      <x:c r="AH29" s="12"/>
-      <x:c r="AI29" s="12"/>
+      <x:c r="Z29" s="12" t="str">
+        <x:v>Une station riche en fonctions et accessible, intéressante pour débuter ou équiper un home gym avec un budget maîtrisé.</x:v>
+      </x:c>
+      <x:c r="AA29" s="12" t="str">
+        <x:v>Très nombreuses possibilités d’exercice | Bon rapport équipement/prix | Travail du haut et du bas du corps | Structure tout-en-un</x:v>
+      </x:c>
+      <x:c r="AB29" s="12" t="str">
+        <x:v>Note client plus moyenne | Montage exigeant | Prend beaucoup de place | Finitions moins premium</x:v>
+      </x:c>
+      <x:c r="AC29" s="12" t="str">
+        <x:v>Débutant ou intermédiaire recherchant un appareil complet à prix contenu</x:v>
+      </x:c>
+      <x:c r="AD29" s="12" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="AE29" s="38" t="n">
+        <x:v>3.9</x:v>
+      </x:c>
+      <x:c r="AF29" s="55" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="AG29" s="12" t="str">
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH29" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B07B7QN69F</x:v>
+      </x:c>
+      <x:c r="AI29" s="12" t="str">
+        <x:v>ASIN, note Amazon 3,9/5 et 21 commentaires vérifiés le 04/08/2026. Dimensions Amazon annoncées : 214 × 180 × 214 cm.</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="12"/>
-      <x:c r="B30" s="12"/>
-      <x:c r="C30" s="12"/>
-      <x:c r="D30" s="12"/>
-      <x:c r="E30" s="12"/>
-      <x:c r="F30" s="12"/>
-      <x:c r="G30" s="12"/>
-      <x:c r="H30" s="12"/>
-      <x:c r="I30" s="12"/>
+      <x:c r="A30" s="12" t="str">
+        <x:v>MG-HOME-003</x:v>
+      </x:c>
+      <x:c r="B30" s="12" t="str">
+        <x:v>Station Home Gym</x:v>
+      </x:c>
+      <x:c r="C30" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D30" s="12" t="str">
+        <x:v>Premium</x:v>
+      </x:c>
+      <x:c r="E30" s="12" t="str">
+        <x:v>Dione HG5 Multi-Gym</x:v>
+      </x:c>
+      <x:c r="F30" s="12" t="str">
+        <x:v>Dione</x:v>
+      </x:c>
+      <x:c r="G30" s="12" t="str">
+        <x:v>65 kg inclus — extensible à 100 kg — sac de frappe</x:v>
+      </x:c>
+      <x:c r="H30" s="12" t="str">
+        <x:v>B08CS1PRRJ</x:v>
+      </x:c>
+      <x:c r="I30" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B08CS1PRRJ</x:v>
+      </x:c>
       <x:c r="J30" s="12"/>
       <x:c r="K30" s="12" t="str">
         <x:f>IF(OR(H30="",J30=""),"", "https://www.amazon.fr/dp/"&amp;H30&amp;"?tag="&amp;J30)</x:f>
       </x:c>
       <x:c r="L30" s="12"/>
       <x:c r="M30" s="36"/>
-      <x:c r="N30" s="12"/>
-      <x:c r="O30" s="12"/>
-      <x:c r="P30" s="12"/>
-      <x:c r="Q30" s="12"/>
-      <x:c r="R30" s="12"/>
-      <x:c r="S30" s="12"/>
-      <x:c r="T30" s="12"/>
-      <x:c r="U30" s="12" t="str">
+      <x:c r="N30" s="12" t="str">
+        <x:v>Elite</x:v>
+      </x:c>
+      <x:c r="O30" s="12" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P30" s="12" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="Q30" s="12" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R30" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="S30" s="12" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="T30" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="U30" s="12" t="n">
         <x:f>IF(COUNTA(O30:T30)=0,"",SUM(O30:T30))</x:f>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="V30" s="12" t="str">
         <x:f>IF(U30="","",IF(U30&gt;=95,"Exceptionnel",IF(U30&gt;=90,"Excellent",IF(U30&gt;=85,"Très bon",IF(U30&gt;=80,"Bon",IF(U30&gt;=70,"Correct","À revoir"))))))</x:f>
+        <x:v>Très bon</x:v>
       </x:c>
       <x:c r="W30" s="12"/>
-      <x:c r="X30" s="12"/>
-      <x:c r="Y30" s="12"/>
-      <x:c r="Z30" s="12"/>
-      <x:c r="AA30" s="12"/>
-      <x:c r="AB30" s="12"/>
-      <x:c r="AC30" s="12"/>
-      <x:c r="AD30" s="12"/>
-      <x:c r="AE30" s="38"/>
-      <x:c r="AF30" s="40"/>
-      <x:c r="AG30" s="12"/>
-      <x:c r="AH30" s="12"/>
-      <x:c r="AI30" s="12"/>
+      <x:c r="X30" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="Y30" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="Z30" s="12" t="str">
+        <x:v>Une station très complète pour les foyers disposant d’une véritable pièce de sport, avec plusieurs postes et un sac de frappe.</x:v>
+      </x:c>
+      <x:c r="AA30" s="12" t="str">
+        <x:v>Plus de 44 exercices | 65 kg de poids inclus | Extensible à 100 kg | Sac de frappe inclus | Plusieurs utilisateurs possibles</x:v>
+      </x:c>
+      <x:c r="AB30" s="12" t="str">
+        <x:v>Très encombrante | Très lourde | Montage complexe | Investissement conséquent</x:v>
+      </x:c>
+      <x:c r="AC30" s="12" t="str">
+        <x:v>Intermédiaire ou confirmé souhaitant un home gym complet et permanent</x:v>
+      </x:c>
+      <x:c r="AD30" s="12" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="AE30" s="38" t="n">
+        <x:v>4.3</x:v>
+      </x:c>
+      <x:c r="AF30" s="55" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="AG30" s="12" t="str">
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH30" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B08CS1PRRJ</x:v>
+      </x:c>
+      <x:c r="AI30" s="12" t="str">
+        <x:v>ASIN, note Amazon 4,3/5 et 70 évaluations vérifiés le 04/08/2026. Plus de 44 exercices, 65 kg inclus et extension à 100 kg confirmés.</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="12"/>
@@ -12969,7 +13221,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95fec52e65ac4803"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4b651cd5c964ebc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13776,9 +14028,8 @@
         <x:f>Produits!L9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K9" s="12" t="n">
+      <x:c r="K9" s="12" t="str">
         <x:f>Produits!U9</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="L9" s="12" t="str">
         <x:f>Produits!V9</x:f>
@@ -13823,19 +14074,19 @@
       </x:c>
       <x:c r="E10" s="12" t="str">
         <x:f>Produits!E10</x:f>
-        <x:v>SelectTech 552</x:v>
+        <x:v>Bowflex SelectTech 552</x:v>
       </x:c>
       <x:c r="F10" s="12" t="str">
         <x:f>Produits!F10</x:f>
         <x:v>Bowflex</x:v>
       </x:c>
-      <x:c r="G10" s="12" t="n">
+      <x:c r="G10" s="12" t="str">
         <x:f>Produits!H10</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H10" s="12" t="n">
+        <x:v>B09MT5C8VB</x:v>
+      </x:c>
+      <x:c r="H10" s="12" t="str">
         <x:f>Produits!I10</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B09MT5C8VB</x:v>
       </x:c>
       <x:c r="I10" s="12" t="n">
         <x:f>Produits!K10</x:f>
@@ -13847,30 +14098,31 @@
       </x:c>
       <x:c r="K10" s="12" t="n">
         <x:f>Produits!U10</x:f>
-        <x:v>0</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="L10" s="12" t="str">
         <x:f>Produits!V10</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="M10" s="12" t="str">
         <x:f>Produits!Z10</x:f>
-        <x:v>Paire réglable iconique pour home gym compact.</x:v>
+        <x:v>Une référence fiable et compacte pour s’entraîner à domicile, avec un réglage rapide et une large plage de charges.</x:v>
       </x:c>
       <x:c r="N10" s="12" t="str">
         <x:f>Produits!AA10</x:f>
-        <x:v>Réglage rapide | Gain de place | Marque connue</x:v>
+        <x:v>15 niveaux de charge | Réglage rapide | Gain de place important | Marque reconnue | Polyvalent</x:v>
       </x:c>
       <x:c r="O10" s="12" t="str">
         <x:f>Produits!AB10</x:f>
-        <x:v>Amplitude encombrante | Prix</x:v>
+        <x:v>Format assez long aux faibles charges | Mécanisme à manipuler avec soin | Tarif supérieur aux modèles d’entrée de gamme</x:v>
       </x:c>
       <x:c r="P10" s="12" t="str">
         <x:f>Produits!AC10</x:f>
-        <x:v>Home gym polyvalent</x:v>
+        <x:v>Débutant à confirmé recherchant une solution polyvalente et éprouvée</x:v>
       </x:c>
       <x:c r="Q10" s="12" t="str">
         <x:f>Produits!AG10</x:f>
-        <x:v>À rechercher</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -13892,19 +14144,19 @@
       </x:c>
       <x:c r="E11" s="12" t="str">
         <x:f>Produits!E11</x:f>
-        <x:v>Haltères réglables</x:v>
+        <x:v>Paire d’haltères réglables 2 × 12 kg</x:v>
       </x:c>
       <x:c r="F11" s="12" t="str">
         <x:f>Produits!F11</x:f>
         <x:v>DH FitLife</x:v>
       </x:c>
-      <x:c r="G11" s="12" t="n">
+      <x:c r="G11" s="12" t="str">
         <x:f>Produits!H11</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H11" s="12" t="n">
+        <x:v>B0D1HJLJLD</x:v>
+      </x:c>
+      <x:c r="H11" s="12" t="str">
         <x:f>Produits!I11</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B0D1HJLJLD</x:v>
       </x:c>
       <x:c r="I11" s="12" t="n">
         <x:f>Produits!K11</x:f>
@@ -13916,31 +14168,31 @@
       </x:c>
       <x:c r="K11" s="12" t="n">
         <x:f>Produits!U11</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L11" s="12" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="L11" s="12" t="str">
         <x:f>Produits!V11</x:f>
-        <x:v>0</x:v>
+        <x:v>Très bon</x:v>
       </x:c>
       <x:c r="M11" s="12" t="str">
         <x:f>Produits!Z11</x:f>
-        <x:v>Alternative plus accessible pour débuter.</x:v>
+        <x:v>Une paire accessible et facile à utiliser, particulièrement adaptée aux débutants et aux entraînements légers à modérés.</x:v>
       </x:c>
       <x:c r="N11" s="12" t="str">
         <x:f>Produits!AA11</x:f>
-        <x:v>Prix | Polyvalence | Gain de place</x:v>
+        <x:v>Paire complète | Excellent rapport qualité/prix | Réglage rapide | Format compact | Poignée antidérapante</x:v>
       </x:c>
       <x:c r="O11" s="12" t="str">
         <x:f>Produits!AB11</x:f>
-        <x:v>Disponibilité et SAV à vérifier</x:v>
+        <x:v>Charge maximale limitée à 12 kg par haltère | Seulement 5 niveaux | Moins évolutif pour les pratiquants confirmés</x:v>
       </x:c>
       <x:c r="P11" s="12" t="str">
         <x:f>Produits!AC11</x:f>
-        <x:v>Débutant / intermédiaire</x:v>
+        <x:v>Débutant ou utilisateur fitness avec budget maîtrisé</x:v>
       </x:c>
       <x:c r="Q11" s="12" t="str">
         <x:f>Produits!AG11</x:f>
-        <x:v>À rechercher</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -13962,19 +14214,19 @@
       </x:c>
       <x:c r="E12" s="12" t="str">
         <x:f>Produits!E12</x:f>
-        <x:v>NÜOBELL</x:v>
+        <x:v>NÜOBELL 232</x:v>
       </x:c>
       <x:c r="F12" s="12" t="str">
         <x:f>Produits!F12</x:f>
         <x:v>NÜO Athletics</x:v>
       </x:c>
-      <x:c r="G12" s="12" t="n">
+      <x:c r="G12" s="12" t="str">
         <x:f>Produits!H12</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H12" s="12" t="n">
+        <x:v>B0FGSRYX7C</x:v>
+      </x:c>
+      <x:c r="H12" s="12" t="str">
         <x:f>Produits!I12</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B0FGSRYX7C</x:v>
       </x:c>
       <x:c r="I12" s="12" t="n">
         <x:f>Produits!K12</x:f>
@@ -13986,30 +14238,31 @@
       </x:c>
       <x:c r="K12" s="12" t="n">
         <x:f>Produits!U12</x:f>
-        <x:v>0</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="L12" s="12" t="str">
         <x:f>Produits!V12</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="M12" s="12" t="str">
         <x:f>Produits!Z12</x:f>
-        <x:v>Solution premium avec changement de charge fluide.</x:v>
+        <x:v>Une solution premium très fluide, proche de la sensation d’un haltère classique, destinée aux home gyms exigeants.</x:v>
       </x:c>
       <x:c r="N12" s="12" t="str">
         <x:f>Produits!AA12</x:f>
-        <x:v>Finition | Ergonomie | Réglage rapide</x:v>
+        <x:v>Plage 2 à 32 kg | Réglage par rotation | Poignée en aluminium | Équilibre proche d’un haltère fixe | Paire compacte</x:v>
       </x:c>
       <x:c r="O12" s="12" t="str">
         <x:f>Produits!AB12</x:f>
-        <x:v>Très cher | Disponibilité</x:v>
+        <x:v>Prix très élevé | Ne doit pas être lâché au sol | Encombrement et poids importants au réglage maximal</x:v>
       </x:c>
       <x:c r="P12" s="12" t="str">
         <x:f>Produits!AC12</x:f>
-        <x:v>Home gym premium</x:v>
+        <x:v>Intermédiaire ou confirmé recherchant une solution premium et durable</x:v>
       </x:c>
       <x:c r="Q12" s="12" t="str">
         <x:f>Produits!AG12</x:f>
-        <x:v>À rechercher</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -15026,13 +15279,11 @@
         <x:f>Produits!L27</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K27" s="12" t="n">
+      <x:c r="K27" s="12" t="str">
         <x:f>Produits!U27</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L27" s="12" t="n">
+      </x:c>
+      <x:c r="L27" s="12" t="str">
         <x:f>Produits!V27</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="M27" s="12" t="str">
         <x:f>Produits!Z27</x:f>
@@ -15056,37 +15307,37 @@
       </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="12" t="n">
+      <x:c r="A28" s="12" t="str">
         <x:f>Produits!A28</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B28" s="12" t="n">
+        <x:v>MG-HOME-001</x:v>
+      </x:c>
+      <x:c r="B28" s="12" t="str">
         <x:f>Produits!B28</x:f>
-        <x:v>0</x:v>
+        <x:v>Station Home Gym</x:v>
       </x:c>
       <x:c r="C28" s="12" t="n">
         <x:f>Produits!C28</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D28" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D28" s="12" t="str">
         <x:f>Produits!D28</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E28" s="12" t="n">
+        <x:v>Choix MuscuGuide</x:v>
+      </x:c>
+      <x:c r="E28" s="12" t="str">
         <x:f>Produits!E28</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F28" s="12" t="n">
+        <x:v>Sportstech HGX100</x:v>
+      </x:c>
+      <x:c r="F28" s="12" t="str">
         <x:f>Produits!F28</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G28" s="12" t="n">
+        <x:v>Sportstech</x:v>
+      </x:c>
+      <x:c r="G28" s="12" t="str">
         <x:f>Produits!H28</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H28" s="12" t="n">
+        <x:v>B07FCHL7TL</x:v>
+      </x:c>
+      <x:c r="H28" s="12" t="str">
         <x:f>Produits!I28</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B07FCHL7TL</x:v>
       </x:c>
       <x:c r="I28" s="12" t="n">
         <x:f>Produits!K28</x:f>
@@ -15098,65 +15349,65 @@
       </x:c>
       <x:c r="K28" s="12" t="n">
         <x:f>Produits!U28</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L28" s="12" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="L28" s="12" t="str">
         <x:f>Produits!V28</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M28" s="12" t="n">
+        <x:v>Excellent</x:v>
+      </x:c>
+      <x:c r="M28" s="12" t="str">
         <x:f>Produits!Z28</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N28" s="12" t="n">
+        <x:v>Une station complète et robuste pour entraîner l’ensemble du corps à domicile, avec une large variété d’exercices guidés.</x:v>
+      </x:c>
+      <x:c r="N28" s="12" t="str">
         <x:f>Produits!AA28</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O28" s="12" t="n">
+        <x:v>Plus de 30 exercices | Bloc de 70 kg | Construction stable | Nombreux accessoires | Bonne réputation client</x:v>
+      </x:c>
+      <x:c r="O28" s="12" t="str">
         <x:f>Produits!AB28</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P28" s="12" t="n">
+        <x:v>Montage long | Encombrement important | Charge limitée pour certains pratiquants très avancés</x:v>
+      </x:c>
+      <x:c r="P28" s="12" t="str">
         <x:f>Produits!AC28</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q28" s="12" t="n">
+        <x:v>Débutant à confirmé disposant d’un espace dédié au home gym</x:v>
+      </x:c>
+      <x:c r="Q28" s="12" t="str">
         <x:f>Produits!AG28</x:f>
-        <x:v>0</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="12" t="n">
+      <x:c r="A29" s="12" t="str">
         <x:f>Produits!A29</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B29" s="12" t="n">
+        <x:v>MG-HOME-002</x:v>
+      </x:c>
+      <x:c r="B29" s="12" t="str">
         <x:f>Produits!B29</x:f>
-        <x:v>0</x:v>
+        <x:v>Station Home Gym</x:v>
       </x:c>
       <x:c r="C29" s="12" t="n">
         <x:f>Produits!C29</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D29" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D29" s="12" t="str">
         <x:f>Produits!D29</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E29" s="12" t="n">
+        <x:v>Meilleur rapport qualité/prix</x:v>
+      </x:c>
+      <x:c r="E29" s="12" t="str">
         <x:f>Produits!E29</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F29" s="12" t="n">
+        <x:v>ISE SY-4009 50-en-1</x:v>
+      </x:c>
+      <x:c r="F29" s="12" t="str">
         <x:f>Produits!F29</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G29" s="12" t="n">
+        <x:v>ISE</x:v>
+      </x:c>
+      <x:c r="G29" s="12" t="str">
         <x:f>Produits!H29</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H29" s="12" t="n">
+        <x:v>B07B7QN69F</x:v>
+      </x:c>
+      <x:c r="H29" s="12" t="str">
         <x:f>Produits!I29</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B07B7QN69F</x:v>
       </x:c>
       <x:c r="I29" s="12" t="n">
         <x:f>Produits!K29</x:f>
@@ -15168,65 +15419,65 @@
       </x:c>
       <x:c r="K29" s="12" t="n">
         <x:f>Produits!U29</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L29" s="12" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="L29" s="12" t="str">
         <x:f>Produits!V29</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M29" s="12" t="n">
+        <x:v>Bon</x:v>
+      </x:c>
+      <x:c r="M29" s="12" t="str">
         <x:f>Produits!Z29</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N29" s="12" t="n">
+        <x:v>Une station riche en fonctions et accessible, intéressante pour débuter ou équiper un home gym avec un budget maîtrisé.</x:v>
+      </x:c>
+      <x:c r="N29" s="12" t="str">
         <x:f>Produits!AA29</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O29" s="12" t="n">
+        <x:v>Très nombreuses possibilités d’exercice | Bon rapport équipement/prix | Travail du haut et du bas du corps | Structure tout-en-un</x:v>
+      </x:c>
+      <x:c r="O29" s="12" t="str">
         <x:f>Produits!AB29</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P29" s="12" t="n">
+        <x:v>Note client plus moyenne | Montage exigeant | Prend beaucoup de place | Finitions moins premium</x:v>
+      </x:c>
+      <x:c r="P29" s="12" t="str">
         <x:f>Produits!AC29</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q29" s="12" t="n">
+        <x:v>Débutant ou intermédiaire recherchant un appareil complet à prix contenu</x:v>
+      </x:c>
+      <x:c r="Q29" s="12" t="str">
         <x:f>Produits!AG29</x:f>
-        <x:v>0</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="12" t="n">
+      <x:c r="A30" s="12" t="str">
         <x:f>Produits!A30</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B30" s="12" t="n">
+        <x:v>MG-HOME-003</x:v>
+      </x:c>
+      <x:c r="B30" s="12" t="str">
         <x:f>Produits!B30</x:f>
-        <x:v>0</x:v>
+        <x:v>Station Home Gym</x:v>
       </x:c>
       <x:c r="C30" s="12" t="n">
         <x:f>Produits!C30</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D30" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D30" s="12" t="str">
         <x:f>Produits!D30</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E30" s="12" t="n">
+        <x:v>Premium</x:v>
+      </x:c>
+      <x:c r="E30" s="12" t="str">
         <x:f>Produits!E30</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F30" s="12" t="n">
+        <x:v>Dione HG5 Multi-Gym</x:v>
+      </x:c>
+      <x:c r="F30" s="12" t="str">
         <x:f>Produits!F30</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G30" s="12" t="n">
+        <x:v>Dione</x:v>
+      </x:c>
+      <x:c r="G30" s="12" t="str">
         <x:f>Produits!H30</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H30" s="12" t="n">
+        <x:v>B08CS1PRRJ</x:v>
+      </x:c>
+      <x:c r="H30" s="12" t="str">
         <x:f>Produits!I30</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B08CS1PRRJ</x:v>
       </x:c>
       <x:c r="I30" s="12" t="n">
         <x:f>Produits!K30</x:f>
@@ -15238,31 +15489,31 @@
       </x:c>
       <x:c r="K30" s="12" t="n">
         <x:f>Produits!U30</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L30" s="12" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="L30" s="12" t="str">
         <x:f>Produits!V30</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M30" s="12" t="n">
+        <x:v>Très bon</x:v>
+      </x:c>
+      <x:c r="M30" s="12" t="str">
         <x:f>Produits!Z30</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N30" s="12" t="n">
+        <x:v>Une station très complète pour les foyers disposant d’une véritable pièce de sport, avec plusieurs postes et un sac de frappe.</x:v>
+      </x:c>
+      <x:c r="N30" s="12" t="str">
         <x:f>Produits!AA30</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O30" s="12" t="n">
+        <x:v>Plus de 44 exercices | 65 kg de poids inclus | Extensible à 100 kg | Sac de frappe inclus | Plusieurs utilisateurs possibles</x:v>
+      </x:c>
+      <x:c r="O30" s="12" t="str">
         <x:f>Produits!AB30</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P30" s="12" t="n">
+        <x:v>Très encombrante | Très lourde | Montage complexe | Investissement conséquent</x:v>
+      </x:c>
+      <x:c r="P30" s="12" t="str">
         <x:f>Produits!AC30</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q30" s="12" t="n">
+        <x:v>Intermédiaire ou confirmé souhaitant un home gym complet et permanent</x:v>
+      </x:c>
+      <x:c r="Q30" s="12" t="str">
         <x:f>Produits!AG30</x:f>
-        <x:v>0</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="31">

--- a/data/import/MuscuGuide_Base_Produits.xlsx
+++ b/data/import/MuscuGuide_Base_Produits.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R522bf75483b04886"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produits" sheetId="2" r:id="R34840a6fb0594569"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notation" sheetId="3" r:id="R401ff5e0443743be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Claude" sheetId="4" r:id="Rd16a4a0e530e4800"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="5" r:id="R73bbdd50b8fe41e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="6" r:id="R4c621db2a7974146"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R3a4cc9a4069144c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produits" sheetId="2" r:id="R1bb0f492ab444dfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notation" sheetId="3" r:id="R11eab3a461fc4c63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Claude" sheetId="4" r:id="Re3890aa6224344f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="5" r:id="R597c0c1ffd8f4db8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="6" r:id="Rad35a208921646af"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -435,7 +435,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R52766ea4b689480e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R30f4a2766dc4498c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -747,7 +747,7 @@
       </x:c>
       <x:c r="B6" s="12" t="n">
         <x:f>COUNTIF(Produits!AG4:AG250,"Validé")</x:f>
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C6" s="12"/>
       <x:c r="D6" s="12" t="str">
@@ -777,7 +777,7 @@
       </x:c>
       <x:c r="B7" s="12" t="n">
         <x:f>COUNTIF(Produits!AG4:AG250,"À rechercher")</x:f>
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C7" s="12"/>
       <x:c r="D7" s="12" t="str">
@@ -807,7 +807,7 @@
       </x:c>
       <x:c r="B8" s="38" t="n">
         <x:f>IFERROR(AVERAGE(Produits!U4:U250),0)</x:f>
-        <x:v>87.77777777777777</x:v>
+        <x:v>88.08333333333333</x:v>
       </x:c>
       <x:c r="C8" s="12"/>
       <x:c r="D8" s="12" t="str">
@@ -934,7 +934,7 @@
       </x:c>
       <x:c r="G12" s="12" t="n">
         <x:f>COUNTIFS(Produits!B:B,D12,Produits!AG:AG,"Validé")</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H12" s="46" t="n">
         <x:f>IFERROR(F12/E12,0)</x:f>
@@ -1259,7 +1259,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3a2d5f181e24d1c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b439c9fcded408c"/>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -2737,14 +2737,20 @@
         <x:v>Choix MuscuGuide</x:v>
       </x:c>
       <x:c r="E19" s="12" t="str">
-        <x:v>WalkingPad A1 Pro</x:v>
+        <x:v>CITYSPORTS Tapis de course pliable 12 km/h</x:v>
       </x:c>
       <x:c r="F19" s="12" t="str">
-        <x:v>KingSmith</x:v>
-      </x:c>
-      <x:c r="G19" s="12" t="str"/>
-      <x:c r="H19" s="12" t="str"/>
-      <x:c r="I19" s="12" t="str"/>
+        <x:v>CITYSPORTS</x:v>
+      </x:c>
+      <x:c r="G19" s="12" t="str">
+        <x:v>Bluetooth, application, support tablette 360°</x:v>
+      </x:c>
+      <x:c r="H19" s="12" t="str">
+        <x:v>B0C6KTPFGB</x:v>
+      </x:c>
+      <x:c r="I19" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0C6KTPFGB</x:v>
+      </x:c>
       <x:c r="J19" s="12" t="str"/>
       <x:c r="K19" s="12" t="str">
         <x:f>IF(OR(H19="",J19=""),"", "https://www.amazon.fr/dp/"&amp;H19&amp;"?tag="&amp;J19)</x:f>
@@ -2754,17 +2760,31 @@
       <x:c r="N19" s="12" t="str">
         <x:v>Performance</x:v>
       </x:c>
-      <x:c r="O19" s="12" t="str"/>
-      <x:c r="P19" s="12" t="str"/>
-      <x:c r="Q19" s="12" t="str"/>
-      <x:c r="R19" s="12" t="str"/>
-      <x:c r="S19" s="12" t="str"/>
-      <x:c r="T19" s="12" t="str"/>
-      <x:c r="U19" s="12" t="str">
+      <x:c r="O19" s="12" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P19" s="12" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q19" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="R19" s="12" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="S19" s="12" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="T19" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="U19" s="12" t="n">
         <x:f>IF(COUNTA(O19:T19)=0,"",SUM(O19:T19))</x:f>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="V19" s="12" t="str">
         <x:f>IF(U19="","",IF(U19&gt;=95,"Exceptionnel",IF(U19&gt;=90,"Excellent",IF(U19&gt;=85,"Très bon",IF(U19&gt;=80,"Bon",IF(U19&gt;=70,"Correct","À revoir"))))))</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="W19" s="12" t="str">
         <x:v>Oui</x:v>
@@ -2774,26 +2794,34 @@
       </x:c>
       <x:c r="Y19" s="12" t="str"/>
       <x:c r="Z19" s="12" t="str">
-        <x:v>Walking pad compact pour appartement et télétravail.</x:v>
+        <x:v>Un tapis de course pliable polyvalent et très populaire, adapté à la marche, au jogging et à la course légère à domicile.</x:v>
       </x:c>
       <x:c r="AA19" s="12" t="str">
-        <x:v>Compact | Silencieux | Pliable</x:v>
+        <x:v>Jusqu’à 12 km/h | 4,4/5 sur plus de 4 700 évaluations | Bluetooth et application | Support tablette | Pliable et prêt à l’emploi</x:v>
       </x:c>
       <x:c r="AB19" s="12" t="str">
-        <x:v>Vitesse limitée | Pas pour course intense</x:v>
+        <x:v>Surface de course compacte | Moins adapté aux grandes foulées | Capacité limitée pour un entraînement intensif</x:v>
       </x:c>
       <x:c r="AC19" s="12" t="str">
-        <x:v>Marche / petit espace</x:v>
-      </x:c>
-      <x:c r="AD19" s="12" t="str"/>
-      <x:c r="AE19" s="38" t="str"/>
-      <x:c r="AF19" s="40" t="str"/>
+        <x:v>Débutant à intermédiaire recherchant un tapis compact et polyvalent</x:v>
+      </x:c>
+      <x:c r="AD19" s="12" t="n">
+        <x:v>4766</x:v>
+      </x:c>
+      <x:c r="AE19" s="38" t="n">
+        <x:v>4.4</x:v>
+      </x:c>
+      <x:c r="AF19" s="55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
       <x:c r="AG19" s="12" t="str">
-        <x:v>À rechercher</x:v>
-      </x:c>
-      <x:c r="AH19" s="12" t="str"/>
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH19" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0C6KTPFGB</x:v>
+      </x:c>
       <x:c r="AI19" s="12" t="str">
-        <x:v>Vérifier modèle officiel.</x:v>
+        <x:v>ASIN, note Amazon 4,4/5 et 4 766 évaluations vérifiés le 05/08/2026. Vitesse 12 km/h, Bluetooth, application, support tablette et charge maximale 120 kg confirmés sur Amazon FR.</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -2810,14 +2838,20 @@
         <x:v>Meilleur rapport qualité/prix</x:v>
       </x:c>
       <x:c r="E20" s="12" t="str">
-        <x:v>Walking Pad</x:v>
+        <x:v>FITFIU Fitness MC-160</x:v>
       </x:c>
       <x:c r="F20" s="12" t="str">
-        <x:v>CITYSPORTS</x:v>
-      </x:c>
-      <x:c r="G20" s="12" t="str"/>
-      <x:c r="H20" s="12" t="str"/>
-      <x:c r="I20" s="12" t="str"/>
+        <x:v>FITFIU Fitness</x:v>
+      </x:c>
+      <x:c r="G20" s="12" t="str">
+        <x:v>14 km/h — inclinaison manuelle 9 % — 12 programmes</x:v>
+      </x:c>
+      <x:c r="H20" s="12" t="str">
+        <x:v>B0846FFY27</x:v>
+      </x:c>
+      <x:c r="I20" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0846FFY27</x:v>
+      </x:c>
       <x:c r="J20" s="12" t="str"/>
       <x:c r="K20" s="12" t="str">
         <x:f>IF(OR(H20="",J20=""),"", "https://www.amazon.fr/dp/"&amp;H20&amp;"?tag="&amp;J20)</x:f>
@@ -2827,17 +2861,31 @@
       <x:c r="N20" s="12" t="str">
         <x:v>Essentials</x:v>
       </x:c>
-      <x:c r="O20" s="12" t="str"/>
-      <x:c r="P20" s="12" t="str"/>
-      <x:c r="Q20" s="12" t="str"/>
-      <x:c r="R20" s="12" t="str"/>
-      <x:c r="S20" s="12" t="str"/>
-      <x:c r="T20" s="12" t="str"/>
-      <x:c r="U20" s="12" t="str">
+      <x:c r="O20" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P20" s="12" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q20" s="12" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="R20" s="12" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="S20" s="12" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="T20" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="U20" s="12" t="n">
         <x:f>IF(COUNTA(O20:T20)=0,"",SUM(O20:T20))</x:f>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="V20" s="12" t="str">
         <x:f>IF(U20="","",IF(U20&gt;=95,"Exceptionnel",IF(U20&gt;=90,"Excellent",IF(U20&gt;=85,"Très bon",IF(U20&gt;=80,"Bon",IF(U20&gt;=70,"Correct","À revoir"))))))</x:f>
+        <x:v>Très bon</x:v>
       </x:c>
       <x:c r="W20" s="12" t="str">
         <x:v>Oui</x:v>
@@ -2847,26 +2895,34 @@
       </x:c>
       <x:c r="Y20" s="12" t="str"/>
       <x:c r="Z20" s="12" t="str">
-        <x:v>Solution accessible pour marcher à domicile.</x:v>
+        <x:v>Un modèle accessible et complet pour commencer à courir chez soi, avec inclinaison, programmes et applications connectées.</x:v>
       </x:c>
       <x:c r="AA20" s="12" t="str">
-        <x:v>Prix | Compact | Simple</x:v>
+        <x:v>Bon rapport qualité/prix | Jusqu’à 14 km/h | Inclinaison 9 % | 12 programmes | Compatible Kinomap et Zwift</x:v>
       </x:c>
       <x:c r="AB20" s="12" t="str">
-        <x:v>SAV et longévité à vérifier</x:v>
+        <x:v>Surface de course assez courte | Inclinaison manuelle | Moins confortable pour les grands gabarits</x:v>
       </x:c>
       <x:c r="AC20" s="12" t="str">
-        <x:v>Débutant / marche</x:v>
-      </x:c>
-      <x:c r="AD20" s="12" t="str"/>
-      <x:c r="AE20" s="38" t="str"/>
-      <x:c r="AF20" s="40" t="str"/>
+        <x:v>Débutant ou intermédiaire souhaitant progresser avec un budget maîtrisé</x:v>
+      </x:c>
+      <x:c r="AD20" s="12" t="n">
+        <x:v>1656</x:v>
+      </x:c>
+      <x:c r="AE20" s="38" t="n">
+        <x:v>4.3</x:v>
+      </x:c>
+      <x:c r="AF20" s="55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
       <x:c r="AG20" s="12" t="str">
-        <x:v>À rechercher</x:v>
-      </x:c>
-      <x:c r="AH20" s="12" t="str"/>
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH20" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0846FFY27</x:v>
+      </x:c>
       <x:c r="AI20" s="12" t="str">
-        <x:v>Sélection exacte selon stock Amazon FR.</x:v>
+        <x:v>ASIN, note Amazon 4,3/5 et 1 656 évaluations vérifiés le 05/08/2026. Vitesse 14 km/h, inclinaison 9 %, 12 programmes et compatibilité avec plusieurs applications confirmées.</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -2883,14 +2939,20 @@
         <x:v>Premium</x:v>
       </x:c>
       <x:c r="E21" s="12" t="str">
-        <x:v>Commercial Series</x:v>
+        <x:v>Sportstech F31s</x:v>
       </x:c>
       <x:c r="F21" s="12" t="str">
-        <x:v>NordicTrack</x:v>
-      </x:c>
-      <x:c r="G21" s="12" t="str"/>
-      <x:c r="H21" s="12" t="str"/>
-      <x:c r="I21" s="12" t="str"/>
+        <x:v>Sportstech</x:v>
+      </x:c>
+      <x:c r="G21" s="12" t="str">
+        <x:v>16 km/h — inclinaison jusqu’à 15 % — 20 programmes</x:v>
+      </x:c>
+      <x:c r="H21" s="12" t="str">
+        <x:v>B0733BSRCV</x:v>
+      </x:c>
+      <x:c r="I21" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0733BSRCV</x:v>
+      </x:c>
       <x:c r="J21" s="12" t="str"/>
       <x:c r="K21" s="12" t="str">
         <x:f>IF(OR(H21="",J21=""),"", "https://www.amazon.fr/dp/"&amp;H21&amp;"?tag="&amp;J21)</x:f>
@@ -2900,17 +2962,31 @@
       <x:c r="N21" s="12" t="str">
         <x:v>Elite</x:v>
       </x:c>
-      <x:c r="O21" s="12" t="str"/>
-      <x:c r="P21" s="12" t="str"/>
-      <x:c r="Q21" s="12" t="str"/>
-      <x:c r="R21" s="12" t="str"/>
-      <x:c r="S21" s="12" t="str"/>
-      <x:c r="T21" s="12" t="str"/>
-      <x:c r="U21" s="12" t="str">
+      <x:c r="O21" s="12" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P21" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="Q21" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="R21" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="S21" s="12" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="T21" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="U21" s="12" t="n">
         <x:f>IF(COUNTA(O21:T21)=0,"",SUM(O21:T21))</x:f>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="V21" s="12" t="str">
         <x:f>IF(U21="","",IF(U21&gt;=95,"Exceptionnel",IF(U21&gt;=90,"Excellent",IF(U21&gt;=85,"Très bon",IF(U21&gt;=80,"Bon",IF(U21&gt;=70,"Correct","À revoir"))))))</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="W21" s="12" t="str"/>
       <x:c r="X21" s="12" t="str">
@@ -2920,26 +2996,34 @@
         <x:v>Oui</x:v>
       </x:c>
       <x:c r="Z21" s="12" t="str">
-        <x:v>Tapis premium pour entraînement cardio complet.</x:v>
+        <x:v>Un tapis robuste et mieux équipé pour les séances régulières, avec une vitesse plus élevée, une forte inclinaison et de nombreux programmes.</x:v>
       </x:c>
       <x:c r="AA21" s="12" t="str">
-        <x:v>Puissance | Confort | Fonctions connectées</x:v>
+        <x:v>Jusqu’à 16 km/h | Inclinaison jusqu’à 15 % | 20 programmes | Construction robuste | Pliable et autolubrifié</x:v>
       </x:c>
       <x:c r="AB21" s="12" t="str">
-        <x:v>Très cher | Encombrant</x:v>
+        <x:v>Plus lourd et encombrant | Prix supérieur | Surface encore limitée pour la course très rapide</x:v>
       </x:c>
       <x:c r="AC21" s="12" t="str">
-        <x:v>Sportif exigeant</x:v>
-      </x:c>
-      <x:c r="AD21" s="12" t="str"/>
-      <x:c r="AE21" s="38" t="str"/>
-      <x:c r="AF21" s="40" t="str"/>
+        <x:v>Intermédiaire à confirmé recherchant un appareil plus performant</x:v>
+      </x:c>
+      <x:c r="AD21" s="12" t="n">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="AE21" s="38" t="n">
+        <x:v>4.3</x:v>
+      </x:c>
+      <x:c r="AF21" s="55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
       <x:c r="AG21" s="12" t="str">
-        <x:v>À rechercher</x:v>
-      </x:c>
-      <x:c r="AH21" s="12" t="str"/>
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH21" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0733BSRCV</x:v>
+      </x:c>
       <x:c r="AI21" s="12" t="str">
-        <x:v>Choisir un modèle réellement pliable et disponible.</x:v>
+        <x:v>ASIN, note Amazon 4,3/5 et 164 commentaires vérifiés le 05/08/2026. Vitesse 16 km/h, inclinaison 15 %, 20 programmes et charge maximale 120 kg confirmés.</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -13221,7 +13305,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4b651cd5c964ebc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ab47c45491a4604"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14702,19 +14786,19 @@
       </x:c>
       <x:c r="E19" s="12" t="str">
         <x:f>Produits!E19</x:f>
-        <x:v>WalkingPad A1 Pro</x:v>
+        <x:v>CITYSPORTS Tapis de course pliable 12 km/h</x:v>
       </x:c>
       <x:c r="F19" s="12" t="str">
         <x:f>Produits!F19</x:f>
-        <x:v>KingSmith</x:v>
-      </x:c>
-      <x:c r="G19" s="12" t="n">
+        <x:v>CITYSPORTS</x:v>
+      </x:c>
+      <x:c r="G19" s="12" t="str">
         <x:f>Produits!H19</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H19" s="12" t="n">
+        <x:v>B0C6KTPFGB</x:v>
+      </x:c>
+      <x:c r="H19" s="12" t="str">
         <x:f>Produits!I19</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B0C6KTPFGB</x:v>
       </x:c>
       <x:c r="I19" s="12" t="n">
         <x:f>Produits!K19</x:f>
@@ -14726,30 +14810,31 @@
       </x:c>
       <x:c r="K19" s="12" t="n">
         <x:f>Produits!U19</x:f>
-        <x:v>0</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="L19" s="12" t="str">
         <x:f>Produits!V19</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="M19" s="12" t="str">
         <x:f>Produits!Z19</x:f>
-        <x:v>Walking pad compact pour appartement et télétravail.</x:v>
+        <x:v>Un tapis de course pliable polyvalent et très populaire, adapté à la marche, au jogging et à la course légère à domicile.</x:v>
       </x:c>
       <x:c r="N19" s="12" t="str">
         <x:f>Produits!AA19</x:f>
-        <x:v>Compact | Silencieux | Pliable</x:v>
+        <x:v>Jusqu’à 12 km/h | 4,4/5 sur plus de 4 700 évaluations | Bluetooth et application | Support tablette | Pliable et prêt à l’emploi</x:v>
       </x:c>
       <x:c r="O19" s="12" t="str">
         <x:f>Produits!AB19</x:f>
-        <x:v>Vitesse limitée | Pas pour course intense</x:v>
+        <x:v>Surface de course compacte | Moins adapté aux grandes foulées | Capacité limitée pour un entraînement intensif</x:v>
       </x:c>
       <x:c r="P19" s="12" t="str">
         <x:f>Produits!AC19</x:f>
-        <x:v>Marche / petit espace</x:v>
+        <x:v>Débutant à intermédiaire recherchant un tapis compact et polyvalent</x:v>
       </x:c>
       <x:c r="Q19" s="12" t="str">
         <x:f>Produits!AG19</x:f>
-        <x:v>À rechercher</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -14771,19 +14856,19 @@
       </x:c>
       <x:c r="E20" s="12" t="str">
         <x:f>Produits!E20</x:f>
-        <x:v>Walking Pad</x:v>
+        <x:v>FITFIU Fitness MC-160</x:v>
       </x:c>
       <x:c r="F20" s="12" t="str">
         <x:f>Produits!F20</x:f>
-        <x:v>CITYSPORTS</x:v>
-      </x:c>
-      <x:c r="G20" s="12" t="n">
+        <x:v>FITFIU Fitness</x:v>
+      </x:c>
+      <x:c r="G20" s="12" t="str">
         <x:f>Produits!H20</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H20" s="12" t="n">
+        <x:v>B0846FFY27</x:v>
+      </x:c>
+      <x:c r="H20" s="12" t="str">
         <x:f>Produits!I20</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B0846FFY27</x:v>
       </x:c>
       <x:c r="I20" s="12" t="n">
         <x:f>Produits!K20</x:f>
@@ -14795,31 +14880,31 @@
       </x:c>
       <x:c r="K20" s="12" t="n">
         <x:f>Produits!U20</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L20" s="12" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="L20" s="12" t="str">
         <x:f>Produits!V20</x:f>
-        <x:v>0</x:v>
+        <x:v>Très bon</x:v>
       </x:c>
       <x:c r="M20" s="12" t="str">
         <x:f>Produits!Z20</x:f>
-        <x:v>Solution accessible pour marcher à domicile.</x:v>
+        <x:v>Un modèle accessible et complet pour commencer à courir chez soi, avec inclinaison, programmes et applications connectées.</x:v>
       </x:c>
       <x:c r="N20" s="12" t="str">
         <x:f>Produits!AA20</x:f>
-        <x:v>Prix | Compact | Simple</x:v>
+        <x:v>Bon rapport qualité/prix | Jusqu’à 14 km/h | Inclinaison 9 % | 12 programmes | Compatible Kinomap et Zwift</x:v>
       </x:c>
       <x:c r="O20" s="12" t="str">
         <x:f>Produits!AB20</x:f>
-        <x:v>SAV et longévité à vérifier</x:v>
+        <x:v>Surface de course assez courte | Inclinaison manuelle | Moins confortable pour les grands gabarits</x:v>
       </x:c>
       <x:c r="P20" s="12" t="str">
         <x:f>Produits!AC20</x:f>
-        <x:v>Débutant / marche</x:v>
+        <x:v>Débutant ou intermédiaire souhaitant progresser avec un budget maîtrisé</x:v>
       </x:c>
       <x:c r="Q20" s="12" t="str">
         <x:f>Produits!AG20</x:f>
-        <x:v>À rechercher</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -14841,19 +14926,19 @@
       </x:c>
       <x:c r="E21" s="12" t="str">
         <x:f>Produits!E21</x:f>
-        <x:v>Commercial Series</x:v>
+        <x:v>Sportstech F31s</x:v>
       </x:c>
       <x:c r="F21" s="12" t="str">
         <x:f>Produits!F21</x:f>
-        <x:v>NordicTrack</x:v>
-      </x:c>
-      <x:c r="G21" s="12" t="n">
+        <x:v>Sportstech</x:v>
+      </x:c>
+      <x:c r="G21" s="12" t="str">
         <x:f>Produits!H21</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H21" s="12" t="n">
+        <x:v>B0733BSRCV</x:v>
+      </x:c>
+      <x:c r="H21" s="12" t="str">
         <x:f>Produits!I21</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B0733BSRCV</x:v>
       </x:c>
       <x:c r="I21" s="12" t="n">
         <x:f>Produits!K21</x:f>
@@ -14865,30 +14950,31 @@
       </x:c>
       <x:c r="K21" s="12" t="n">
         <x:f>Produits!U21</x:f>
-        <x:v>0</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="L21" s="12" t="str">
         <x:f>Produits!V21</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="M21" s="12" t="str">
         <x:f>Produits!Z21</x:f>
-        <x:v>Tapis premium pour entraînement cardio complet.</x:v>
+        <x:v>Un tapis robuste et mieux équipé pour les séances régulières, avec une vitesse plus élevée, une forte inclinaison et de nombreux programmes.</x:v>
       </x:c>
       <x:c r="N21" s="12" t="str">
         <x:f>Produits!AA21</x:f>
-        <x:v>Puissance | Confort | Fonctions connectées</x:v>
+        <x:v>Jusqu’à 16 km/h | Inclinaison jusqu’à 15 % | 20 programmes | Construction robuste | Pliable et autolubrifié</x:v>
       </x:c>
       <x:c r="O21" s="12" t="str">
         <x:f>Produits!AB21</x:f>
-        <x:v>Très cher | Encombrant</x:v>
+        <x:v>Plus lourd et encombrant | Prix supérieur | Surface encore limitée pour la course très rapide</x:v>
       </x:c>
       <x:c r="P21" s="12" t="str">
         <x:f>Produits!AC21</x:f>
-        <x:v>Sportif exigeant</x:v>
+        <x:v>Intermédiaire à confirmé recherchant un appareil plus performant</x:v>
       </x:c>
       <x:c r="Q21" s="12" t="str">
         <x:f>Produits!AG21</x:f>
-        <x:v>À rechercher</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="22">

--- a/data/import/MuscuGuide_Base_Produits.xlsx
+++ b/data/import/MuscuGuide_Base_Produits.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R3a4cc9a4069144c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produits" sheetId="2" r:id="R1bb0f492ab444dfa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notation" sheetId="3" r:id="R11eab3a461fc4c63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Claude" sheetId="4" r:id="Re3890aa6224344f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="5" r:id="R597c0c1ffd8f4db8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="6" r:id="Rad35a208921646af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Re18a0502bd594196"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produits" sheetId="2" r:id="R680521ec077b4502"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notation" sheetId="3" r:id="R7f641ca45b6e42d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Claude" sheetId="4" r:id="Rc652bcfe81094517"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="5" r:id="R2ec6f64b12324307"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="6" r:id="R328bddf118a7432d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -435,7 +435,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R30f4a2766dc4498c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R57a2a156b70c45af"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -747,7 +747,7 @@
       </x:c>
       <x:c r="B6" s="12" t="n">
         <x:f>COUNTIF(Produits!AG4:AG250,"Validé")</x:f>
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C6" s="12"/>
       <x:c r="D6" s="12" t="str">
@@ -777,7 +777,7 @@
       </x:c>
       <x:c r="B7" s="12" t="n">
         <x:f>COUNTIF(Produits!AG4:AG250,"À rechercher")</x:f>
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C7" s="12"/>
       <x:c r="D7" s="12" t="str">
@@ -807,7 +807,7 @@
       </x:c>
       <x:c r="B8" s="38" t="n">
         <x:f>IFERROR(AVERAGE(Produits!U4:U250),0)</x:f>
-        <x:v>88.08333333333333</x:v>
+        <x:v>88.8</x:v>
       </x:c>
       <x:c r="C8" s="12"/>
       <x:c r="D8" s="12" t="str">
@@ -992,7 +992,7 @@
       </x:c>
       <x:c r="G14" s="12" t="n">
         <x:f>COUNTIFS(Produits!B:B,D14,Produits!AG:AG,"Validé")</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H14" s="46" t="n">
         <x:f>IFERROR(F14/E14,0)</x:f>
@@ -1259,7 +1259,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b439c9fcded408c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb37b627c42434673"/>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -2516,14 +2516,20 @@
         <x:v>Choix MuscuGuide</x:v>
       </x:c>
       <x:c r="E16" s="12" t="str">
-        <x:v>Vivoactive 5</x:v>
+        <x:v>Garmin vívoactive 5</x:v>
       </x:c>
       <x:c r="F16" s="12" t="str">
         <x:v>Garmin</x:v>
       </x:c>
-      <x:c r="G16" s="12" t="str"/>
-      <x:c r="H16" s="12" t="str"/>
-      <x:c r="I16" s="12" t="str"/>
+      <x:c r="G16" s="12" t="str">
+        <x:v>42 mm — écran AMOLED — autonomie jusqu’à 11 jours</x:v>
+      </x:c>
+      <x:c r="H16" s="12" t="str">
+        <x:v>B0CG6NR413</x:v>
+      </x:c>
+      <x:c r="I16" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0CG6NR413</x:v>
+      </x:c>
       <x:c r="J16" s="12" t="str"/>
       <x:c r="K16" s="12" t="str">
         <x:f>IF(OR(H16="",J16=""),"", "https://www.amazon.fr/dp/"&amp;H16&amp;"?tag="&amp;J16)</x:f>
@@ -2533,17 +2539,31 @@
       <x:c r="N16" s="12" t="str">
         <x:v>Performance</x:v>
       </x:c>
-      <x:c r="O16" s="12" t="str"/>
-      <x:c r="P16" s="12" t="str"/>
-      <x:c r="Q16" s="12" t="str"/>
-      <x:c r="R16" s="12" t="str"/>
-      <x:c r="S16" s="12" t="str"/>
-      <x:c r="T16" s="12" t="str"/>
-      <x:c r="U16" s="12" t="str">
+      <x:c r="O16" s="12" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P16" s="12" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q16" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="R16" s="12" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="S16" s="12" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="T16" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="U16" s="12" t="n">
         <x:f>IF(COUNTA(O16:T16)=0,"",SUM(O16:T16))</x:f>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="V16" s="12" t="str">
         <x:f>IF(U16="","",IF(U16&gt;=95,"Exceptionnel",IF(U16&gt;=90,"Excellent",IF(U16&gt;=85,"Très bon",IF(U16&gt;=80,"Bon",IF(U16&gt;=70,"Correct","À revoir"))))))</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="W16" s="12" t="str">
         <x:v>Oui</x:v>
@@ -2555,26 +2575,34 @@
         <x:v>Oui</x:v>
       </x:c>
       <x:c r="Z16" s="12" t="str">
-        <x:v>Montre polyvalente pour fitness, santé et cardio.</x:v>
+        <x:v>Une montre GPS très équilibrée pour le fitness, la santé et le cardio quotidien, simple à utiliser et compatible avec de nombreux sports.</x:v>
       </x:c>
       <x:c r="AA16" s="12" t="str">
-        <x:v>Autonomie | Suivi complet | Marque reconnue</x:v>
+        <x:v>Écran AMOLED | Autonomie jusqu’à 11 jours | Plus de 30 sports | Suivi santé complet | Garmin Pay et musique</x:v>
       </x:c>
       <x:c r="AB16" s="12" t="str">
-        <x:v>Pas la plus avancée en sport outdoor</x:v>
+        <x:v>Pas de cartographie complète | Fonctions outdoor moins avancées | Design assez sobre</x:v>
       </x:c>
       <x:c r="AC16" s="12" t="str">
-        <x:v>Fitness général</x:v>
-      </x:c>
-      <x:c r="AD16" s="12" t="str"/>
-      <x:c r="AE16" s="38" t="str"/>
-      <x:c r="AF16" s="40" t="str"/>
+        <x:v>Débutant à confirmé recherchant une montre polyvalente pour le fitness et la santé</x:v>
+      </x:c>
+      <x:c r="AD16" s="12" t="n">
+        <x:v>11443</x:v>
+      </x:c>
+      <x:c r="AE16" s="38" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="AF16" s="55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
       <x:c r="AG16" s="12" t="str">
-        <x:v>À rechercher</x:v>
-      </x:c>
-      <x:c r="AH16" s="12" t="str"/>
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH16" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0CG6NR413</x:v>
+      </x:c>
       <x:c r="AI16" s="12" t="str">
-        <x:v>ASIN déjà recherché historiquement — revalider.</x:v>
+        <x:v>ASIN, note Amazon 4,5/5 et 11 443 évaluations vérifiés le 05/08/2026. Autonomie 11 jours et 30+ sports confirmés par Garmin : https://www.garmin.com/fr-FR/p/1057989/</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -2591,14 +2619,20 @@
         <x:v>Meilleur rapport qualité/prix</x:v>
       </x:c>
       <x:c r="E17" s="12" t="str">
-        <x:v>Balance</x:v>
+        <x:v>Amazfit Balance 2</x:v>
       </x:c>
       <x:c r="F17" s="12" t="str">
         <x:v>Amazfit</x:v>
       </x:c>
-      <x:c r="G17" s="12" t="str"/>
-      <x:c r="H17" s="12" t="str"/>
-      <x:c r="I17" s="12" t="str"/>
+      <x:c r="G17" s="12" t="str">
+        <x:v>47 mm — verre saphir — autonomie jusqu’à 21 jours</x:v>
+      </x:c>
+      <x:c r="H17" s="12" t="str">
+        <x:v>B0F8HNKK6Z</x:v>
+      </x:c>
+      <x:c r="I17" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0F8HNKK6Z</x:v>
+      </x:c>
       <x:c r="J17" s="12" t="str"/>
       <x:c r="K17" s="12" t="str">
         <x:f>IF(OR(H17="",J17=""),"", "https://www.amazon.fr/dp/"&amp;H17&amp;"?tag="&amp;J17)</x:f>
@@ -2608,17 +2642,31 @@
       <x:c r="N17" s="12" t="str">
         <x:v>Essentials</x:v>
       </x:c>
-      <x:c r="O17" s="12" t="str"/>
-      <x:c r="P17" s="12" t="str"/>
-      <x:c r="Q17" s="12" t="str"/>
-      <x:c r="R17" s="12" t="str"/>
-      <x:c r="S17" s="12" t="str"/>
-      <x:c r="T17" s="12" t="str"/>
-      <x:c r="U17" s="12" t="str">
+      <x:c r="O17" s="12" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P17" s="12" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q17" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="R17" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="S17" s="12" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="T17" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="U17" s="12" t="n">
         <x:f>IF(COUNTA(O17:T17)=0,"",SUM(O17:T17))</x:f>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="V17" s="12" t="str">
         <x:f>IF(U17="","",IF(U17&gt;=95,"Exceptionnel",IF(U17&gt;=90,"Excellent",IF(U17&gt;=85,"Très bon",IF(U17&gt;=80,"Bon",IF(U17&gt;=70,"Correct","À revoir"))))))</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="W17" s="12" t="str">
         <x:v>Oui</x:v>
@@ -2628,26 +2676,34 @@
       </x:c>
       <x:c r="Y17" s="12" t="str"/>
       <x:c r="Z17" s="12" t="str">
-        <x:v>Montre riche en fonctions à prix compétitif.</x:v>
+        <x:v>Une montre très riche en fonctions avec une excellente autonomie, un GPS double bande et un positionnement tarifaire compétitif.</x:v>
       </x:c>
       <x:c r="AA17" s="12" t="str">
-        <x:v>Écran | Autonomie | Fonctions</x:v>
+        <x:v>Autonomie jusqu’à 21 jours | Plus de 170 sports | Verre saphir | GPS double bande | Étanchéité 10 ATM</x:v>
       </x:c>
       <x:c r="AB17" s="12" t="str">
-        <x:v>Écosystème moins mature que Garmin</x:v>
+        <x:v>Écosystème d’applications moins riche que Garmin | Format imposant | Fonctions connectées plus limitées</x:v>
       </x:c>
       <x:c r="AC17" s="12" t="str">
-        <x:v>Débutant / intermédiaire</x:v>
-      </x:c>
-      <x:c r="AD17" s="12" t="str"/>
-      <x:c r="AE17" s="38" t="str"/>
-      <x:c r="AF17" s="40" t="str"/>
+        <x:v>Débutant à intermédiaire voulant beaucoup de fonctions et une longue autonomie</x:v>
+      </x:c>
+      <x:c r="AD17" s="12" t="n">
+        <x:v>1164</x:v>
+      </x:c>
+      <x:c r="AE17" s="38" t="n">
+        <x:v>4.3</x:v>
+      </x:c>
+      <x:c r="AF17" s="55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
       <x:c r="AG17" s="12" t="str">
-        <x:v>À rechercher</x:v>
-      </x:c>
-      <x:c r="AH17" s="12" t="str"/>
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH17" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0F8HNKK6Z</x:v>
+      </x:c>
       <x:c r="AI17" s="12" t="str">
-        <x:v>Vérifier version européenne.</x:v>
+        <x:v>ASIN, note Amazon 4,3/5 et 1 164 évaluations vérifiés le 05/08/2026. Autonomie 21 jours, 170+ sports et 10 ATM confirmés par Amazfit : https://fr.amazfit.com/products/balance-2</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -2664,14 +2720,20 @@
         <x:v>Premium</x:v>
       </x:c>
       <x:c r="E18" s="12" t="str">
-        <x:v>Fenix 8</x:v>
+        <x:v>Garmin fēnix 8 AMOLED 43 mm</x:v>
       </x:c>
       <x:c r="F18" s="12" t="str">
         <x:v>Garmin</x:v>
       </x:c>
-      <x:c r="G18" s="12" t="str"/>
-      <x:c r="H18" s="12" t="str"/>
-      <x:c r="I18" s="12" t="str"/>
+      <x:c r="G18" s="12" t="str">
+        <x:v>43 mm — AMOLED — cartographie — lampe LED — 10 ATM</x:v>
+      </x:c>
+      <x:c r="H18" s="12" t="str">
+        <x:v>B0FSFDF2N8</x:v>
+      </x:c>
+      <x:c r="I18" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0FSFDF2N8</x:v>
+      </x:c>
       <x:c r="J18" s="12" t="str"/>
       <x:c r="K18" s="12" t="str">
         <x:f>IF(OR(H18="",J18=""),"", "https://www.amazon.fr/dp/"&amp;H18&amp;"?tag="&amp;J18)</x:f>
@@ -2681,17 +2743,31 @@
       <x:c r="N18" s="12" t="str">
         <x:v>Elite</x:v>
       </x:c>
-      <x:c r="O18" s="12" t="str"/>
-      <x:c r="P18" s="12" t="str"/>
-      <x:c r="Q18" s="12" t="str"/>
-      <x:c r="R18" s="12" t="str"/>
-      <x:c r="S18" s="12" t="str"/>
-      <x:c r="T18" s="12" t="str"/>
-      <x:c r="U18" s="12" t="str">
+      <x:c r="O18" s="12" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="P18" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="Q18" s="12" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="R18" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="S18" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="T18" s="12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="U18" s="12" t="n">
         <x:f>IF(COUNTA(O18:T18)=0,"",SUM(O18:T18))</x:f>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="V18" s="12" t="str">
         <x:f>IF(U18="","",IF(U18&gt;=95,"Exceptionnel",IF(U18&gt;=90,"Excellent",IF(U18&gt;=85,"Très bon",IF(U18&gt;=80,"Bon",IF(U18&gt;=70,"Correct","À revoir"))))))</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="W18" s="12" t="str"/>
       <x:c r="X18" s="12" t="str">
@@ -2701,26 +2777,34 @@
         <x:v>Oui</x:v>
       </x:c>
       <x:c r="Z18" s="12" t="str">
-        <x:v>Montre multisport premium pour utilisateurs exigeants.</x:v>
+        <x:v>Une montre multisport premium très complète pour l’entraînement avancé, l’outdoor et la navigation, dans un format compact.</x:v>
       </x:c>
       <x:c r="AA18" s="12" t="str">
-        <x:v>Robustesse | Cartographie | Fonctions avancées</x:v>
+        <x:v>Cartographie et GPS multibande | Lampe LED | Étanchéité 10 ATM | Fonctions sport très avancées | Construction premium</x:v>
       </x:c>
       <x:c r="AB18" s="12" t="str">
-        <x:v>Prix très élevé | Surdimensionnée pour certains</x:v>
+        <x:v>Prix très élevé | Complexe pour un usage basique | Autonomie inférieure aux grandes tailles de la gamme</x:v>
       </x:c>
       <x:c r="AC18" s="12" t="str">
-        <x:v>Sportif confirmé</x:v>
-      </x:c>
-      <x:c r="AD18" s="12" t="str"/>
-      <x:c r="AE18" s="38" t="str"/>
-      <x:c r="AF18" s="40" t="str"/>
+        <x:v>Sportif confirmé ou pratiquant outdoor recherchant une montre haut de gamme</x:v>
+      </x:c>
+      <x:c r="AD18" s="12" t="n">
+        <x:v>1222</x:v>
+      </x:c>
+      <x:c r="AE18" s="38" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="AF18" s="55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
       <x:c r="AG18" s="12" t="str">
-        <x:v>À rechercher</x:v>
-      </x:c>
-      <x:c r="AH18" s="12" t="str"/>
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH18" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0FSFDF2N8</x:v>
+      </x:c>
       <x:c r="AI18" s="12" t="str">
-        <x:v>Choisir taille/version précise.</x:v>
+        <x:v>ASIN, note Amazon 4,5/5 et 1 222 évaluations vérifiés le 05/08/2026. Autonomie 10 jours, 10 ATM et format 43 mm confirmés par Garmin : https://www.garmin.com/fr-FR/p/1228493/pn/010-02903-00/</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -13305,7 +13389,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ab47c45491a4604"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e823cdb6f54475d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14578,19 +14662,19 @@
       </x:c>
       <x:c r="E16" s="12" t="str">
         <x:f>Produits!E16</x:f>
-        <x:v>Vivoactive 5</x:v>
+        <x:v>Garmin vívoactive 5</x:v>
       </x:c>
       <x:c r="F16" s="12" t="str">
         <x:f>Produits!F16</x:f>
         <x:v>Garmin</x:v>
       </x:c>
-      <x:c r="G16" s="12" t="n">
+      <x:c r="G16" s="12" t="str">
         <x:f>Produits!H16</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H16" s="12" t="n">
+        <x:v>B0CG6NR413</x:v>
+      </x:c>
+      <x:c r="H16" s="12" t="str">
         <x:f>Produits!I16</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B0CG6NR413</x:v>
       </x:c>
       <x:c r="I16" s="12" t="n">
         <x:f>Produits!K16</x:f>
@@ -14602,30 +14686,31 @@
       </x:c>
       <x:c r="K16" s="12" t="n">
         <x:f>Produits!U16</x:f>
-        <x:v>0</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="L16" s="12" t="str">
         <x:f>Produits!V16</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="M16" s="12" t="str">
         <x:f>Produits!Z16</x:f>
-        <x:v>Montre polyvalente pour fitness, santé et cardio.</x:v>
+        <x:v>Une montre GPS très équilibrée pour le fitness, la santé et le cardio quotidien, simple à utiliser et compatible avec de nombreux sports.</x:v>
       </x:c>
       <x:c r="N16" s="12" t="str">
         <x:f>Produits!AA16</x:f>
-        <x:v>Autonomie | Suivi complet | Marque reconnue</x:v>
+        <x:v>Écran AMOLED | Autonomie jusqu’à 11 jours | Plus de 30 sports | Suivi santé complet | Garmin Pay et musique</x:v>
       </x:c>
       <x:c r="O16" s="12" t="str">
         <x:f>Produits!AB16</x:f>
-        <x:v>Pas la plus avancée en sport outdoor</x:v>
+        <x:v>Pas de cartographie complète | Fonctions outdoor moins avancées | Design assez sobre</x:v>
       </x:c>
       <x:c r="P16" s="12" t="str">
         <x:f>Produits!AC16</x:f>
-        <x:v>Fitness général</x:v>
+        <x:v>Débutant à confirmé recherchant une montre polyvalente pour le fitness et la santé</x:v>
       </x:c>
       <x:c r="Q16" s="12" t="str">
         <x:f>Produits!AG16</x:f>
-        <x:v>À rechercher</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -14647,19 +14732,19 @@
       </x:c>
       <x:c r="E17" s="12" t="str">
         <x:f>Produits!E17</x:f>
-        <x:v>Balance</x:v>
+        <x:v>Amazfit Balance 2</x:v>
       </x:c>
       <x:c r="F17" s="12" t="str">
         <x:f>Produits!F17</x:f>
         <x:v>Amazfit</x:v>
       </x:c>
-      <x:c r="G17" s="12" t="n">
+      <x:c r="G17" s="12" t="str">
         <x:f>Produits!H17</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H17" s="12" t="n">
+        <x:v>B0F8HNKK6Z</x:v>
+      </x:c>
+      <x:c r="H17" s="12" t="str">
         <x:f>Produits!I17</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B0F8HNKK6Z</x:v>
       </x:c>
       <x:c r="I17" s="12" t="n">
         <x:f>Produits!K17</x:f>
@@ -14671,31 +14756,31 @@
       </x:c>
       <x:c r="K17" s="12" t="n">
         <x:f>Produits!U17</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L17" s="12" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="L17" s="12" t="str">
         <x:f>Produits!V17</x:f>
-        <x:v>0</x:v>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="M17" s="12" t="str">
         <x:f>Produits!Z17</x:f>
-        <x:v>Montre riche en fonctions à prix compétitif.</x:v>
+        <x:v>Une montre très riche en fonctions avec une excellente autonomie, un GPS double bande et un positionnement tarifaire compétitif.</x:v>
       </x:c>
       <x:c r="N17" s="12" t="str">
         <x:f>Produits!AA17</x:f>
-        <x:v>Écran | Autonomie | Fonctions</x:v>
+        <x:v>Autonomie jusqu’à 21 jours | Plus de 170 sports | Verre saphir | GPS double bande | Étanchéité 10 ATM</x:v>
       </x:c>
       <x:c r="O17" s="12" t="str">
         <x:f>Produits!AB17</x:f>
-        <x:v>Écosystème moins mature que Garmin</x:v>
+        <x:v>Écosystème d’applications moins riche que Garmin | Format imposant | Fonctions connectées plus limitées</x:v>
       </x:c>
       <x:c r="P17" s="12" t="str">
         <x:f>Produits!AC17</x:f>
-        <x:v>Débutant / intermédiaire</x:v>
+        <x:v>Débutant à intermédiaire voulant beaucoup de fonctions et une longue autonomie</x:v>
       </x:c>
       <x:c r="Q17" s="12" t="str">
         <x:f>Produits!AG17</x:f>
-        <x:v>À rechercher</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -14717,19 +14802,19 @@
       </x:c>
       <x:c r="E18" s="12" t="str">
         <x:f>Produits!E18</x:f>
-        <x:v>Fenix 8</x:v>
+        <x:v>Garmin fēnix 8 AMOLED 43 mm</x:v>
       </x:c>
       <x:c r="F18" s="12" t="str">
         <x:f>Produits!F18</x:f>
         <x:v>Garmin</x:v>
       </x:c>
-      <x:c r="G18" s="12" t="n">
+      <x:c r="G18" s="12" t="str">
         <x:f>Produits!H18</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H18" s="12" t="n">
+        <x:v>B0FSFDF2N8</x:v>
+      </x:c>
+      <x:c r="H18" s="12" t="str">
         <x:f>Produits!I18</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B0FSFDF2N8</x:v>
       </x:c>
       <x:c r="I18" s="12" t="n">
         <x:f>Produits!K18</x:f>
@@ -14741,30 +14826,31 @@
       </x:c>
       <x:c r="K18" s="12" t="n">
         <x:f>Produits!U18</x:f>
-        <x:v>0</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="L18" s="12" t="str">
         <x:f>Produits!V18</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="M18" s="12" t="str">
         <x:f>Produits!Z18</x:f>
-        <x:v>Montre multisport premium pour utilisateurs exigeants.</x:v>
+        <x:v>Une montre multisport premium très complète pour l’entraînement avancé, l’outdoor et la navigation, dans un format compact.</x:v>
       </x:c>
       <x:c r="N18" s="12" t="str">
         <x:f>Produits!AA18</x:f>
-        <x:v>Robustesse | Cartographie | Fonctions avancées</x:v>
+        <x:v>Cartographie et GPS multibande | Lampe LED | Étanchéité 10 ATM | Fonctions sport très avancées | Construction premium</x:v>
       </x:c>
       <x:c r="O18" s="12" t="str">
         <x:f>Produits!AB18</x:f>
-        <x:v>Prix très élevé | Surdimensionnée pour certains</x:v>
+        <x:v>Prix très élevé | Complexe pour un usage basique | Autonomie inférieure aux grandes tailles de la gamme</x:v>
       </x:c>
       <x:c r="P18" s="12" t="str">
         <x:f>Produits!AC18</x:f>
-        <x:v>Sportif confirmé</x:v>
+        <x:v>Sportif confirmé ou pratiquant outdoor recherchant une montre haut de gamme</x:v>
       </x:c>
       <x:c r="Q18" s="12" t="str">
         <x:f>Produits!AG18</x:f>
-        <x:v>À rechercher</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="19">

--- a/data/import/MuscuGuide_Base_Produits.xlsx
+++ b/data/import/MuscuGuide_Base_Produits.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Re18a0502bd594196"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produits" sheetId="2" r:id="R680521ec077b4502"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notation" sheetId="3" r:id="R7f641ca45b6e42d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Claude" sheetId="4" r:id="Rc652bcfe81094517"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="5" r:id="R2ec6f64b12324307"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="6" r:id="R328bddf118a7432d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rbc1c19aa14524c49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produits" sheetId="2" r:id="R0717cbc682e144c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notation" sheetId="3" r:id="Rba48f9bb3e884651"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Claude" sheetId="4" r:id="Rc0ac66eb845549bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="5" r:id="R3961eff14e1743fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="6" r:id="R1d5d1225fcaa4464"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -435,7 +435,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R57a2a156b70c45af"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1cce5c658ba04fd6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -687,7 +687,7 @@
       </x:c>
       <x:c r="B4" s="12" t="n">
         <x:f>COUNTA(Produits!E4:E250)</x:f>
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C4" s="12"/>
       <x:c r="D4" s="12" t="str">
@@ -747,7 +747,7 @@
       </x:c>
       <x:c r="B6" s="12" t="n">
         <x:f>COUNTIF(Produits!AG4:AG250,"Validé")</x:f>
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C6" s="12"/>
       <x:c r="D6" s="12" t="str">
@@ -807,7 +807,7 @@
       </x:c>
       <x:c r="B8" s="38" t="n">
         <x:f>IFERROR(AVERAGE(Produits!U4:U250),0)</x:f>
-        <x:v>88.8</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C8" s="12"/>
       <x:c r="D8" s="12" t="str">
@@ -876,7 +876,7 @@
       </x:c>
       <x:c r="E10" s="12" t="n">
         <x:f>COUNTIF(Produits!B:B,D10)</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F10" s="12" t="n">
         <x:f>COUNTIFS(Produits!B:B,D10,Produits!H:H,"??????????")</x:f>
@@ -884,7 +884,7 @@
       </x:c>
       <x:c r="G10" s="12" t="n">
         <x:f>COUNTIFS(Produits!B:B,D10,Produits!AG:AG,"Validé")</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H10" s="46" t="n">
         <x:f>IFERROR(F10/E10,0)</x:f>
@@ -1259,7 +1259,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb37b627c42434673"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fab862b0d784031"/>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -3860,133 +3860,309 @@
       </x:c>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="12"/>
-      <x:c r="B31" s="12"/>
-      <x:c r="C31" s="12"/>
-      <x:c r="D31" s="12"/>
-      <x:c r="E31" s="12"/>
-      <x:c r="F31" s="12"/>
-      <x:c r="G31" s="12"/>
-      <x:c r="H31" s="12"/>
-      <x:c r="I31" s="12"/>
+      <x:c r="A31" s="12" t="str">
+        <x:v>MG-RACK-001</x:v>
+      </x:c>
+      <x:c r="B31" s="12" t="str">
+        <x:v>Rack à squat</x:v>
+      </x:c>
+      <x:c r="C31" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D31" s="12" t="str">
+        <x:v>Choix MuscuGuide</x:v>
+      </x:c>
+      <x:c r="E31" s="12" t="str">
+        <x:v>PASYOU SR30</x:v>
+      </x:c>
+      <x:c r="F31" s="12" t="str">
+        <x:v>PASYOU</x:v>
+      </x:c>
+      <x:c r="G31" s="12" t="str">
+        <x:v>Squat rack 29,9 kg — 14 positions J-cups — sécurités réglables</x:v>
+      </x:c>
+      <x:c r="H31" s="12" t="str">
+        <x:v>B0C27XKJJN</x:v>
+      </x:c>
+      <x:c r="I31" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0C27XKJJN</x:v>
+      </x:c>
       <x:c r="J31" s="12"/>
       <x:c r="K31" s="12" t="str">
         <x:f>IF(OR(H31="",J31=""),"", "https://www.amazon.fr/dp/"&amp;H31&amp;"?tag="&amp;J31)</x:f>
       </x:c>
       <x:c r="L31" s="12"/>
       <x:c r="M31" s="36"/>
-      <x:c r="N31" s="12"/>
-      <x:c r="O31" s="12"/>
-      <x:c r="P31" s="12"/>
-      <x:c r="Q31" s="12"/>
-      <x:c r="R31" s="12"/>
-      <x:c r="S31" s="12"/>
-      <x:c r="T31" s="12"/>
-      <x:c r="U31" s="12" t="str">
+      <x:c r="N31" s="12" t="str">
+        <x:v>Performance</x:v>
+      </x:c>
+      <x:c r="O31" s="12" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P31" s="12" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q31" s="12" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="R31" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="S31" s="12" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="T31" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="U31" s="12" t="n">
         <x:f>IF(COUNTA(O31:T31)=0,"",SUM(O31:T31))</x:f>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="V31" s="12" t="str">
         <x:f>IF(U31="","",IF(U31&gt;=95,"Exceptionnel",IF(U31&gt;=90,"Excellent",IF(U31&gt;=85,"Très bon",IF(U31&gt;=80,"Bon",IF(U31&gt;=70,"Correct","À revoir"))))))</x:f>
-      </x:c>
-      <x:c r="W31" s="12"/>
-      <x:c r="X31" s="12"/>
-      <x:c r="Y31" s="12"/>
-      <x:c r="Z31" s="12"/>
-      <x:c r="AA31" s="12"/>
-      <x:c r="AB31" s="12"/>
-      <x:c r="AC31" s="12"/>
-      <x:c r="AD31" s="12"/>
-      <x:c r="AE31" s="38"/>
-      <x:c r="AF31" s="40"/>
-      <x:c r="AG31" s="12"/>
-      <x:c r="AH31" s="12"/>
-      <x:c r="AI31" s="12"/>
+        <x:v>Excellent</x:v>
+      </x:c>
+      <x:c r="W31" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="X31" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="Y31" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="Z31" s="12" t="str">
+        <x:v>Un rack lourd et stable, bien adapté à un home gym sérieux grâce à ses nombreux réglages et à ses sécurités robustes.</x:v>
+      </x:c>
+      <x:c r="AA31" s="12" t="str">
+        <x:v>Structure de 29,9 kg | 14 positions pour les J-cups | Sécurités réglables | Charge annoncée élevée | Très bon équilibre stabilité/prix</x:v>
+      </x:c>
+      <x:c r="AB31" s="12" t="str">
+        <x:v>Encombrement supérieur aux chandelles séparées | Montage nécessaire | SAV moins établi que les grandes marques</x:v>
+      </x:c>
+      <x:c r="AC31" s="12" t="str">
+        <x:v>Intermédiaire à confirmé recherchant un rack stable pour squat et développé couché</x:v>
+      </x:c>
+      <x:c r="AD31" s="12" t="n">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="AE31" s="38" t="n">
+        <x:v>4.4</x:v>
+      </x:c>
+      <x:c r="AF31" s="55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="AG31" s="12" t="str">
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH31" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0C27XKJJN</x:v>
+      </x:c>
+      <x:c r="AI31" s="12" t="str">
+        <x:v>ASIN, note Amazon 4,4/5 et 575 évaluations vérifiés le 05/08/2026. Poids de 29,9 kg, J-cups jusqu’à 200 kg, sécurités annoncées jusqu’à 800 kg et réglages confirmés sur Amazon FR.</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="12"/>
-      <x:c r="B32" s="12"/>
-      <x:c r="C32" s="12"/>
-      <x:c r="D32" s="12"/>
-      <x:c r="E32" s="12"/>
-      <x:c r="F32" s="12"/>
-      <x:c r="G32" s="12"/>
-      <x:c r="H32" s="12"/>
-      <x:c r="I32" s="12"/>
+      <x:c r="A32" s="12" t="str">
+        <x:v>MG-RACK-002</x:v>
+      </x:c>
+      <x:c r="B32" s="12" t="str">
+        <x:v>Rack à squat</x:v>
+      </x:c>
+      <x:c r="C32" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D32" s="12" t="str">
+        <x:v>Meilleur rapport qualité/prix</x:v>
+      </x:c>
+      <x:c r="E32" s="12" t="str">
+        <x:v>ISE SY-RK1001</x:v>
+      </x:c>
+      <x:c r="F32" s="12" t="str">
+        <x:v>ISE</x:v>
+      </x:c>
+      <x:c r="G32" s="12" t="str">
+        <x:v>16 positions de hauteur — capacité annoncée 200 kg</x:v>
+      </x:c>
+      <x:c r="H32" s="12" t="str">
+        <x:v>B07F63NLYG</x:v>
+      </x:c>
+      <x:c r="I32" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B07F63NLYG</x:v>
+      </x:c>
       <x:c r="J32" s="12"/>
       <x:c r="K32" s="12" t="str">
         <x:f>IF(OR(H32="",J32=""),"", "https://www.amazon.fr/dp/"&amp;H32&amp;"?tag="&amp;J32)</x:f>
       </x:c>
       <x:c r="L32" s="12"/>
       <x:c r="M32" s="36"/>
-      <x:c r="N32" s="12"/>
-      <x:c r="O32" s="12"/>
-      <x:c r="P32" s="12"/>
-      <x:c r="Q32" s="12"/>
-      <x:c r="R32" s="12"/>
-      <x:c r="S32" s="12"/>
-      <x:c r="T32" s="12"/>
-      <x:c r="U32" s="12" t="str">
+      <x:c r="N32" s="12" t="str">
+        <x:v>Essentials</x:v>
+      </x:c>
+      <x:c r="O32" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P32" s="12" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q32" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="R32" s="12" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="S32" s="12" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="T32" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="U32" s="12" t="n">
         <x:f>IF(COUNTA(O32:T32)=0,"",SUM(O32:T32))</x:f>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="V32" s="12" t="str">
         <x:f>IF(U32="","",IF(U32&gt;=95,"Exceptionnel",IF(U32&gt;=90,"Excellent",IF(U32&gt;=85,"Très bon",IF(U32&gt;=80,"Bon",IF(U32&gt;=70,"Correct","À revoir"))))))</x:f>
-      </x:c>
-      <x:c r="W32" s="12"/>
-      <x:c r="X32" s="12"/>
+        <x:v>Très bon</x:v>
+      </x:c>
+      <x:c r="W32" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="X32" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
       <x:c r="Y32" s="12"/>
-      <x:c r="Z32" s="12"/>
-      <x:c r="AA32" s="12"/>
-      <x:c r="AB32" s="12"/>
-      <x:c r="AC32" s="12"/>
-      <x:c r="AD32" s="12"/>
-      <x:c r="AE32" s="38"/>
-      <x:c r="AF32" s="40"/>
-      <x:c r="AG32" s="12"/>
-      <x:c r="AH32" s="12"/>
-      <x:c r="AI32" s="12"/>
+      <x:c r="Z32" s="12" t="str">
+        <x:v>Une solution très populaire et accessible pour débuter la musculation avec barre à domicile sans investir dans une cage complète.</x:v>
+      </x:c>
+      <x:c r="AA32" s="12" t="str">
+        <x:v>Excellent rapport qualité/prix | 16 positions de hauteur | Capacité annoncée 200 kg | Large base d’avis clients | Compact</x:v>
+      </x:c>
+      <x:c r="AB32" s="12" t="str">
+        <x:v>Moins protecteur qu’une cage complète | Pas de barre de traction | Stabilité dépendante du réglage et du sol</x:v>
+      </x:c>
+      <x:c r="AC32" s="12" t="str">
+        <x:v>Débutant à intermédiaire disposant de peu d’espace</x:v>
+      </x:c>
+      <x:c r="AD32" s="12" t="n">
+        <x:v>1934</x:v>
+      </x:c>
+      <x:c r="AE32" s="38" t="n">
+        <x:v>4.4</x:v>
+      </x:c>
+      <x:c r="AF32" s="55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="AG32" s="12" t="str">
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH32" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B07F63NLYG</x:v>
+      </x:c>
+      <x:c r="AI32" s="12" t="str">
+        <x:v>ASIN, note Amazon 4,4/5 et 1 934 évaluations vérifiés le 05/08/2026. Les 16 positions et la capacité annoncée de 200 kg sont confirmées sur Amazon FR.</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="12"/>
-      <x:c r="B33" s="12"/>
-      <x:c r="C33" s="12"/>
-      <x:c r="D33" s="12"/>
-      <x:c r="E33" s="12"/>
-      <x:c r="F33" s="12"/>
-      <x:c r="G33" s="12"/>
-      <x:c r="H33" s="12"/>
-      <x:c r="I33" s="12"/>
+      <x:c r="A33" s="12" t="str">
+        <x:v>MG-RACK-003</x:v>
+      </x:c>
+      <x:c r="B33" s="12" t="str">
+        <x:v>Rack à squat</x:v>
+      </x:c>
+      <x:c r="C33" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D33" s="12" t="str">
+        <x:v>Premium</x:v>
+      </x:c>
+      <x:c r="E33" s="12" t="str">
+        <x:v>HOP-Sport HS-1014K</x:v>
+      </x:c>
+      <x:c r="F33" s="12" t="str">
+        <x:v>HS HOP-SPORT</x:v>
+      </x:c>
+      <x:c r="G33" s="12" t="str">
+        <x:v>Power tower, squat rack, dips et barre de traction — charge 300 kg</x:v>
+      </x:c>
+      <x:c r="H33" s="12" t="str">
+        <x:v>B08VKPD44D</x:v>
+      </x:c>
+      <x:c r="I33" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B08VKPD44D</x:v>
+      </x:c>
       <x:c r="J33" s="12"/>
       <x:c r="K33" s="12" t="str">
         <x:f>IF(OR(H33="",J33=""),"", "https://www.amazon.fr/dp/"&amp;H33&amp;"?tag="&amp;J33)</x:f>
       </x:c>
       <x:c r="L33" s="12"/>
       <x:c r="M33" s="36"/>
-      <x:c r="N33" s="12"/>
-      <x:c r="O33" s="12"/>
-      <x:c r="P33" s="12"/>
-      <x:c r="Q33" s="12"/>
-      <x:c r="R33" s="12"/>
-      <x:c r="S33" s="12"/>
-      <x:c r="T33" s="12"/>
-      <x:c r="U33" s="12" t="str">
+      <x:c r="N33" s="12" t="str">
+        <x:v>Elite</x:v>
+      </x:c>
+      <x:c r="O33" s="12" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P33" s="12" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="Q33" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="R33" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="S33" s="12" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="T33" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="U33" s="12" t="n">
         <x:f>IF(COUNTA(O33:T33)=0,"",SUM(O33:T33))</x:f>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="V33" s="12" t="str">
         <x:f>IF(U33="","",IF(U33&gt;=95,"Exceptionnel",IF(U33&gt;=90,"Excellent",IF(U33&gt;=85,"Très bon",IF(U33&gt;=80,"Bon",IF(U33&gt;=70,"Correct","À revoir"))))))</x:f>
+        <x:v>Très bon</x:v>
       </x:c>
       <x:c r="W33" s="12"/>
-      <x:c r="X33" s="12"/>
-      <x:c r="Y33" s="12"/>
-      <x:c r="Z33" s="12"/>
-      <x:c r="AA33" s="12"/>
-      <x:c r="AB33" s="12"/>
-      <x:c r="AC33" s="12"/>
-      <x:c r="AD33" s="12"/>
-      <x:c r="AE33" s="38"/>
-      <x:c r="AF33" s="40"/>
-      <x:c r="AG33" s="12"/>
-      <x:c r="AH33" s="12"/>
-      <x:c r="AI33" s="12"/>
+      <x:c r="X33" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="Y33" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="Z33" s="12" t="str">
+        <x:v>Une station premium très polyvalente qui combine rack à squat, chaise romaine, dips et barre de traction dans une structure unique.</x:v>
+      </x:c>
+      <x:c r="AA33" s="12" t="str">
+        <x:v>Charge maximale annoncée 300 kg | Barre de traction | Station à dips | Double sécurité pour la barre | Structure acier 50 × 50 mm</x:v>
+      </x:c>
+      <x:c r="AB33" s="12" t="str">
+        <x:v>Plus encombrante et lourde | Prix supérieur | Montage plus long | Moins compacte qu’un rack simple</x:v>
+      </x:c>
+      <x:c r="AC33" s="12" t="str">
+        <x:v>Intermédiaire ou confirmé souhaitant une station multifonction durable</x:v>
+      </x:c>
+      <x:c r="AD33" s="12" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="AE33" s="38" t="n">
+        <x:v>4.4</x:v>
+      </x:c>
+      <x:c r="AF33" s="55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="AG33" s="12" t="str">
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH33" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B08VKPD44D</x:v>
+      </x:c>
+      <x:c r="AI33" s="12" t="str">
+        <x:v>ASIN, note Amazon 4,4/5 et 101 évaluations vérifiés le 05/08/2026. Charge maximale annoncée 300 kg, cadre 50 × 50 mm et fonctions squat/dips/traction confirmées sur Amazon FR.</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="12"/>
@@ -13389,7 +13565,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e823cdb6f54475d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R013c85eea3404df4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15689,37 +15865,37 @@
       </x:c>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="12" t="n">
+      <x:c r="A31" s="12" t="str">
         <x:f>Produits!A31</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B31" s="12" t="n">
+        <x:v>MG-RACK-001</x:v>
+      </x:c>
+      <x:c r="B31" s="12" t="str">
         <x:f>Produits!B31</x:f>
-        <x:v>0</x:v>
+        <x:v>Rack à squat</x:v>
       </x:c>
       <x:c r="C31" s="12" t="n">
         <x:f>Produits!C31</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D31" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D31" s="12" t="str">
         <x:f>Produits!D31</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E31" s="12" t="n">
+        <x:v>Choix MuscuGuide</x:v>
+      </x:c>
+      <x:c r="E31" s="12" t="str">
         <x:f>Produits!E31</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F31" s="12" t="n">
+        <x:v>PASYOU SR30</x:v>
+      </x:c>
+      <x:c r="F31" s="12" t="str">
         <x:f>Produits!F31</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G31" s="12" t="n">
+        <x:v>PASYOU</x:v>
+      </x:c>
+      <x:c r="G31" s="12" t="str">
         <x:f>Produits!H31</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H31" s="12" t="n">
+        <x:v>B0C27XKJJN</x:v>
+      </x:c>
+      <x:c r="H31" s="12" t="str">
         <x:f>Produits!I31</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B0C27XKJJN</x:v>
       </x:c>
       <x:c r="I31" s="12" t="n">
         <x:f>Produits!K31</x:f>
@@ -15731,65 +15907,65 @@
       </x:c>
       <x:c r="K31" s="12" t="n">
         <x:f>Produits!U31</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L31" s="12" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="L31" s="12" t="str">
         <x:f>Produits!V31</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M31" s="12" t="n">
+        <x:v>Excellent</x:v>
+      </x:c>
+      <x:c r="M31" s="12" t="str">
         <x:f>Produits!Z31</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N31" s="12" t="n">
+        <x:v>Un rack lourd et stable, bien adapté à un home gym sérieux grâce à ses nombreux réglages et à ses sécurités robustes.</x:v>
+      </x:c>
+      <x:c r="N31" s="12" t="str">
         <x:f>Produits!AA31</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O31" s="12" t="n">
+        <x:v>Structure de 29,9 kg | 14 positions pour les J-cups | Sécurités réglables | Charge annoncée élevée | Très bon équilibre stabilité/prix</x:v>
+      </x:c>
+      <x:c r="O31" s="12" t="str">
         <x:f>Produits!AB31</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P31" s="12" t="n">
+        <x:v>Encombrement supérieur aux chandelles séparées | Montage nécessaire | SAV moins établi que les grandes marques</x:v>
+      </x:c>
+      <x:c r="P31" s="12" t="str">
         <x:f>Produits!AC31</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q31" s="12" t="n">
+        <x:v>Intermédiaire à confirmé recherchant un rack stable pour squat et développé couché</x:v>
+      </x:c>
+      <x:c r="Q31" s="12" t="str">
         <x:f>Produits!AG31</x:f>
-        <x:v>0</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="12" t="n">
+      <x:c r="A32" s="12" t="str">
         <x:f>Produits!A32</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B32" s="12" t="n">
+        <x:v>MG-RACK-002</x:v>
+      </x:c>
+      <x:c r="B32" s="12" t="str">
         <x:f>Produits!B32</x:f>
-        <x:v>0</x:v>
+        <x:v>Rack à squat</x:v>
       </x:c>
       <x:c r="C32" s="12" t="n">
         <x:f>Produits!C32</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D32" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D32" s="12" t="str">
         <x:f>Produits!D32</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E32" s="12" t="n">
+        <x:v>Meilleur rapport qualité/prix</x:v>
+      </x:c>
+      <x:c r="E32" s="12" t="str">
         <x:f>Produits!E32</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F32" s="12" t="n">
+        <x:v>ISE SY-RK1001</x:v>
+      </x:c>
+      <x:c r="F32" s="12" t="str">
         <x:f>Produits!F32</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G32" s="12" t="n">
+        <x:v>ISE</x:v>
+      </x:c>
+      <x:c r="G32" s="12" t="str">
         <x:f>Produits!H32</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H32" s="12" t="n">
+        <x:v>B07F63NLYG</x:v>
+      </x:c>
+      <x:c r="H32" s="12" t="str">
         <x:f>Produits!I32</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B07F63NLYG</x:v>
       </x:c>
       <x:c r="I32" s="12" t="n">
         <x:f>Produits!K32</x:f>
@@ -15801,65 +15977,65 @@
       </x:c>
       <x:c r="K32" s="12" t="n">
         <x:f>Produits!U32</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L32" s="12" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="L32" s="12" t="str">
         <x:f>Produits!V32</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M32" s="12" t="n">
+        <x:v>Très bon</x:v>
+      </x:c>
+      <x:c r="M32" s="12" t="str">
         <x:f>Produits!Z32</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N32" s="12" t="n">
+        <x:v>Une solution très populaire et accessible pour débuter la musculation avec barre à domicile sans investir dans une cage complète.</x:v>
+      </x:c>
+      <x:c r="N32" s="12" t="str">
         <x:f>Produits!AA32</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O32" s="12" t="n">
+        <x:v>Excellent rapport qualité/prix | 16 positions de hauteur | Capacité annoncée 200 kg | Large base d’avis clients | Compact</x:v>
+      </x:c>
+      <x:c r="O32" s="12" t="str">
         <x:f>Produits!AB32</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P32" s="12" t="n">
+        <x:v>Moins protecteur qu’une cage complète | Pas de barre de traction | Stabilité dépendante du réglage et du sol</x:v>
+      </x:c>
+      <x:c r="P32" s="12" t="str">
         <x:f>Produits!AC32</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q32" s="12" t="n">
+        <x:v>Débutant à intermédiaire disposant de peu d’espace</x:v>
+      </x:c>
+      <x:c r="Q32" s="12" t="str">
         <x:f>Produits!AG32</x:f>
-        <x:v>0</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="12" t="n">
+      <x:c r="A33" s="12" t="str">
         <x:f>Produits!A33</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B33" s="12" t="n">
+        <x:v>MG-RACK-003</x:v>
+      </x:c>
+      <x:c r="B33" s="12" t="str">
         <x:f>Produits!B33</x:f>
-        <x:v>0</x:v>
+        <x:v>Rack à squat</x:v>
       </x:c>
       <x:c r="C33" s="12" t="n">
         <x:f>Produits!C33</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D33" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D33" s="12" t="str">
         <x:f>Produits!D33</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E33" s="12" t="n">
+        <x:v>Premium</x:v>
+      </x:c>
+      <x:c r="E33" s="12" t="str">
         <x:f>Produits!E33</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F33" s="12" t="n">
+        <x:v>HOP-Sport HS-1014K</x:v>
+      </x:c>
+      <x:c r="F33" s="12" t="str">
         <x:f>Produits!F33</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G33" s="12" t="n">
+        <x:v>HS HOP-SPORT</x:v>
+      </x:c>
+      <x:c r="G33" s="12" t="str">
         <x:f>Produits!H33</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H33" s="12" t="n">
+        <x:v>B08VKPD44D</x:v>
+      </x:c>
+      <x:c r="H33" s="12" t="str">
         <x:f>Produits!I33</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B08VKPD44D</x:v>
       </x:c>
       <x:c r="I33" s="12" t="n">
         <x:f>Produits!K33</x:f>
@@ -15871,31 +16047,31 @@
       </x:c>
       <x:c r="K33" s="12" t="n">
         <x:f>Produits!U33</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L33" s="12" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="L33" s="12" t="str">
         <x:f>Produits!V33</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M33" s="12" t="n">
+        <x:v>Très bon</x:v>
+      </x:c>
+      <x:c r="M33" s="12" t="str">
         <x:f>Produits!Z33</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N33" s="12" t="n">
+        <x:v>Une station premium très polyvalente qui combine rack à squat, chaise romaine, dips et barre de traction dans une structure unique.</x:v>
+      </x:c>
+      <x:c r="N33" s="12" t="str">
         <x:f>Produits!AA33</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O33" s="12" t="n">
+        <x:v>Charge maximale annoncée 300 kg | Barre de traction | Station à dips | Double sécurité pour la barre | Structure acier 50 × 50 mm</x:v>
+      </x:c>
+      <x:c r="O33" s="12" t="str">
         <x:f>Produits!AB33</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P33" s="12" t="n">
+        <x:v>Plus encombrante et lourde | Prix supérieur | Montage plus long | Moins compacte qu’un rack simple</x:v>
+      </x:c>
+      <x:c r="P33" s="12" t="str">
         <x:f>Produits!AC33</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q33" s="12" t="n">
+        <x:v>Intermédiaire ou confirmé souhaitant une station multifonction durable</x:v>
+      </x:c>
+      <x:c r="Q33" s="12" t="str">
         <x:f>Produits!AG33</x:f>
-        <x:v>0</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="34">

--- a/data/import/MuscuGuide_Base_Produits.xlsx
+++ b/data/import/MuscuGuide_Base_Produits.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rbc1c19aa14524c49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produits" sheetId="2" r:id="R0717cbc682e144c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notation" sheetId="3" r:id="Rba48f9bb3e884651"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Claude" sheetId="4" r:id="Rc0ac66eb845549bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="5" r:id="R3961eff14e1743fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="6" r:id="R1d5d1225fcaa4464"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R7fe4e726a84d4ecc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produits" sheetId="2" r:id="R7b5f62162fe34974"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notation" sheetId="3" r:id="R9cec57baca004427"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Claude" sheetId="4" r:id="R93688208b42f417f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="5" r:id="Rc34668e0f1974ff9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="6" r:id="R90f8366475ec45f0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -435,7 +435,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1cce5c658ba04fd6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4c1b41b7f9d243ce"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -687,7 +687,7 @@
       </x:c>
       <x:c r="B4" s="12" t="n">
         <x:f>COUNTA(Produits!E4:E250)</x:f>
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C4" s="12"/>
       <x:c r="D4" s="12" t="str">
@@ -747,7 +747,7 @@
       </x:c>
       <x:c r="B6" s="12" t="n">
         <x:f>COUNTIF(Produits!AG4:AG250,"Validé")</x:f>
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C6" s="12"/>
       <x:c r="D6" s="12" t="str">
@@ -1042,7 +1042,7 @@
       </x:c>
       <x:c r="E16" s="12" t="n">
         <x:f>COUNTIF(Produits!B:B,D16)</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F16" s="12" t="n">
         <x:f>COUNTIFS(Produits!B:B,D16,Produits!H:H,"??????????")</x:f>
@@ -1050,7 +1050,7 @@
       </x:c>
       <x:c r="G16" s="12" t="n">
         <x:f>COUNTIFS(Produits!B:B,D16,Produits!AG:AG,"Validé")</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H16" s="46" t="n">
         <x:f>IFERROR(F16/E16,0)</x:f>
@@ -1259,7 +1259,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fab862b0d784031"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1299c99b45ce4653"/>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -4165,133 +4165,305 @@
       </x:c>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="12"/>
-      <x:c r="B34" s="12"/>
-      <x:c r="C34" s="12"/>
-      <x:c r="D34" s="12"/>
-      <x:c r="E34" s="12"/>
-      <x:c r="F34" s="12"/>
-      <x:c r="G34" s="12"/>
-      <x:c r="H34" s="12"/>
-      <x:c r="I34" s="12"/>
+      <x:c r="A34" s="12" t="str">
+        <x:v>MG-BARRE-001</x:v>
+      </x:c>
+      <x:c r="B34" s="12" t="str">
+        <x:v>Barre olympique</x:v>
+      </x:c>
+      <x:c r="C34" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D34" s="12" t="str">
+        <x:v>Choix MuscuGuide</x:v>
+      </x:c>
+      <x:c r="E34" s="12" t="str">
+        <x:v>Strength Shop Original 2029 Power Bar</x:v>
+      </x:c>
+      <x:c r="F34" s="12" t="str">
+        <x:v>Strength Shop</x:v>
+      </x:c>
+      <x:c r="G34" s="12" t="str">
+        <x:v>20 kg — 220 cm — axe 29 mm — 185K PSI — bagues bronze</x:v>
+      </x:c>
+      <x:c r="H34" s="12" t="str">
+        <x:v>B0CLT8NFSW</x:v>
+      </x:c>
+      <x:c r="I34" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0CLT8NFSW</x:v>
+      </x:c>
       <x:c r="J34" s="12"/>
       <x:c r="K34" s="12" t="str">
         <x:f>IF(OR(H34="",J34=""),"", "https://www.amazon.fr/dp/"&amp;H34&amp;"?tag="&amp;J34)</x:f>
       </x:c>
       <x:c r="L34" s="12"/>
       <x:c r="M34" s="36"/>
-      <x:c r="N34" s="12"/>
-      <x:c r="O34" s="12"/>
-      <x:c r="P34" s="12"/>
-      <x:c r="Q34" s="12"/>
-      <x:c r="R34" s="12"/>
-      <x:c r="S34" s="12"/>
-      <x:c r="T34" s="12"/>
-      <x:c r="U34" s="12" t="str">
+      <x:c r="N34" s="12" t="str">
+        <x:v>Performance</x:v>
+      </x:c>
+      <x:c r="O34" s="12" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P34" s="12" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Q34" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="R34" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="S34" s="12" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="T34" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="U34" s="12" t="n">
         <x:f>IF(COUNTA(O34:T34)=0,"",SUM(O34:T34))</x:f>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="V34" s="12" t="str">
         <x:f>IF(U34="","",IF(U34&gt;=95,"Exceptionnel",IF(U34&gt;=90,"Excellent",IF(U34&gt;=85,"Très bon",IF(U34&gt;=80,"Bon",IF(U34&gt;=70,"Correct","À revoir"))))))</x:f>
-      </x:c>
-      <x:c r="W34" s="12"/>
-      <x:c r="X34" s="12"/>
-      <x:c r="Y34" s="12"/>
-      <x:c r="Z34" s="12"/>
-      <x:c r="AA34" s="12"/>
-      <x:c r="AB34" s="12"/>
-      <x:c r="AC34" s="12"/>
-      <x:c r="AD34" s="12"/>
-      <x:c r="AE34" s="38"/>
-      <x:c r="AF34" s="40"/>
-      <x:c r="AG34" s="12"/>
-      <x:c r="AH34" s="12"/>
-      <x:c r="AI34" s="12"/>
+        <x:v>Excellent</x:v>
+      </x:c>
+      <x:c r="W34" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="X34" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="Y34" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="Z34" s="12" t="str">
+        <x:v>Une barre de force sérieuse et bien équilibrée pour le squat, le développé couché et le soulevé de terre dans un home gym exigeant.</x:v>
+      </x:c>
+      <x:c r="AA34" s="12" t="str">
+        <x:v>Standard 20 kg et 220 cm | Axe 29 mm typé powerlifting | Moletage central | Bagues en bronze | Revêtement E-Coat résistant</x:v>
+      </x:c>
+      <x:c r="AB34" s="12" t="str">
+        <x:v>Charge conseillée de 260 kg | Moletage assez agressif | Moins adaptée à l’haltérophilie olympique dynamique</x:v>
+      </x:c>
+      <x:c r="AC34" s="12" t="str">
+        <x:v>Intermédiaire à confirmé orienté powerlifting et mouvements de force</x:v>
+      </x:c>
+      <x:c r="AD34" s="12" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="AE34" s="38" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="AF34" s="55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="AG34" s="12" t="str">
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH34" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0CLT8NFSW</x:v>
+      </x:c>
+      <x:c r="AI34" s="12" t="str">
+        <x:v>ASIN, note Amazon 4,5/5 et 58 évaluations vérifiés le 05/08/2026. Spécifications 20 kg, 220 cm, axe 29 mm, 185K PSI, bagues bronze et charge conseillée 260 kg confirmées par Strength Shop : https://strengthshop.eu/products/original-2029-power-bar-all-black</x:v>
+      </x:c>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="12"/>
-      <x:c r="B35" s="12"/>
-      <x:c r="C35" s="12"/>
-      <x:c r="D35" s="12"/>
-      <x:c r="E35" s="12"/>
-      <x:c r="F35" s="12"/>
-      <x:c r="G35" s="12"/>
-      <x:c r="H35" s="12"/>
-      <x:c r="I35" s="12"/>
+      <x:c r="A35" s="12" t="str">
+        <x:v>MG-BARRE-002</x:v>
+      </x:c>
+      <x:c r="B35" s="12" t="str">
+        <x:v>Barre olympique</x:v>
+      </x:c>
+      <x:c r="C35" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D35" s="12" t="str">
+        <x:v>Meilleur rapport qualité/prix</x:v>
+      </x:c>
+      <x:c r="E35" s="12" t="str">
+        <x:v>DIAMOND Barre olympique Power Training 220 cm</x:v>
+      </x:c>
+      <x:c r="F35" s="12" t="str">
+        <x:v>DIAMOND</x:v>
+      </x:c>
+      <x:c r="G35" s="12" t="str">
+        <x:v>220 cm — manchons 50 mm — charge maximale annoncée 320 kg</x:v>
+      </x:c>
+      <x:c r="H35" s="12" t="str">
+        <x:v>B0CWFD1FKH</x:v>
+      </x:c>
+      <x:c r="I35" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0CWFD1FKH</x:v>
+      </x:c>
       <x:c r="J35" s="12"/>
       <x:c r="K35" s="12" t="str">
         <x:f>IF(OR(H35="",J35=""),"", "https://www.amazon.fr/dp/"&amp;H35&amp;"?tag="&amp;J35)</x:f>
       </x:c>
       <x:c r="L35" s="12"/>
       <x:c r="M35" s="36"/>
-      <x:c r="N35" s="12"/>
-      <x:c r="O35" s="12"/>
-      <x:c r="P35" s="12"/>
-      <x:c r="Q35" s="12"/>
-      <x:c r="R35" s="12"/>
-      <x:c r="S35" s="12"/>
-      <x:c r="T35" s="12"/>
-      <x:c r="U35" s="12" t="str">
+      <x:c r="N35" s="12" t="str">
+        <x:v>Essentials</x:v>
+      </x:c>
+      <x:c r="O35" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P35" s="12" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q35" s="12" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="R35" s="12" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="S35" s="12" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="T35" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="U35" s="12" t="n">
         <x:f>IF(COUNTA(O35:T35)=0,"",SUM(O35:T35))</x:f>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="V35" s="12" t="str">
         <x:f>IF(U35="","",IF(U35&gt;=95,"Exceptionnel",IF(U35&gt;=90,"Excellent",IF(U35&gt;=85,"Très bon",IF(U35&gt;=80,"Bon",IF(U35&gt;=70,"Correct","À revoir"))))))</x:f>
-      </x:c>
-      <x:c r="W35" s="12"/>
-      <x:c r="X35" s="12"/>
+        <x:v>Très bon</x:v>
+      </x:c>
+      <x:c r="W35" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="X35" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
       <x:c r="Y35" s="12"/>
-      <x:c r="Z35" s="12"/>
-      <x:c r="AA35" s="12"/>
-      <x:c r="AB35" s="12"/>
-      <x:c r="AC35" s="12"/>
-      <x:c r="AD35" s="12"/>
-      <x:c r="AE35" s="38"/>
-      <x:c r="AF35" s="40"/>
-      <x:c r="AG35" s="12"/>
-      <x:c r="AH35" s="12"/>
-      <x:c r="AI35" s="12"/>
+      <x:c r="Z35" s="12" t="str">
+        <x:v>Une barre olympique accessible et polyvalente, intéressante pour équiper un premier home gym avec des disques de 50 mm.</x:v>
+      </x:c>
+      <x:c r="AA35" s="12" t="str">
+        <x:v>Bon rapport qualité/prix | Longueur standard 220 cm | Compatible disques 50 mm | Charge annoncée 320 kg | Polyvalente</x:v>
+      </x:c>
+      <x:c r="AB35" s="12" t="str">
+        <x:v>Finitions plus simples | Informations techniques moins détaillées | Moins spécialisée qu’une vraie power bar</x:v>
+      </x:c>
+      <x:c r="AC35" s="12" t="str">
+        <x:v>Débutant à intermédiaire recherchant une barre olympique polyvalente</x:v>
+      </x:c>
+      <x:c r="AD35" s="12" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="AE35" s="38" t="n">
+        <x:v>4.6</x:v>
+      </x:c>
+      <x:c r="AF35" s="55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="AG35" s="12" t="str">
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH35" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0CWFD1FKH</x:v>
+      </x:c>
+      <x:c r="AI35" s="12" t="str">
+        <x:v>ASIN, note Amazon 4,6/5 et 82 évaluations vérifiés le 05/08/2026. Longueur 220 cm, manchons 50 mm et charge maximale annoncée 320 kg confirmés sur Amazon FR.</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="12"/>
-      <x:c r="B36" s="12"/>
-      <x:c r="C36" s="12"/>
-      <x:c r="D36" s="12"/>
-      <x:c r="E36" s="12"/>
-      <x:c r="F36" s="12"/>
-      <x:c r="G36" s="12"/>
-      <x:c r="H36" s="12"/>
-      <x:c r="I36" s="12"/>
+      <x:c r="A36" s="12" t="str">
+        <x:v>MG-BARRE-003</x:v>
+      </x:c>
+      <x:c r="B36" s="12" t="str">
+        <x:v>Barre olympique</x:v>
+      </x:c>
+      <x:c r="C36" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D36" s="12" t="str">
+        <x:v>Premium</x:v>
+      </x:c>
+      <x:c r="E36" s="12" t="str">
+        <x:v>GORILLA SPORTS Barre olympique longue 220 cm</x:v>
+      </x:c>
+      <x:c r="F36" s="12" t="str">
+        <x:v>GORILLA SPORTS</x:v>
+      </x:c>
+      <x:c r="G36" s="12" t="str">
+        <x:v>20 kg — 220 cm — disques 50 mm — charge maximale annoncée 680 kg</x:v>
+      </x:c>
+      <x:c r="H36" s="12" t="str">
+        <x:v>B07PYJKJFY</x:v>
+      </x:c>
+      <x:c r="I36" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B07PYJKJFY</x:v>
+      </x:c>
       <x:c r="J36" s="12"/>
       <x:c r="K36" s="12" t="str">
         <x:f>IF(OR(H36="",J36=""),"", "https://www.amazon.fr/dp/"&amp;H36&amp;"?tag="&amp;J36)</x:f>
       </x:c>
       <x:c r="L36" s="12"/>
       <x:c r="M36" s="36"/>
-      <x:c r="N36" s="12"/>
-      <x:c r="O36" s="12"/>
-      <x:c r="P36" s="12"/>
-      <x:c r="Q36" s="12"/>
-      <x:c r="R36" s="12"/>
-      <x:c r="S36" s="12"/>
-      <x:c r="T36" s="12"/>
-      <x:c r="U36" s="12" t="str">
+      <x:c r="N36" s="12" t="str">
+        <x:v>Elite</x:v>
+      </x:c>
+      <x:c r="O36" s="12" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P36" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="Q36" s="12" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="R36" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="S36" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="T36" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="U36" s="12" t="n">
         <x:f>IF(COUNTA(O36:T36)=0,"",SUM(O36:T36))</x:f>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="V36" s="12" t="str">
         <x:f>IF(U36="","",IF(U36&gt;=95,"Exceptionnel",IF(U36&gt;=90,"Excellent",IF(U36&gt;=85,"Très bon",IF(U36&gt;=80,"Bon",IF(U36&gt;=70,"Correct","À revoir"))))))</x:f>
+        <x:v>Très bon</x:v>
       </x:c>
       <x:c r="W36" s="12"/>
-      <x:c r="X36" s="12"/>
-      <x:c r="Y36" s="12"/>
-      <x:c r="Z36" s="12"/>
-      <x:c r="AA36" s="12"/>
-      <x:c r="AB36" s="12"/>
-      <x:c r="AC36" s="12"/>
+      <x:c r="X36" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="Y36" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="Z36" s="12" t="str">
+        <x:v>Une barre très robuste destinée aux charges lourdes, avec un standard olympique de 50 mm et une capacité annoncée particulièrement élevée.</x:v>
+      </x:c>
+      <x:c r="AA36" s="12" t="str">
+        <x:v>Poids standard 20 kg | Longueur 220 cm | Charge annoncée 680 kg | Manchons 50 mm | Roulement pivotant et poignées moletées</x:v>
+      </x:c>
+      <x:c r="AB36" s="12" t="str">
+        <x:v>Prix plus élevé | Données d’avis variables selon la déclinaison | Moletage et rigidité potentiellement excessifs pour un débutant</x:v>
+      </x:c>
+      <x:c r="AC36" s="12" t="str">
+        <x:v>Confirmé recherchant une barre robuste pour progresser sur les mouvements lourds</x:v>
+      </x:c>
       <x:c r="AD36" s="12"/>
       <x:c r="AE36" s="38"/>
-      <x:c r="AF36" s="40"/>
-      <x:c r="AG36" s="12"/>
-      <x:c r="AH36" s="12"/>
-      <x:c r="AI36" s="12"/>
+      <x:c r="AF36" s="55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="AG36" s="12" t="str">
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH36" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B07PYJKJFY</x:v>
+      </x:c>
+      <x:c r="AI36" s="12" t="str">
+        <x:v>ASIN et caractéristiques vérifiés le 05/08/2026. Amazon FR annonce 20 kg, 220 cm, manchons 50 mm et charge maximale 680 kg. Note et nombre d’avis laissés vides car les valeurs affichées varient selon la déclinaison.</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="12"/>
@@ -13565,7 +13737,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R013c85eea3404df4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c9c29d655b84855"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16075,37 +16247,37 @@
       </x:c>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="12" t="n">
+      <x:c r="A34" s="12" t="str">
         <x:f>Produits!A34</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B34" s="12" t="n">
+        <x:v>MG-BARRE-001</x:v>
+      </x:c>
+      <x:c r="B34" s="12" t="str">
         <x:f>Produits!B34</x:f>
-        <x:v>0</x:v>
+        <x:v>Barre olympique</x:v>
       </x:c>
       <x:c r="C34" s="12" t="n">
         <x:f>Produits!C34</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D34" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D34" s="12" t="str">
         <x:f>Produits!D34</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E34" s="12" t="n">
+        <x:v>Choix MuscuGuide</x:v>
+      </x:c>
+      <x:c r="E34" s="12" t="str">
         <x:f>Produits!E34</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F34" s="12" t="n">
+        <x:v>Strength Shop Original 2029 Power Bar</x:v>
+      </x:c>
+      <x:c r="F34" s="12" t="str">
         <x:f>Produits!F34</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G34" s="12" t="n">
+        <x:v>Strength Shop</x:v>
+      </x:c>
+      <x:c r="G34" s="12" t="str">
         <x:f>Produits!H34</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H34" s="12" t="n">
+        <x:v>B0CLT8NFSW</x:v>
+      </x:c>
+      <x:c r="H34" s="12" t="str">
         <x:f>Produits!I34</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B0CLT8NFSW</x:v>
       </x:c>
       <x:c r="I34" s="12" t="n">
         <x:f>Produits!K34</x:f>
@@ -16117,65 +16289,65 @@
       </x:c>
       <x:c r="K34" s="12" t="n">
         <x:f>Produits!U34</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L34" s="12" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="L34" s="12" t="str">
         <x:f>Produits!V34</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M34" s="12" t="n">
+        <x:v>Excellent</x:v>
+      </x:c>
+      <x:c r="M34" s="12" t="str">
         <x:f>Produits!Z34</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N34" s="12" t="n">
+        <x:v>Une barre de force sérieuse et bien équilibrée pour le squat, le développé couché et le soulevé de terre dans un home gym exigeant.</x:v>
+      </x:c>
+      <x:c r="N34" s="12" t="str">
         <x:f>Produits!AA34</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O34" s="12" t="n">
+        <x:v>Standard 20 kg et 220 cm | Axe 29 mm typé powerlifting | Moletage central | Bagues en bronze | Revêtement E-Coat résistant</x:v>
+      </x:c>
+      <x:c r="O34" s="12" t="str">
         <x:f>Produits!AB34</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P34" s="12" t="n">
+        <x:v>Charge conseillée de 260 kg | Moletage assez agressif | Moins adaptée à l’haltérophilie olympique dynamique</x:v>
+      </x:c>
+      <x:c r="P34" s="12" t="str">
         <x:f>Produits!AC34</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q34" s="12" t="n">
+        <x:v>Intermédiaire à confirmé orienté powerlifting et mouvements de force</x:v>
+      </x:c>
+      <x:c r="Q34" s="12" t="str">
         <x:f>Produits!AG34</x:f>
-        <x:v>0</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="12" t="n">
+      <x:c r="A35" s="12" t="str">
         <x:f>Produits!A35</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B35" s="12" t="n">
+        <x:v>MG-BARRE-002</x:v>
+      </x:c>
+      <x:c r="B35" s="12" t="str">
         <x:f>Produits!B35</x:f>
-        <x:v>0</x:v>
+        <x:v>Barre olympique</x:v>
       </x:c>
       <x:c r="C35" s="12" t="n">
         <x:f>Produits!C35</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D35" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D35" s="12" t="str">
         <x:f>Produits!D35</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E35" s="12" t="n">
+        <x:v>Meilleur rapport qualité/prix</x:v>
+      </x:c>
+      <x:c r="E35" s="12" t="str">
         <x:f>Produits!E35</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F35" s="12" t="n">
+        <x:v>DIAMOND Barre olympique Power Training 220 cm</x:v>
+      </x:c>
+      <x:c r="F35" s="12" t="str">
         <x:f>Produits!F35</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G35" s="12" t="n">
+        <x:v>DIAMOND</x:v>
+      </x:c>
+      <x:c r="G35" s="12" t="str">
         <x:f>Produits!H35</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H35" s="12" t="n">
+        <x:v>B0CWFD1FKH</x:v>
+      </x:c>
+      <x:c r="H35" s="12" t="str">
         <x:f>Produits!I35</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B0CWFD1FKH</x:v>
       </x:c>
       <x:c r="I35" s="12" t="n">
         <x:f>Produits!K35</x:f>
@@ -16187,65 +16359,65 @@
       </x:c>
       <x:c r="K35" s="12" t="n">
         <x:f>Produits!U35</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L35" s="12" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="L35" s="12" t="str">
         <x:f>Produits!V35</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M35" s="12" t="n">
+        <x:v>Très bon</x:v>
+      </x:c>
+      <x:c r="M35" s="12" t="str">
         <x:f>Produits!Z35</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N35" s="12" t="n">
+        <x:v>Une barre olympique accessible et polyvalente, intéressante pour équiper un premier home gym avec des disques de 50 mm.</x:v>
+      </x:c>
+      <x:c r="N35" s="12" t="str">
         <x:f>Produits!AA35</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O35" s="12" t="n">
+        <x:v>Bon rapport qualité/prix | Longueur standard 220 cm | Compatible disques 50 mm | Charge annoncée 320 kg | Polyvalente</x:v>
+      </x:c>
+      <x:c r="O35" s="12" t="str">
         <x:f>Produits!AB35</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P35" s="12" t="n">
+        <x:v>Finitions plus simples | Informations techniques moins détaillées | Moins spécialisée qu’une vraie power bar</x:v>
+      </x:c>
+      <x:c r="P35" s="12" t="str">
         <x:f>Produits!AC35</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q35" s="12" t="n">
+        <x:v>Débutant à intermédiaire recherchant une barre olympique polyvalente</x:v>
+      </x:c>
+      <x:c r="Q35" s="12" t="str">
         <x:f>Produits!AG35</x:f>
-        <x:v>0</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="12" t="n">
+      <x:c r="A36" s="12" t="str">
         <x:f>Produits!A36</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B36" s="12" t="n">
+        <x:v>MG-BARRE-003</x:v>
+      </x:c>
+      <x:c r="B36" s="12" t="str">
         <x:f>Produits!B36</x:f>
-        <x:v>0</x:v>
+        <x:v>Barre olympique</x:v>
       </x:c>
       <x:c r="C36" s="12" t="n">
         <x:f>Produits!C36</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D36" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D36" s="12" t="str">
         <x:f>Produits!D36</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E36" s="12" t="n">
+        <x:v>Premium</x:v>
+      </x:c>
+      <x:c r="E36" s="12" t="str">
         <x:f>Produits!E36</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F36" s="12" t="n">
+        <x:v>GORILLA SPORTS Barre olympique longue 220 cm</x:v>
+      </x:c>
+      <x:c r="F36" s="12" t="str">
         <x:f>Produits!F36</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G36" s="12" t="n">
+        <x:v>GORILLA SPORTS</x:v>
+      </x:c>
+      <x:c r="G36" s="12" t="str">
         <x:f>Produits!H36</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H36" s="12" t="n">
+        <x:v>B07PYJKJFY</x:v>
+      </x:c>
+      <x:c r="H36" s="12" t="str">
         <x:f>Produits!I36</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B07PYJKJFY</x:v>
       </x:c>
       <x:c r="I36" s="12" t="n">
         <x:f>Produits!K36</x:f>
@@ -16257,31 +16429,31 @@
       </x:c>
       <x:c r="K36" s="12" t="n">
         <x:f>Produits!U36</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L36" s="12" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="L36" s="12" t="str">
         <x:f>Produits!V36</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M36" s="12" t="n">
+        <x:v>Très bon</x:v>
+      </x:c>
+      <x:c r="M36" s="12" t="str">
         <x:f>Produits!Z36</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N36" s="12" t="n">
+        <x:v>Une barre très robuste destinée aux charges lourdes, avec un standard olympique de 50 mm et une capacité annoncée particulièrement élevée.</x:v>
+      </x:c>
+      <x:c r="N36" s="12" t="str">
         <x:f>Produits!AA36</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O36" s="12" t="n">
+        <x:v>Poids standard 20 kg | Longueur 220 cm | Charge annoncée 680 kg | Manchons 50 mm | Roulement pivotant et poignées moletées</x:v>
+      </x:c>
+      <x:c r="O36" s="12" t="str">
         <x:f>Produits!AB36</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P36" s="12" t="n">
+        <x:v>Prix plus élevé | Données d’avis variables selon la déclinaison | Moletage et rigidité potentiellement excessifs pour un débutant</x:v>
+      </x:c>
+      <x:c r="P36" s="12" t="str">
         <x:f>Produits!AC36</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q36" s="12" t="n">
+        <x:v>Confirmé recherchant une barre robuste pour progresser sur les mouvements lourds</x:v>
+      </x:c>
+      <x:c r="Q36" s="12" t="str">
         <x:f>Produits!AG36</x:f>
-        <x:v>0</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="37">

--- a/data/import/MuscuGuide_Base_Produits.xlsx
+++ b/data/import/MuscuGuide_Base_Produits.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R7fe4e726a84d4ecc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produits" sheetId="2" r:id="R7b5f62162fe34974"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notation" sheetId="3" r:id="R9cec57baca004427"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Claude" sheetId="4" r:id="R93688208b42f417f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="5" r:id="Rc34668e0f1974ff9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="6" r:id="R90f8366475ec45f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Re3a09d93d4f94b04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produits" sheetId="2" r:id="R4e3c4196cca148c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notation" sheetId="3" r:id="Rae2c657b2ee64e14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Claude" sheetId="4" r:id="R7ff59f63b1bc4820"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="5" r:id="R00f7979a1bfe47ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="6" r:id="R76ad8f9768994f14"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -435,7 +435,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4c1b41b7f9d243ce"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc938825c9b0f437b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -687,7 +687,7 @@
       </x:c>
       <x:c r="B4" s="12" t="n">
         <x:f>COUNTA(Produits!E4:E250)</x:f>
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C4" s="12"/>
       <x:c r="D4" s="12" t="str">
@@ -747,7 +747,7 @@
       </x:c>
       <x:c r="B6" s="12" t="n">
         <x:f>COUNTIF(Produits!AG4:AG250,"Validé")</x:f>
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C6" s="12"/>
       <x:c r="D6" s="12" t="str">
@@ -807,7 +807,7 @@
       </x:c>
       <x:c r="B8" s="38" t="n">
         <x:f>IFERROR(AVERAGE(Produits!U4:U250),0)</x:f>
-        <x:v>89</x:v>
+        <x:v>89.25</x:v>
       </x:c>
       <x:c r="C8" s="12"/>
       <x:c r="D8" s="12" t="str">
@@ -1013,7 +1013,7 @@
       </x:c>
       <x:c r="E15" s="12" t="n">
         <x:f>COUNTIF(Produits!B:B,D15)</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F15" s="12" t="n">
         <x:f>COUNTIFS(Produits!B:B,D15,Produits!H:H,"??????????")</x:f>
@@ -1021,7 +1021,7 @@
       </x:c>
       <x:c r="G15" s="12" t="n">
         <x:f>COUNTIFS(Produits!B:B,D15,Produits!AG:AG,"Validé")</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H15" s="46" t="n">
         <x:f>IFERROR(F15/E15,0)</x:f>
@@ -1259,7 +1259,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1299c99b45ce4653"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60461de78beb45da"/>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -4466,133 +4466,309 @@
       </x:c>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="12"/>
-      <x:c r="B37" s="12"/>
-      <x:c r="C37" s="12"/>
-      <x:c r="D37" s="12"/>
-      <x:c r="E37" s="12"/>
-      <x:c r="F37" s="12"/>
-      <x:c r="G37" s="12"/>
-      <x:c r="H37" s="12"/>
-      <x:c r="I37" s="12"/>
+      <x:c r="A37" s="12" t="str">
+        <x:v>MG-KETT-001</x:v>
+      </x:c>
+      <x:c r="B37" s="12" t="str">
+        <x:v>Kettlebells</x:v>
+      </x:c>
+      <x:c r="C37" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D37" s="12" t="str">
+        <x:v>Choix MuscuGuide</x:v>
+      </x:c>
+      <x:c r="E37" s="12" t="str">
+        <x:v>PROIRON Kettlebell 12 kg en néoprène</x:v>
+      </x:c>
+      <x:c r="F37" s="12" t="str">
+        <x:v>PROIRON</x:v>
+      </x:c>
+      <x:c r="G37" s="12" t="str">
+        <x:v>12 kg — fonte monobloc — revêtement néoprène — poignée large</x:v>
+      </x:c>
+      <x:c r="H37" s="12" t="str">
+        <x:v>B09T9MY8L3</x:v>
+      </x:c>
+      <x:c r="I37" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B09T9MY8L3</x:v>
+      </x:c>
       <x:c r="J37" s="12"/>
       <x:c r="K37" s="12" t="str">
         <x:f>IF(OR(H37="",J37=""),"", "https://www.amazon.fr/dp/"&amp;H37&amp;"?tag="&amp;J37)</x:f>
       </x:c>
       <x:c r="L37" s="12"/>
       <x:c r="M37" s="36"/>
-      <x:c r="N37" s="12"/>
-      <x:c r="O37" s="12"/>
-      <x:c r="P37" s="12"/>
-      <x:c r="Q37" s="12"/>
-      <x:c r="R37" s="12"/>
-      <x:c r="S37" s="12"/>
-      <x:c r="T37" s="12"/>
-      <x:c r="U37" s="12" t="str">
+      <x:c r="N37" s="12" t="str">
+        <x:v>Performance</x:v>
+      </x:c>
+      <x:c r="O37" s="12" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P37" s="12" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="Q37" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="R37" s="12" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="S37" s="12" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="T37" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="U37" s="12" t="n">
         <x:f>IF(COUNTA(O37:T37)=0,"",SUM(O37:T37))</x:f>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="V37" s="12" t="str">
         <x:f>IF(U37="","",IF(U37&gt;=95,"Exceptionnel",IF(U37&gt;=90,"Excellent",IF(U37&gt;=85,"Très bon",IF(U37&gt;=80,"Bon",IF(U37&gt;=70,"Correct","À revoir"))))))</x:f>
-      </x:c>
-      <x:c r="W37" s="12"/>
-      <x:c r="X37" s="12"/>
-      <x:c r="Y37" s="12"/>
-      <x:c r="Z37" s="12"/>
-      <x:c r="AA37" s="12"/>
-      <x:c r="AB37" s="12"/>
-      <x:c r="AC37" s="12"/>
-      <x:c r="AD37" s="12"/>
-      <x:c r="AE37" s="38"/>
-      <x:c r="AF37" s="40"/>
-      <x:c r="AG37" s="12"/>
-      <x:c r="AH37" s="12"/>
-      <x:c r="AI37" s="12"/>
+        <x:v>Excellent</x:v>
+      </x:c>
+      <x:c r="W37" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="X37" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="Y37" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="Z37" s="12" t="str">
+        <x:v>Une kettlebell polyvalente et bien finie pour progresser sur les swings, squats et exercices de renforcement à domicile.</x:v>
+      </x:c>
+      <x:c r="AA37" s="12" t="str">
+        <x:v>Fonte monobloc | Revêtement néoprène protecteur | Poignée large | Note Amazon élevée | Format 12 kg polyvalent</x:v>
+      </x:c>
+      <x:c r="AB37" s="12" t="str">
+        <x:v>Poids fixe | Moins adaptée aux grands débutants | Le néoprène peut s’user avec un usage très intensif</x:v>
+      </x:c>
+      <x:c r="AC37" s="12" t="str">
+        <x:v>Débutant à intermédiaire recherchant une kettlebell polyvalente pour le home gym</x:v>
+      </x:c>
+      <x:c r="AD37" s="12" t="n">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="AE37" s="38" t="n">
+        <x:v>4.8</x:v>
+      </x:c>
+      <x:c r="AF37" s="55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="AG37" s="12" t="str">
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH37" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B09T9MY8L3</x:v>
+      </x:c>
+      <x:c r="AI37" s="12" t="str">
+        <x:v>ASIN, poids de 12 kg, matière néoprène, note Amazon 4,8/5 et 116 commentaires vérifiés le 05/08/2026.</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="12"/>
-      <x:c r="B38" s="12"/>
-      <x:c r="C38" s="12"/>
-      <x:c r="D38" s="12"/>
-      <x:c r="E38" s="12"/>
-      <x:c r="F38" s="12"/>
-      <x:c r="G38" s="12"/>
-      <x:c r="H38" s="12"/>
-      <x:c r="I38" s="12"/>
+      <x:c r="A38" s="12" t="str">
+        <x:v>MG-KETT-002</x:v>
+      </x:c>
+      <x:c r="B38" s="12" t="str">
+        <x:v>Kettlebells</x:v>
+      </x:c>
+      <x:c r="C38" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D38" s="12" t="str">
+        <x:v>Meilleur rapport qualité/prix</x:v>
+      </x:c>
+      <x:c r="E38" s="12" t="str">
+        <x:v>Yes4All Kettlebell en fonte avec revêtement poudre</x:v>
+      </x:c>
+      <x:c r="F38" s="12" t="str">
+        <x:v>Yes4All</x:v>
+      </x:c>
+      <x:c r="G38" s="12" t="str">
+        <x:v>Gamme 4 à 32 kg — fonte monobloc — poignée large</x:v>
+      </x:c>
+      <x:c r="H38" s="12" t="str">
+        <x:v>B0DNK2V1WR</x:v>
+      </x:c>
+      <x:c r="I38" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0DNK2V1WR</x:v>
+      </x:c>
       <x:c r="J38" s="12"/>
       <x:c r="K38" s="12" t="str">
         <x:f>IF(OR(H38="",J38=""),"", "https://www.amazon.fr/dp/"&amp;H38&amp;"?tag="&amp;J38)</x:f>
       </x:c>
       <x:c r="L38" s="12"/>
       <x:c r="M38" s="36"/>
-      <x:c r="N38" s="12"/>
-      <x:c r="O38" s="12"/>
-      <x:c r="P38" s="12"/>
-      <x:c r="Q38" s="12"/>
-      <x:c r="R38" s="12"/>
-      <x:c r="S38" s="12"/>
-      <x:c r="T38" s="12"/>
-      <x:c r="U38" s="12" t="str">
+      <x:c r="N38" s="12" t="str">
+        <x:v>Essentials</x:v>
+      </x:c>
+      <x:c r="O38" s="12" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P38" s="12" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q38" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="R38" s="12" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="S38" s="12" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="T38" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="U38" s="12" t="n">
         <x:f>IF(COUNTA(O38:T38)=0,"",SUM(O38:T38))</x:f>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="V38" s="12" t="str">
         <x:f>IF(U38="","",IF(U38&gt;=95,"Exceptionnel",IF(U38&gt;=90,"Excellent",IF(U38&gt;=85,"Très bon",IF(U38&gt;=80,"Bon",IF(U38&gt;=70,"Correct","À revoir"))))))</x:f>
-      </x:c>
-      <x:c r="W38" s="12"/>
-      <x:c r="X38" s="12"/>
+        <x:v>Excellent</x:v>
+      </x:c>
+      <x:c r="W38" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="X38" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
       <x:c r="Y38" s="12"/>
-      <x:c r="Z38" s="12"/>
-      <x:c r="AA38" s="12"/>
-      <x:c r="AB38" s="12"/>
-      <x:c r="AC38" s="12"/>
-      <x:c r="AD38" s="12"/>
-      <x:c r="AE38" s="38"/>
-      <x:c r="AF38" s="40"/>
-      <x:c r="AG38" s="12"/>
-      <x:c r="AH38" s="12"/>
-      <x:c r="AI38" s="12"/>
+      <x:c r="Z38" s="12" t="str">
+        <x:v>Une gamme populaire et accessible, avec de nombreux poids disponibles et une finition poudre adaptée aux entraînements réguliers.</x:v>
+      </x:c>
+      <x:c r="AA38" s="12" t="str">
+        <x:v>Très bon rapport qualité/prix | Gamme 4 à 32 kg | 4,7/5 sur plus de 4 500 évaluations | Poignée large | Fonte sans soudure</x:v>
+      </x:c>
+      <x:c r="AB38" s="12" t="str">
+        <x:v>L’ASIN correspond à une variante légère | Finition moins premium | Disponibilité variable selon le poids</x:v>
+      </x:c>
+      <x:c r="AC38" s="12" t="str">
+        <x:v>Débutant à confirmé souhaitant choisir précisément son poids</x:v>
+      </x:c>
+      <x:c r="AD38" s="12" t="n">
+        <x:v>4566</x:v>
+      </x:c>
+      <x:c r="AE38" s="38" t="n">
+        <x:v>4.7</x:v>
+      </x:c>
+      <x:c r="AF38" s="55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="AG38" s="12" t="str">
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH38" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0DNK2V1WR</x:v>
+      </x:c>
+      <x:c r="AI38" s="12" t="str">
+        <x:v>ASIN de la variante Amazon FR, note 4,7/5 et 4 566 évaluations vérifiés le 05/08/2026. La fiche produit regroupe une gamme de 4 à 32 kg.</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="12"/>
-      <x:c r="B39" s="12"/>
-      <x:c r="C39" s="12"/>
-      <x:c r="D39" s="12"/>
-      <x:c r="E39" s="12"/>
-      <x:c r="F39" s="12"/>
-      <x:c r="G39" s="12"/>
-      <x:c r="H39" s="12"/>
-      <x:c r="I39" s="12"/>
+      <x:c r="A39" s="12" t="str">
+        <x:v>MG-KETT-003</x:v>
+      </x:c>
+      <x:c r="B39" s="12" t="str">
+        <x:v>Kettlebells</x:v>
+      </x:c>
+      <x:c r="C39" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D39" s="12" t="str">
+        <x:v>Premium</x:v>
+      </x:c>
+      <x:c r="E39" s="12" t="str">
+        <x:v>Kettlebell Kings Powder Coat 8 kg</x:v>
+      </x:c>
+      <x:c r="F39" s="12" t="str">
+        <x:v>Kettlebell Kings</x:v>
+      </x:c>
+      <x:c r="G39" s="12" t="str">
+        <x:v>8 kg — fonte moulée en une pièce — finition poudre — base usinée</x:v>
+      </x:c>
+      <x:c r="H39" s="12" t="str">
+        <x:v>B017WB2OHQ</x:v>
+      </x:c>
+      <x:c r="I39" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B017WB2OHQ</x:v>
+      </x:c>
       <x:c r="J39" s="12"/>
       <x:c r="K39" s="12" t="str">
         <x:f>IF(OR(H39="",J39=""),"", "https://www.amazon.fr/dp/"&amp;H39&amp;"?tag="&amp;J39)</x:f>
       </x:c>
       <x:c r="L39" s="12"/>
       <x:c r="M39" s="36"/>
-      <x:c r="N39" s="12"/>
-      <x:c r="O39" s="12"/>
-      <x:c r="P39" s="12"/>
-      <x:c r="Q39" s="12"/>
-      <x:c r="R39" s="12"/>
-      <x:c r="S39" s="12"/>
-      <x:c r="T39" s="12"/>
-      <x:c r="U39" s="12" t="str">
+      <x:c r="N39" s="12" t="str">
+        <x:v>Elite</x:v>
+      </x:c>
+      <x:c r="O39" s="12" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="P39" s="12" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="Q39" s="12" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="R39" s="12" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="S39" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="T39" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="U39" s="12" t="n">
         <x:f>IF(COUNTA(O39:T39)=0,"",SUM(O39:T39))</x:f>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="V39" s="12" t="str">
         <x:f>IF(U39="","",IF(U39&gt;=95,"Exceptionnel",IF(U39&gt;=90,"Excellent",IF(U39&gt;=85,"Très bon",IF(U39&gt;=80,"Bon",IF(U39&gt;=70,"Correct","À revoir"))))))</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="W39" s="12"/>
-      <x:c r="X39" s="12"/>
-      <x:c r="Y39" s="12"/>
-      <x:c r="Z39" s="12"/>
-      <x:c r="AA39" s="12"/>
-      <x:c r="AB39" s="12"/>
-      <x:c r="AC39" s="12"/>
-      <x:c r="AD39" s="12"/>
-      <x:c r="AE39" s="38"/>
-      <x:c r="AF39" s="40"/>
-      <x:c r="AG39" s="12"/>
-      <x:c r="AH39" s="12"/>
-      <x:c r="AI39" s="12"/>
+      <x:c r="X39" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="Y39" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="Z39" s="12" t="str">
+        <x:v>Une kettlebell premium en fonte monobloc, conçue pour une prise fiable et une grande durabilité lors des entraînements techniques.</x:v>
+      </x:c>
+      <x:c r="AA39" s="12" t="str">
+        <x:v>Fonte moulée en une pièce | Finition poudre durable | Base plane usinée | Très bonne prise en main | Fabrication précise</x:v>
+      </x:c>
+      <x:c r="AB39" s="12" t="str">
+        <x:v>Prix plus élevé | Poids fixe de 8 kg sur cet ASIN | Disponibilité parfois limitée</x:v>
+      </x:c>
+      <x:c r="AC39" s="12" t="str">
+        <x:v>Intermédiaire à confirmé privilégiant la qualité de fabrication et la durabilité</x:v>
+      </x:c>
+      <x:c r="AD39" s="12" t="n">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="AE39" s="38" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="AF39" s="55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="AG39" s="12" t="str">
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH39" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B017WB2OHQ</x:v>
+      </x:c>
+      <x:c r="AI39" s="12" t="str">
+        <x:v>ASIN, modèle 8 kg, note Amazon 4,5/5 et 354 évaluations vérifiés le 05/08/2026. Fonte monobloc, finition poudre et base plane confirmées sur la fiche Amazon FR.</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="12"/>
@@ -13737,7 +13913,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c9c29d655b84855"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c2e6940412c4221"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16457,37 +16633,37 @@
       </x:c>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="12" t="n">
+      <x:c r="A37" s="12" t="str">
         <x:f>Produits!A37</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B37" s="12" t="n">
+        <x:v>MG-KETT-001</x:v>
+      </x:c>
+      <x:c r="B37" s="12" t="str">
         <x:f>Produits!B37</x:f>
-        <x:v>0</x:v>
+        <x:v>Kettlebells</x:v>
       </x:c>
       <x:c r="C37" s="12" t="n">
         <x:f>Produits!C37</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D37" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D37" s="12" t="str">
         <x:f>Produits!D37</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E37" s="12" t="n">
+        <x:v>Choix MuscuGuide</x:v>
+      </x:c>
+      <x:c r="E37" s="12" t="str">
         <x:f>Produits!E37</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F37" s="12" t="n">
+        <x:v>PROIRON Kettlebell 12 kg en néoprène</x:v>
+      </x:c>
+      <x:c r="F37" s="12" t="str">
         <x:f>Produits!F37</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G37" s="12" t="n">
+        <x:v>PROIRON</x:v>
+      </x:c>
+      <x:c r="G37" s="12" t="str">
         <x:f>Produits!H37</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H37" s="12" t="n">
+        <x:v>B09T9MY8L3</x:v>
+      </x:c>
+      <x:c r="H37" s="12" t="str">
         <x:f>Produits!I37</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B09T9MY8L3</x:v>
       </x:c>
       <x:c r="I37" s="12" t="n">
         <x:f>Produits!K37</x:f>
@@ -16499,65 +16675,65 @@
       </x:c>
       <x:c r="K37" s="12" t="n">
         <x:f>Produits!U37</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L37" s="12" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="L37" s="12" t="str">
         <x:f>Produits!V37</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M37" s="12" t="n">
+        <x:v>Excellent</x:v>
+      </x:c>
+      <x:c r="M37" s="12" t="str">
         <x:f>Produits!Z37</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N37" s="12" t="n">
+        <x:v>Une kettlebell polyvalente et bien finie pour progresser sur les swings, squats et exercices de renforcement à domicile.</x:v>
+      </x:c>
+      <x:c r="N37" s="12" t="str">
         <x:f>Produits!AA37</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O37" s="12" t="n">
+        <x:v>Fonte monobloc | Revêtement néoprène protecteur | Poignée large | Note Amazon élevée | Format 12 kg polyvalent</x:v>
+      </x:c>
+      <x:c r="O37" s="12" t="str">
         <x:f>Produits!AB37</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P37" s="12" t="n">
+        <x:v>Poids fixe | Moins adaptée aux grands débutants | Le néoprène peut s’user avec un usage très intensif</x:v>
+      </x:c>
+      <x:c r="P37" s="12" t="str">
         <x:f>Produits!AC37</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q37" s="12" t="n">
+        <x:v>Débutant à intermédiaire recherchant une kettlebell polyvalente pour le home gym</x:v>
+      </x:c>
+      <x:c r="Q37" s="12" t="str">
         <x:f>Produits!AG37</x:f>
-        <x:v>0</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="12" t="n">
+      <x:c r="A38" s="12" t="str">
         <x:f>Produits!A38</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B38" s="12" t="n">
+        <x:v>MG-KETT-002</x:v>
+      </x:c>
+      <x:c r="B38" s="12" t="str">
         <x:f>Produits!B38</x:f>
-        <x:v>0</x:v>
+        <x:v>Kettlebells</x:v>
       </x:c>
       <x:c r="C38" s="12" t="n">
         <x:f>Produits!C38</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D38" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D38" s="12" t="str">
         <x:f>Produits!D38</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E38" s="12" t="n">
+        <x:v>Meilleur rapport qualité/prix</x:v>
+      </x:c>
+      <x:c r="E38" s="12" t="str">
         <x:f>Produits!E38</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F38" s="12" t="n">
+        <x:v>Yes4All Kettlebell en fonte avec revêtement poudre</x:v>
+      </x:c>
+      <x:c r="F38" s="12" t="str">
         <x:f>Produits!F38</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G38" s="12" t="n">
+        <x:v>Yes4All</x:v>
+      </x:c>
+      <x:c r="G38" s="12" t="str">
         <x:f>Produits!H38</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H38" s="12" t="n">
+        <x:v>B0DNK2V1WR</x:v>
+      </x:c>
+      <x:c r="H38" s="12" t="str">
         <x:f>Produits!I38</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B0DNK2V1WR</x:v>
       </x:c>
       <x:c r="I38" s="12" t="n">
         <x:f>Produits!K38</x:f>
@@ -16569,65 +16745,65 @@
       </x:c>
       <x:c r="K38" s="12" t="n">
         <x:f>Produits!U38</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L38" s="12" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="L38" s="12" t="str">
         <x:f>Produits!V38</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M38" s="12" t="n">
+        <x:v>Excellent</x:v>
+      </x:c>
+      <x:c r="M38" s="12" t="str">
         <x:f>Produits!Z38</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N38" s="12" t="n">
+        <x:v>Une gamme populaire et accessible, avec de nombreux poids disponibles et une finition poudre adaptée aux entraînements réguliers.</x:v>
+      </x:c>
+      <x:c r="N38" s="12" t="str">
         <x:f>Produits!AA38</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O38" s="12" t="n">
+        <x:v>Très bon rapport qualité/prix | Gamme 4 à 32 kg | 4,7/5 sur plus de 4 500 évaluations | Poignée large | Fonte sans soudure</x:v>
+      </x:c>
+      <x:c r="O38" s="12" t="str">
         <x:f>Produits!AB38</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P38" s="12" t="n">
+        <x:v>L’ASIN correspond à une variante légère | Finition moins premium | Disponibilité variable selon le poids</x:v>
+      </x:c>
+      <x:c r="P38" s="12" t="str">
         <x:f>Produits!AC38</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q38" s="12" t="n">
+        <x:v>Débutant à confirmé souhaitant choisir précisément son poids</x:v>
+      </x:c>
+      <x:c r="Q38" s="12" t="str">
         <x:f>Produits!AG38</x:f>
-        <x:v>0</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="12" t="n">
+      <x:c r="A39" s="12" t="str">
         <x:f>Produits!A39</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B39" s="12" t="n">
+        <x:v>MG-KETT-003</x:v>
+      </x:c>
+      <x:c r="B39" s="12" t="str">
         <x:f>Produits!B39</x:f>
-        <x:v>0</x:v>
+        <x:v>Kettlebells</x:v>
       </x:c>
       <x:c r="C39" s="12" t="n">
         <x:f>Produits!C39</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D39" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D39" s="12" t="str">
         <x:f>Produits!D39</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E39" s="12" t="n">
+        <x:v>Premium</x:v>
+      </x:c>
+      <x:c r="E39" s="12" t="str">
         <x:f>Produits!E39</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F39" s="12" t="n">
+        <x:v>Kettlebell Kings Powder Coat 8 kg</x:v>
+      </x:c>
+      <x:c r="F39" s="12" t="str">
         <x:f>Produits!F39</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G39" s="12" t="n">
+        <x:v>Kettlebell Kings</x:v>
+      </x:c>
+      <x:c r="G39" s="12" t="str">
         <x:f>Produits!H39</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H39" s="12" t="n">
+        <x:v>B017WB2OHQ</x:v>
+      </x:c>
+      <x:c r="H39" s="12" t="str">
         <x:f>Produits!I39</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B017WB2OHQ</x:v>
       </x:c>
       <x:c r="I39" s="12" t="n">
         <x:f>Produits!K39</x:f>
@@ -16639,31 +16815,31 @@
       </x:c>
       <x:c r="K39" s="12" t="n">
         <x:f>Produits!U39</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L39" s="12" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="L39" s="12" t="str">
         <x:f>Produits!V39</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M39" s="12" t="n">
+        <x:v>Excellent</x:v>
+      </x:c>
+      <x:c r="M39" s="12" t="str">
         <x:f>Produits!Z39</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N39" s="12" t="n">
+        <x:v>Une kettlebell premium en fonte monobloc, conçue pour une prise fiable et une grande durabilité lors des entraînements techniques.</x:v>
+      </x:c>
+      <x:c r="N39" s="12" t="str">
         <x:f>Produits!AA39</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O39" s="12" t="n">
+        <x:v>Fonte moulée en une pièce | Finition poudre durable | Base plane usinée | Très bonne prise en main | Fabrication précise</x:v>
+      </x:c>
+      <x:c r="O39" s="12" t="str">
         <x:f>Produits!AB39</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P39" s="12" t="n">
+        <x:v>Prix plus élevé | Poids fixe de 8 kg sur cet ASIN | Disponibilité parfois limitée</x:v>
+      </x:c>
+      <x:c r="P39" s="12" t="str">
         <x:f>Produits!AC39</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q39" s="12" t="n">
+        <x:v>Intermédiaire à confirmé privilégiant la qualité de fabrication et la durabilité</x:v>
+      </x:c>
+      <x:c r="Q39" s="12" t="str">
         <x:f>Produits!AG39</x:f>
-        <x:v>0</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="40">

--- a/data/import/MuscuGuide_Base_Produits.xlsx
+++ b/data/import/MuscuGuide_Base_Produits.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Re3a09d93d4f94b04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produits" sheetId="2" r:id="R4e3c4196cca148c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notation" sheetId="3" r:id="Rae2c657b2ee64e14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Claude" sheetId="4" r:id="R7ff59f63b1bc4820"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="5" r:id="R00f7979a1bfe47ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="6" r:id="R76ad8f9768994f14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R539c652a54024d3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produits" sheetId="2" r:id="R64f6e295511b429a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notation" sheetId="3" r:id="Rdc3186bfebd043f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Claude" sheetId="4" r:id="Rdc2e9e86ec46411d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="5" r:id="Ra4b4f8a93f0d4617"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="6" r:id="Rb1b39ccfcf3c44d9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -435,7 +435,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc938825c9b0f437b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R49611829e2f44a32"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -747,7 +747,7 @@
       </x:c>
       <x:c r="B6" s="12" t="n">
         <x:f>COUNTIF(Produits!AG4:AG250,"Validé")</x:f>
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C6" s="12"/>
       <x:c r="D6" s="12" t="str">
@@ -777,7 +777,7 @@
       </x:c>
       <x:c r="B7" s="12" t="n">
         <x:f>COUNTIF(Produits!AG4:AG250,"À rechercher")</x:f>
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C7" s="12"/>
       <x:c r="D7" s="12" t="str">
@@ -807,7 +807,7 @@
       </x:c>
       <x:c r="B8" s="38" t="n">
         <x:f>IFERROR(AVERAGE(Produits!U4:U250),0)</x:f>
-        <x:v>89.25</x:v>
+        <x:v>89.33333333333333</x:v>
       </x:c>
       <x:c r="C8" s="12"/>
       <x:c r="D8" s="12" t="str">
@@ -1208,7 +1208,7 @@
       </x:c>
       <x:c r="G22" s="12" t="n">
         <x:f>COUNTIFS(Produits!B:B,D22,Produits!AG:AG,"Validé")</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H22" s="46" t="n">
         <x:f>IFERROR(F22/E22,0)</x:f>
@@ -1259,7 +1259,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60461de78beb45da"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49a2e06aea0545b2"/>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -3345,14 +3345,20 @@
         <x:v>Choix MuscuGuide</x:v>
       </x:c>
       <x:c r="E25" s="12" t="str">
-        <x:v>KS300</x:v>
+        <x:v>Sportstech KS350</x:v>
       </x:c>
       <x:c r="F25" s="12" t="str">
         <x:v>Sportstech</x:v>
       </x:c>
-      <x:c r="G25" s="12" t="str"/>
-      <x:c r="H25" s="12" t="str"/>
-      <x:c r="I25" s="12" t="str"/>
+      <x:c r="G25" s="12" t="str">
+        <x:v>Barre murale pliable — 3 prises — 3 œillets — charge utilisateur jusqu’à 150 kg</x:v>
+      </x:c>
+      <x:c r="H25" s="12" t="str">
+        <x:v>B0843FTZ9T</x:v>
+      </x:c>
+      <x:c r="I25" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0843FTZ9T</x:v>
+      </x:c>
       <x:c r="J25" s="12" t="str"/>
       <x:c r="K25" s="12" t="str">
         <x:f>IF(OR(H25="",J25=""),"", "https://www.amazon.fr/dp/"&amp;H25&amp;"?tag="&amp;J25)</x:f>
@@ -3362,17 +3368,31 @@
       <x:c r="N25" s="12" t="str">
         <x:v>Performance</x:v>
       </x:c>
-      <x:c r="O25" s="12" t="str"/>
-      <x:c r="P25" s="12" t="str"/>
-      <x:c r="Q25" s="12" t="str"/>
-      <x:c r="R25" s="12" t="str"/>
-      <x:c r="S25" s="12" t="str"/>
-      <x:c r="T25" s="12" t="str"/>
-      <x:c r="U25" s="12" t="str">
+      <x:c r="O25" s="12" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="P25" s="12" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Q25" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="R25" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="S25" s="12" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="T25" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="U25" s="12" t="n">
         <x:f>IF(COUNTA(O25:T25)=0,"",SUM(O25:T25))</x:f>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="V25" s="12" t="str">
         <x:f>IF(U25="","",IF(U25&gt;=95,"Exceptionnel",IF(U25&gt;=90,"Excellent",IF(U25&gt;=85,"Très bon",IF(U25&gt;=80,"Bon",IF(U25&gt;=70,"Correct","À revoir"))))))</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="W25" s="12" t="str">
         <x:v>Oui</x:v>
@@ -3384,26 +3404,30 @@
         <x:v>Oui</x:v>
       </x:c>
       <x:c r="Z25" s="12" t="str">
-        <x:v>Barre polyvalente pour entraînement du haut du corps.</x:v>
+        <x:v>Une barre murale pliable, stable et polyvalente, particulièrement adaptée à un home gym compact.</x:v>
       </x:c>
       <x:c r="AA25" s="12" t="str">
-        <x:v>Multiprises | Polyvalence | Marque connue</x:v>
+        <x:v>Structure acier triangulaire | Pliable jusqu’à 26 cm | 3 positions de prise | 3 œillets d’entraînement | Kit de fixation inclus</x:v>
       </x:c>
       <x:c r="AB25" s="12" t="str">
-        <x:v>Compatibilité porte à vérifier</x:v>
+        <x:v>Perçage obligatoire | Mur solide indispensable | Moins mobile qu’un modèle de porte</x:v>
       </x:c>
       <x:c r="AC25" s="12" t="str">
-        <x:v>Home gym</x:v>
-      </x:c>
-      <x:c r="AD25" s="12" t="str"/>
-      <x:c r="AE25" s="38" t="str"/>
-      <x:c r="AF25" s="40" t="str"/>
+        <x:v>Débutant à confirmé recherchant une barre murale complète et peu encombrante</x:v>
+      </x:c>
+      <x:c r="AD25" s="12"/>
+      <x:c r="AE25" s="38"/>
+      <x:c r="AF25" s="55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
       <x:c r="AG25" s="12" t="str">
-        <x:v>À rechercher</x:v>
-      </x:c>
-      <x:c r="AH25" s="12" t="str"/>
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH25" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0843FTZ9T</x:v>
+      </x:c>
       <x:c r="AI25" s="12" t="str">
-        <x:v>Vérifier version exacte.</x:v>
+        <x:v>ASIN Amazon FR vérifié le 05/08/2026. Sportstech confirme une structure acier, 3 prises, 3 œillets, un pliage à 26 cm et une charge utilisateur jusqu’à 150 kg. Note Amazon laissée vide faute de valeur FR suffisamment fiable.</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -3420,14 +3444,20 @@
         <x:v>Meilleur rapport qualité/prix</x:v>
       </x:c>
       <x:c r="E26" s="12" t="str">
-        <x:v>Wall Mounted Pull-Up Bar</x:v>
+        <x:v>ONETWOFIT OT103</x:v>
       </x:c>
       <x:c r="F26" s="12" t="str">
         <x:v>ONETWOFIT</x:v>
       </x:c>
-      <x:c r="G26" s="12" t="str"/>
-      <x:c r="H26" s="12" t="str"/>
-      <x:c r="I26" s="12" t="str"/>
+      <x:c r="G26" s="12" t="str">
+        <x:v>Barre de traction murale — conception 6 trous — charge annoncée jusqu’à 200 kg</x:v>
+      </x:c>
+      <x:c r="H26" s="12" t="str">
+        <x:v>B08K3Q74DR</x:v>
+      </x:c>
+      <x:c r="I26" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B08K3Q74DR</x:v>
+      </x:c>
       <x:c r="J26" s="12" t="str"/>
       <x:c r="K26" s="12" t="str">
         <x:f>IF(OR(H26="",J26=""),"", "https://www.amazon.fr/dp/"&amp;H26&amp;"?tag="&amp;J26)</x:f>
@@ -3437,17 +3467,31 @@
       <x:c r="N26" s="12" t="str">
         <x:v>Essentials</x:v>
       </x:c>
-      <x:c r="O26" s="12" t="str"/>
-      <x:c r="P26" s="12" t="str"/>
-      <x:c r="Q26" s="12" t="str"/>
-      <x:c r="R26" s="12" t="str"/>
-      <x:c r="S26" s="12" t="str"/>
-      <x:c r="T26" s="12" t="str"/>
-      <x:c r="U26" s="12" t="str">
+      <x:c r="O26" s="12" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="P26" s="12" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q26" s="12" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="R26" s="12" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="S26" s="12" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="T26" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="U26" s="12" t="n">
         <x:f>IF(COUNTA(O26:T26)=0,"",SUM(O26:T26))</x:f>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="V26" s="12" t="str">
         <x:f>IF(U26="","",IF(U26&gt;=95,"Exceptionnel",IF(U26&gt;=90,"Excellent",IF(U26&gt;=85,"Très bon",IF(U26&gt;=80,"Bon",IF(U26&gt;=70,"Correct","À revoir"))))))</x:f>
+        <x:v>Très bon</x:v>
       </x:c>
       <x:c r="W26" s="12" t="str">
         <x:v>Oui</x:v>
@@ -3459,26 +3503,32 @@
         <x:v>Oui</x:v>
       </x:c>
       <x:c r="Z26" s="12" t="str">
-        <x:v>Barre murale robuste à prix compétitif.</x:v>
+        <x:v>Une barre murale robuste et accessible, conçue pour offrir une fixation stable sans payer le prix d’un modèle premium.</x:v>
       </x:c>
       <x:c r="AA26" s="12" t="str">
-        <x:v>Stabilité | Multiprises | Prix</x:v>
+        <x:v>Excellent rapport qualité/prix | Conception 6 trous | Multiprises | Utilisation intérieure ou extérieure | Structure acier</x:v>
       </x:c>
       <x:c r="AB26" s="12" t="str">
-        <x:v>Installation avec perçage</x:v>
+        <x:v>Montage mural obligatoire | Qualité des chevilles à adapter au support | Finitions plus simples</x:v>
       </x:c>
       <x:c r="AC26" s="12" t="str">
-        <x:v>Débutant à confirmé</x:v>
-      </x:c>
-      <x:c r="AD26" s="12" t="str"/>
-      <x:c r="AE26" s="38" t="str"/>
-      <x:c r="AF26" s="40" t="str"/>
+        <x:v>Débutant à intermédiaire souhaitant une solution murale économique</x:v>
+      </x:c>
+      <x:c r="AD26" s="12"/>
+      <x:c r="AE26" s="38" t="n">
+        <x:v>4.3</x:v>
+      </x:c>
+      <x:c r="AF26" s="55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
       <x:c r="AG26" s="12" t="str">
-        <x:v>À rechercher</x:v>
-      </x:c>
-      <x:c r="AH26" s="12" t="str"/>
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH26" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B08K3Q74DR</x:v>
+      </x:c>
       <x:c r="AI26" s="12" t="str">
-        <x:v>Vérifier charge max et fixations.</x:v>
+        <x:v>ASIN Amazon FR et note 4,3/5 vérifiés le 05/08/2026. Conception murale à 6 trous et charge annoncée jusqu’à 200 kg confirmées dans les résultats Amazon. Nombre d’évaluations laissé vide.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -3495,14 +3545,20 @@
         <x:v>Premium</x:v>
       </x:c>
       <x:c r="E27" s="12" t="str">
-        <x:v>Pull-Up &amp; Dip Bar</x:v>
+        <x:v>PULLUP &amp; DIP Barre de traction porte + station de dips</x:v>
       </x:c>
       <x:c r="F27" s="12" t="str">
-        <x:v>Pullup &amp; Dip</x:v>
-      </x:c>
-      <x:c r="G27" s="12" t="str"/>
-      <x:c r="H27" s="12" t="str"/>
-      <x:c r="I27" s="12" t="str"/>
+        <x:v>PULLUP &amp; DIP</x:v>
+      </x:c>
+      <x:c r="G27" s="12" t="str">
+        <x:v>Sans perçage — 4 prises — cadre 70 à 95 cm — charge jusqu’à 110 kg</x:v>
+      </x:c>
+      <x:c r="H27" s="12" t="str">
+        <x:v>B0CGDTN9VC</x:v>
+      </x:c>
+      <x:c r="I27" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0CGDTN9VC</x:v>
+      </x:c>
       <x:c r="J27" s="12" t="str"/>
       <x:c r="K27" s="12" t="str">
         <x:f>IF(OR(H27="",J27=""),"", "https://www.amazon.fr/dp/"&amp;H27&amp;"?tag="&amp;J27)</x:f>
@@ -3512,17 +3568,31 @@
       <x:c r="N27" s="12" t="str">
         <x:v>Elite</x:v>
       </x:c>
-      <x:c r="O27" s="12" t="str"/>
-      <x:c r="P27" s="12" t="str"/>
-      <x:c r="Q27" s="12" t="str"/>
-      <x:c r="R27" s="12" t="str"/>
-      <x:c r="S27" s="12" t="str"/>
-      <x:c r="T27" s="12" t="str"/>
-      <x:c r="U27" s="12" t="str">
+      <x:c r="O27" s="12" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P27" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="Q27" s="12" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="R27" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="S27" s="12" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="T27" s="12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="U27" s="12" t="n">
         <x:f>IF(COUNTA(O27:T27)=0,"",SUM(O27:T27))</x:f>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="V27" s="12" t="str">
         <x:f>IF(U27="","",IF(U27&gt;=95,"Exceptionnel",IF(U27&gt;=90,"Excellent",IF(U27&gt;=85,"Très bon",IF(U27&gt;=80,"Bon",IF(U27&gt;=70,"Correct","À revoir"))))))</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="W27" s="12" t="str"/>
       <x:c r="X27" s="12" t="str">
@@ -3532,26 +3602,34 @@
         <x:v>Oui</x:v>
       </x:c>
       <x:c r="Z27" s="12" t="str">
-        <x:v>Solution premium pour calisthénie et usage intensif.</x:v>
+        <x:v>Une solution premium sans perçage qui combine tractions et dips, idéale pour la calisthénie à domicile.</x:v>
       </x:c>
       <x:c r="AA27" s="12" t="str">
-        <x:v>Finition | Polyvalence | Stabilité</x:v>
+        <x:v>Aucun perçage | Barre de dips incluse | 4 positions de prise | Garantie 5 ans | Montage et retrait rapides</x:v>
       </x:c>
       <x:c r="AB27" s="12" t="str">
-        <x:v>Prix élevé</x:v>
+        <x:v>Prix élevé | Compatibilité du cadre de porte à vérifier | Charge limitée à 110 kg</x:v>
       </x:c>
       <x:c r="AC27" s="12" t="str">
-        <x:v>Calisthénie / confirmé</x:v>
-      </x:c>
-      <x:c r="AD27" s="12" t="str"/>
-      <x:c r="AE27" s="38" t="str"/>
-      <x:c r="AF27" s="40" t="str"/>
+        <x:v>Intermédiaire à confirmé pratiquant la calisthénie ou vivant en location</x:v>
+      </x:c>
+      <x:c r="AD27" s="12" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="AE27" s="38" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="AF27" s="55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
       <x:c r="AG27" s="12" t="str">
-        <x:v>À rechercher</x:v>
-      </x:c>
-      <x:c r="AH27" s="12" t="str"/>
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH27" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0CGDTN9VC</x:v>
+      </x:c>
       <x:c r="AI27" s="12" t="str">
-        <x:v>Identifier modèle mural ou extérieur exact.</x:v>
+        <x:v>ASIN, note Amazon 4,5/5 et 400 évaluations vérifiés le 05/08/2026. Pullup &amp; Dip confirme l’installation sans perçage, 4 prises, une charge jusqu’à 110 kg, une largeur de cadre de 70 à 95 cm et une garantie de 5 ans.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -13913,7 +13991,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c2e6940412c4221"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47c9c67981fb484a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15814,19 +15892,19 @@
       </x:c>
       <x:c r="E25" s="12" t="str">
         <x:f>Produits!E25</x:f>
-        <x:v>KS300</x:v>
+        <x:v>Sportstech KS350</x:v>
       </x:c>
       <x:c r="F25" s="12" t="str">
         <x:f>Produits!F25</x:f>
         <x:v>Sportstech</x:v>
       </x:c>
-      <x:c r="G25" s="12" t="n">
+      <x:c r="G25" s="12" t="str">
         <x:f>Produits!H25</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H25" s="12" t="n">
+        <x:v>B0843FTZ9T</x:v>
+      </x:c>
+      <x:c r="H25" s="12" t="str">
         <x:f>Produits!I25</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B0843FTZ9T</x:v>
       </x:c>
       <x:c r="I25" s="12" t="n">
         <x:f>Produits!K25</x:f>
@@ -15838,30 +15916,31 @@
       </x:c>
       <x:c r="K25" s="12" t="n">
         <x:f>Produits!U25</x:f>
-        <x:v>0</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="L25" s="12" t="str">
         <x:f>Produits!V25</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="M25" s="12" t="str">
         <x:f>Produits!Z25</x:f>
-        <x:v>Barre polyvalente pour entraînement du haut du corps.</x:v>
+        <x:v>Une barre murale pliable, stable et polyvalente, particulièrement adaptée à un home gym compact.</x:v>
       </x:c>
       <x:c r="N25" s="12" t="str">
         <x:f>Produits!AA25</x:f>
-        <x:v>Multiprises | Polyvalence | Marque connue</x:v>
+        <x:v>Structure acier triangulaire | Pliable jusqu’à 26 cm | 3 positions de prise | 3 œillets d’entraînement | Kit de fixation inclus</x:v>
       </x:c>
       <x:c r="O25" s="12" t="str">
         <x:f>Produits!AB25</x:f>
-        <x:v>Compatibilité porte à vérifier</x:v>
+        <x:v>Perçage obligatoire | Mur solide indispensable | Moins mobile qu’un modèle de porte</x:v>
       </x:c>
       <x:c r="P25" s="12" t="str">
         <x:f>Produits!AC25</x:f>
-        <x:v>Home gym</x:v>
+        <x:v>Débutant à confirmé recherchant une barre murale complète et peu encombrante</x:v>
       </x:c>
       <x:c r="Q25" s="12" t="str">
         <x:f>Produits!AG25</x:f>
-        <x:v>À rechercher</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -15883,19 +15962,19 @@
       </x:c>
       <x:c r="E26" s="12" t="str">
         <x:f>Produits!E26</x:f>
-        <x:v>Wall Mounted Pull-Up Bar</x:v>
+        <x:v>ONETWOFIT OT103</x:v>
       </x:c>
       <x:c r="F26" s="12" t="str">
         <x:f>Produits!F26</x:f>
         <x:v>ONETWOFIT</x:v>
       </x:c>
-      <x:c r="G26" s="12" t="n">
+      <x:c r="G26" s="12" t="str">
         <x:f>Produits!H26</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H26" s="12" t="n">
+        <x:v>B08K3Q74DR</x:v>
+      </x:c>
+      <x:c r="H26" s="12" t="str">
         <x:f>Produits!I26</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B08K3Q74DR</x:v>
       </x:c>
       <x:c r="I26" s="12" t="n">
         <x:f>Produits!K26</x:f>
@@ -15907,31 +15986,31 @@
       </x:c>
       <x:c r="K26" s="12" t="n">
         <x:f>Produits!U26</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L26" s="12" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="L26" s="12" t="str">
         <x:f>Produits!V26</x:f>
-        <x:v>0</x:v>
+        <x:v>Très bon</x:v>
       </x:c>
       <x:c r="M26" s="12" t="str">
         <x:f>Produits!Z26</x:f>
-        <x:v>Barre murale robuste à prix compétitif.</x:v>
+        <x:v>Une barre murale robuste et accessible, conçue pour offrir une fixation stable sans payer le prix d’un modèle premium.</x:v>
       </x:c>
       <x:c r="N26" s="12" t="str">
         <x:f>Produits!AA26</x:f>
-        <x:v>Stabilité | Multiprises | Prix</x:v>
+        <x:v>Excellent rapport qualité/prix | Conception 6 trous | Multiprises | Utilisation intérieure ou extérieure | Structure acier</x:v>
       </x:c>
       <x:c r="O26" s="12" t="str">
         <x:f>Produits!AB26</x:f>
-        <x:v>Installation avec perçage</x:v>
+        <x:v>Montage mural obligatoire | Qualité des chevilles à adapter au support | Finitions plus simples</x:v>
       </x:c>
       <x:c r="P26" s="12" t="str">
         <x:f>Produits!AC26</x:f>
-        <x:v>Débutant à confirmé</x:v>
+        <x:v>Débutant à intermédiaire souhaitant une solution murale économique</x:v>
       </x:c>
       <x:c r="Q26" s="12" t="str">
         <x:f>Produits!AG26</x:f>
-        <x:v>À rechercher</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -15953,19 +16032,19 @@
       </x:c>
       <x:c r="E27" s="12" t="str">
         <x:f>Produits!E27</x:f>
-        <x:v>Pull-Up &amp; Dip Bar</x:v>
+        <x:v>PULLUP &amp; DIP Barre de traction porte + station de dips</x:v>
       </x:c>
       <x:c r="F27" s="12" t="str">
         <x:f>Produits!F27</x:f>
-        <x:v>Pullup &amp; Dip</x:v>
-      </x:c>
-      <x:c r="G27" s="12" t="n">
+        <x:v>PULLUP &amp; DIP</x:v>
+      </x:c>
+      <x:c r="G27" s="12" t="str">
         <x:f>Produits!H27</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H27" s="12" t="n">
+        <x:v>B0CGDTN9VC</x:v>
+      </x:c>
+      <x:c r="H27" s="12" t="str">
         <x:f>Produits!I27</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B0CGDTN9VC</x:v>
       </x:c>
       <x:c r="I27" s="12" t="n">
         <x:f>Produits!K27</x:f>
@@ -15975,31 +16054,33 @@
         <x:f>Produits!L27</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K27" s="12" t="str">
+      <x:c r="K27" s="12" t="n">
         <x:f>Produits!U27</x:f>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="L27" s="12" t="str">
         <x:f>Produits!V27</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="M27" s="12" t="str">
         <x:f>Produits!Z27</x:f>
-        <x:v>Solution premium pour calisthénie et usage intensif.</x:v>
+        <x:v>Une solution premium sans perçage qui combine tractions et dips, idéale pour la calisthénie à domicile.</x:v>
       </x:c>
       <x:c r="N27" s="12" t="str">
         <x:f>Produits!AA27</x:f>
-        <x:v>Finition | Polyvalence | Stabilité</x:v>
+        <x:v>Aucun perçage | Barre de dips incluse | 4 positions de prise | Garantie 5 ans | Montage et retrait rapides</x:v>
       </x:c>
       <x:c r="O27" s="12" t="str">
         <x:f>Produits!AB27</x:f>
-        <x:v>Prix élevé</x:v>
+        <x:v>Prix élevé | Compatibilité du cadre de porte à vérifier | Charge limitée à 110 kg</x:v>
       </x:c>
       <x:c r="P27" s="12" t="str">
         <x:f>Produits!AC27</x:f>
-        <x:v>Calisthénie / confirmé</x:v>
+        <x:v>Intermédiaire à confirmé pratiquant la calisthénie ou vivant en location</x:v>
       </x:c>
       <x:c r="Q27" s="12" t="str">
         <x:f>Produits!AG27</x:f>
-        <x:v>À rechercher</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="28">

--- a/data/import/MuscuGuide_Base_Produits.xlsx
+++ b/data/import/MuscuGuide_Base_Produits.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R539c652a54024d3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produits" sheetId="2" r:id="R64f6e295511b429a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notation" sheetId="3" r:id="Rdc3186bfebd043f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Claude" sheetId="4" r:id="Rdc2e9e86ec46411d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="5" r:id="Ra4b4f8a93f0d4617"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="6" r:id="Rb1b39ccfcf3c44d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R92adaef9abe946de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produits" sheetId="2" r:id="Rf0202f79178f41e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notation" sheetId="3" r:id="R198a761b2c2b434f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Claude" sheetId="4" r:id="R1eb90a37d9054e81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="5" r:id="R7f9ec2f93cd0444f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="6" r:id="R44ab3857d0d5419d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -435,7 +435,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R49611829e2f44a32"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc574ed0a565b42b9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -687,7 +687,7 @@
       </x:c>
       <x:c r="B4" s="12" t="n">
         <x:f>COUNTA(Produits!E4:E250)</x:f>
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C4" s="12"/>
       <x:c r="D4" s="12" t="str">
@@ -747,7 +747,7 @@
       </x:c>
       <x:c r="B6" s="12" t="n">
         <x:f>COUNTIF(Produits!AG4:AG250,"Validé")</x:f>
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C6" s="12"/>
       <x:c r="D6" s="12" t="str">
@@ -807,7 +807,7 @@
       </x:c>
       <x:c r="B8" s="38" t="n">
         <x:f>IFERROR(AVERAGE(Produits!U4:U250),0)</x:f>
-        <x:v>89.33333333333333</x:v>
+        <x:v>89.53333333333333</x:v>
       </x:c>
       <x:c r="C8" s="12"/>
       <x:c r="D8" s="12" t="str">
@@ -1125,7 +1125,7 @@
       </x:c>
       <x:c r="E19" s="12" t="n">
         <x:f>COUNTIF(Produits!B:B,D19)</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F19" s="12" t="n">
         <x:f>COUNTIFS(Produits!B:B,D19,Produits!H:H,"??????????")</x:f>
@@ -1133,7 +1133,7 @@
       </x:c>
       <x:c r="G19" s="12" t="n">
         <x:f>COUNTIFS(Produits!B:B,D19,Produits!AG:AG,"Validé")</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H19" s="46" t="n">
         <x:f>IFERROR(F19/E19,0)</x:f>
@@ -1259,7 +1259,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49a2e06aea0545b2"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b151f4f0c374c5c"/>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -4849,133 +4849,309 @@
       </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="12"/>
-      <x:c r="B40" s="12"/>
-      <x:c r="C40" s="12"/>
-      <x:c r="D40" s="12"/>
-      <x:c r="E40" s="12"/>
-      <x:c r="F40" s="12"/>
-      <x:c r="G40" s="12"/>
-      <x:c r="H40" s="12"/>
-      <x:c r="I40" s="12"/>
+      <x:c r="A40" s="12" t="str">
+        <x:v>MG-ROUE-001</x:v>
+      </x:c>
+      <x:c r="B40" s="12" t="str">
+        <x:v>Roue à abdos</x:v>
+      </x:c>
+      <x:c r="C40" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D40" s="12" t="str">
+        <x:v>Choix MuscuGuide</x:v>
+      </x:c>
+      <x:c r="E40" s="12" t="str">
+        <x:v>Vinsguir Ab Roller noir/rouge</x:v>
+      </x:c>
+      <x:c r="F40" s="12" t="str">
+        <x:v>Vinsguir</x:v>
+      </x:c>
+      <x:c r="G40" s="12" t="str">
+        <x:v>Roue ultra-large 8 cm — axe acier — tapis pour genoux — charge annoncée 200 kg</x:v>
+      </x:c>
+      <x:c r="H40" s="12" t="str">
+        <x:v>B07RKW5H68</x:v>
+      </x:c>
+      <x:c r="I40" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B07RKW5H68</x:v>
+      </x:c>
       <x:c r="J40" s="12"/>
       <x:c r="K40" s="12" t="str">
         <x:f>IF(OR(H40="",J40=""),"", "https://www.amazon.fr/dp/"&amp;H40&amp;"?tag="&amp;J40)</x:f>
       </x:c>
       <x:c r="L40" s="12"/>
       <x:c r="M40" s="36"/>
-      <x:c r="N40" s="12"/>
-      <x:c r="O40" s="12"/>
-      <x:c r="P40" s="12"/>
-      <x:c r="Q40" s="12"/>
-      <x:c r="R40" s="12"/>
-      <x:c r="S40" s="12"/>
-      <x:c r="T40" s="12"/>
-      <x:c r="U40" s="12" t="str">
+      <x:c r="N40" s="12" t="str">
+        <x:v>Performance</x:v>
+      </x:c>
+      <x:c r="O40" s="12" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P40" s="12" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q40" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="R40" s="12" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="S40" s="12" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="T40" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="U40" s="12" t="n">
         <x:f>IF(COUNTA(O40:T40)=0,"",SUM(O40:T40))</x:f>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="V40" s="12" t="str">
         <x:f>IF(U40="","",IF(U40&gt;=95,"Exceptionnel",IF(U40&gt;=90,"Excellent",IF(U40&gt;=85,"Très bon",IF(U40&gt;=80,"Bon",IF(U40&gt;=70,"Correct","À revoir"))))))</x:f>
-      </x:c>
-      <x:c r="W40" s="12"/>
-      <x:c r="X40" s="12"/>
-      <x:c r="Y40" s="12"/>
-      <x:c r="Z40" s="12"/>
-      <x:c r="AA40" s="12"/>
-      <x:c r="AB40" s="12"/>
-      <x:c r="AC40" s="12"/>
-      <x:c r="AD40" s="12"/>
-      <x:c r="AE40" s="38"/>
-      <x:c r="AF40" s="40"/>
-      <x:c r="AG40" s="12"/>
-      <x:c r="AH40" s="12"/>
-      <x:c r="AI40" s="12"/>
+        <x:v>Excellent</x:v>
+      </x:c>
+      <x:c r="W40" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="X40" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="Y40" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="Z40" s="12" t="str">
+        <x:v>Une roue abdominale stable, silencieuse et très populaire, adaptée à la majorité des utilisateurs qui souhaitent renforcer leur sangle abdominale à domicile.</x:v>
+      </x:c>
+      <x:c r="AA40" s="12" t="str">
+        <x:v>Roue ultra-large de 8 cm | Plus de 22 000 évaluations | Tapis pour genoux inclus | Fonctionnement silencieux | Charge annoncée jusqu’à 200 kg</x:v>
+      </x:c>
+      <x:c r="AB40" s="12" t="str">
+        <x:v>Poignées en mousse susceptibles de s’user | Pas de résistance assistée | Le mouvement reste exigeant pour un grand débutant</x:v>
+      </x:c>
+      <x:c r="AC40" s="12" t="str">
+        <x:v>Débutant à confirmé recherchant une roue stable et éprouvée</x:v>
+      </x:c>
+      <x:c r="AD40" s="12" t="n">
+        <x:v>22344</x:v>
+      </x:c>
+      <x:c r="AE40" s="38" t="n">
+        <x:v>4.6</x:v>
+      </x:c>
+      <x:c r="AF40" s="55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="AG40" s="12" t="str">
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH40" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B07RKW5H68</x:v>
+      </x:c>
+      <x:c r="AI40" s="12" t="str">
+        <x:v>ASIN, note Amazon 4,6/5 et 22 344 évaluations vérifiés le 05/08/2026. Roue de 8 cm, tapis inclus et charge annoncée 200 kg confirmés par Amazon et Vinsguir : https://myvinsguir.com/</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="12"/>
-      <x:c r="B41" s="12"/>
-      <x:c r="C41" s="12"/>
-      <x:c r="D41" s="12"/>
-      <x:c r="E41" s="12"/>
-      <x:c r="F41" s="12"/>
-      <x:c r="G41" s="12"/>
-      <x:c r="H41" s="12"/>
-      <x:c r="I41" s="12"/>
+      <x:c r="A41" s="12" t="str">
+        <x:v>MG-ROUE-002</x:v>
+      </x:c>
+      <x:c r="B41" s="12" t="str">
+        <x:v>Roue à abdos</x:v>
+      </x:c>
+      <x:c r="C41" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D41" s="12" t="str">
+        <x:v>Meilleur rapport qualité/prix</x:v>
+      </x:c>
+      <x:c r="E41" s="12" t="str">
+        <x:v>adidas Ab Wheel 18 cm</x:v>
+      </x:c>
+      <x:c r="F41" s="12" t="str">
+        <x:v>adidas</x:v>
+      </x:c>
+      <x:c r="G41" s="12" t="str">
+        <x:v>Diamètre 18 cm — poignées en mousse — surface caoutchoutée antidérapante</x:v>
+      </x:c>
+      <x:c r="H41" s="12" t="str">
+        <x:v>B00EVNXN6K</x:v>
+      </x:c>
+      <x:c r="I41" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B00EVNXN6K</x:v>
+      </x:c>
       <x:c r="J41" s="12"/>
       <x:c r="K41" s="12" t="str">
         <x:f>IF(OR(H41="",J41=""),"", "https://www.amazon.fr/dp/"&amp;H41&amp;"?tag="&amp;J41)</x:f>
       </x:c>
       <x:c r="L41" s="12"/>
       <x:c r="M41" s="36"/>
-      <x:c r="N41" s="12"/>
-      <x:c r="O41" s="12"/>
-      <x:c r="P41" s="12"/>
-      <x:c r="Q41" s="12"/>
-      <x:c r="R41" s="12"/>
-      <x:c r="S41" s="12"/>
-      <x:c r="T41" s="12"/>
-      <x:c r="U41" s="12" t="str">
+      <x:c r="N41" s="12" t="str">
+        <x:v>Essentials</x:v>
+      </x:c>
+      <x:c r="O41" s="12" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P41" s="12" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q41" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="R41" s="12" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="S41" s="12" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="T41" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="U41" s="12" t="n">
         <x:f>IF(COUNTA(O41:T41)=0,"",SUM(O41:T41))</x:f>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="V41" s="12" t="str">
         <x:f>IF(U41="","",IF(U41&gt;=95,"Exceptionnel",IF(U41&gt;=90,"Excellent",IF(U41&gt;=85,"Très bon",IF(U41&gt;=80,"Bon",IF(U41&gt;=70,"Correct","À revoir"))))))</x:f>
-      </x:c>
-      <x:c r="W41" s="12"/>
-      <x:c r="X41" s="12"/>
+        <x:v>Excellent</x:v>
+      </x:c>
+      <x:c r="W41" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="X41" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
       <x:c r="Y41" s="12"/>
-      <x:c r="Z41" s="12"/>
-      <x:c r="AA41" s="12"/>
-      <x:c r="AB41" s="12"/>
-      <x:c r="AC41" s="12"/>
-      <x:c r="AD41" s="12"/>
-      <x:c r="AE41" s="38"/>
-      <x:c r="AF41" s="40"/>
-      <x:c r="AG41" s="12"/>
-      <x:c r="AH41" s="12"/>
-      <x:c r="AI41" s="12"/>
+      <x:c r="Z41" s="12" t="str">
+        <x:v>Une roue simple, solide et accessible, idéale pour s’équiper avec un produit de marque reconnu sans fonctionnalités superflues.</x:v>
+      </x:c>
+      <x:c r="AA41" s="12" t="str">
+        <x:v>Excellent rapport qualité/prix | Diamètre de 18 cm | Surface caoutchoutée antidérapante | Poignées rembourrées | Près de 9 000 évaluations</x:v>
+      </x:c>
+      <x:c r="AB41" s="12" t="str">
+        <x:v>Montage des poignées parfois difficile | Roue unique moins rassurante au début | Aucun tapis pour genoux inclus</x:v>
+      </x:c>
+      <x:c r="AC41" s="12" t="str">
+        <x:v>Débutant à intermédiaire recherchant une roue simple et durable</x:v>
+      </x:c>
+      <x:c r="AD41" s="12" t="n">
+        <x:v>8992</x:v>
+      </x:c>
+      <x:c r="AE41" s="38" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="AF41" s="55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="AG41" s="12" t="str">
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH41" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B00EVNXN6K</x:v>
+      </x:c>
+      <x:c r="AI41" s="12" t="str">
+        <x:v>ASIN, note Amazon 4,5/5 et 8 992 évaluations vérifiés le 05/08/2026. Diamètre 18 cm, poignées en mousse et surface caoutchoutée confirmés sur Amazon FR.</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="12"/>
-      <x:c r="B42" s="12"/>
-      <x:c r="C42" s="12"/>
-      <x:c r="D42" s="12"/>
-      <x:c r="E42" s="12"/>
-      <x:c r="F42" s="12"/>
-      <x:c r="G42" s="12"/>
-      <x:c r="H42" s="12"/>
-      <x:c r="I42" s="12"/>
+      <x:c r="A42" s="12" t="str">
+        <x:v>MG-ROUE-003</x:v>
+      </x:c>
+      <x:c r="B42" s="12" t="str">
+        <x:v>Roue à abdos</x:v>
+      </x:c>
+      <x:c r="C42" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D42" s="12" t="str">
+        <x:v>Premium</x:v>
+      </x:c>
+      <x:c r="E42" s="12" t="str">
+        <x:v>Perfect Fitness Ab Carver Pro</x:v>
+      </x:c>
+      <x:c r="F42" s="12" t="str">
+        <x:v>Perfect Fitness</x:v>
+      </x:c>
+      <x:c r="G42" s="12" t="str">
+        <x:v>Roue ultra-large — ressort interne en acier carbone — poignées ergonomiques — tapis inclus</x:v>
+      </x:c>
+      <x:c r="H42" s="12" t="str">
+        <x:v>B07NCBR97K</x:v>
+      </x:c>
+      <x:c r="I42" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B07NCBR97K</x:v>
+      </x:c>
       <x:c r="J42" s="12"/>
       <x:c r="K42" s="12" t="str">
         <x:f>IF(OR(H42="",J42=""),"", "https://www.amazon.fr/dp/"&amp;H42&amp;"?tag="&amp;J42)</x:f>
       </x:c>
       <x:c r="L42" s="12"/>
       <x:c r="M42" s="36"/>
-      <x:c r="N42" s="12"/>
-      <x:c r="O42" s="12"/>
-      <x:c r="P42" s="12"/>
-      <x:c r="Q42" s="12"/>
-      <x:c r="R42" s="12"/>
-      <x:c r="S42" s="12"/>
-      <x:c r="T42" s="12"/>
-      <x:c r="U42" s="12" t="str">
+      <x:c r="N42" s="12" t="str">
+        <x:v>Elite</x:v>
+      </x:c>
+      <x:c r="O42" s="12" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="P42" s="12" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="Q42" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="R42" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="S42" s="12" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="T42" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="U42" s="12" t="n">
         <x:f>IF(COUNTA(O42:T42)=0,"",SUM(O42:T42))</x:f>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="V42" s="12" t="str">
         <x:f>IF(U42="","",IF(U42&gt;=95,"Exceptionnel",IF(U42&gt;=90,"Excellent",IF(U42&gt;=85,"Très bon",IF(U42&gt;=80,"Bon",IF(U42&gt;=70,"Correct","À revoir"))))))</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="W42" s="12"/>
-      <x:c r="X42" s="12"/>
-      <x:c r="Y42" s="12"/>
-      <x:c r="Z42" s="12"/>
-      <x:c r="AA42" s="12"/>
-      <x:c r="AB42" s="12"/>
-      <x:c r="AC42" s="12"/>
-      <x:c r="AD42" s="12"/>
-      <x:c r="AE42" s="38"/>
-      <x:c r="AF42" s="40"/>
-      <x:c r="AG42" s="12"/>
-      <x:c r="AH42" s="12"/>
-      <x:c r="AI42" s="12"/>
+      <x:c r="X42" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="Y42" s="12" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="Z42" s="12" t="str">
+        <x:v>Une roue abdominale premium avec résistance intégrée, conçue pour améliorer la stabilité, l’activation musculaire et le contrôle du retour.</x:v>
+      </x:c>
+      <x:c r="AA42" s="12" t="str">
+        <x:v>Résistance à ressort intégrée | Assistance au retour | Roue ultra-large | Travail possible des obliques | Poignées ergonomiques et tapis inclus</x:v>
+      </x:c>
+      <x:c r="AB42" s="12" t="str">
+        <x:v>Prix nettement supérieur | Plus lourde et encombrante | Amplitude potentiellement limitée pour les utilisateurs très grands</x:v>
+      </x:c>
+      <x:c r="AC42" s="12" t="str">
+        <x:v>Intermédiaire à confirmé recherchant davantage de contrôle et de progression</x:v>
+      </x:c>
+      <x:c r="AD42" s="12" t="n">
+        <x:v>13447</x:v>
+      </x:c>
+      <x:c r="AE42" s="38" t="n">
+        <x:v>4.6</x:v>
+      </x:c>
+      <x:c r="AF42" s="55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="AG42" s="12" t="str">
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH42" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B07NCBR97K</x:v>
+      </x:c>
+      <x:c r="AI42" s="12" t="str">
+        <x:v>ASIN, note Amazon 4,6/5 et environ 13 447 évaluations vérifiés le 05/08/2026. Ressort interne, roue ultra-large, poignées ergonomiques et tapis confirmés : https://www.fitnessconcept.com.my/brands/perfect-fitness-ab-carver-pro</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="12"/>
@@ -13991,7 +14167,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47c9c67981fb484a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12b0a4b80faf4901"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15845,9 +16021,8 @@
         <x:f>Produits!L24</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K24" s="12" t="n">
+      <x:c r="K24" s="12" t="str">
         <x:f>Produits!U24</x:f>
-        <x:v>0</x:v>
       </x:c>
       <x:c r="L24" s="12" t="str">
         <x:f>Produits!V24</x:f>
@@ -16924,37 +17099,37 @@
       </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="12" t="n">
+      <x:c r="A40" s="12" t="str">
         <x:f>Produits!A40</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B40" s="12" t="n">
+        <x:v>MG-ROUE-001</x:v>
+      </x:c>
+      <x:c r="B40" s="12" t="str">
         <x:f>Produits!B40</x:f>
-        <x:v>0</x:v>
+        <x:v>Roue à abdos</x:v>
       </x:c>
       <x:c r="C40" s="12" t="n">
         <x:f>Produits!C40</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D40" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D40" s="12" t="str">
         <x:f>Produits!D40</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E40" s="12" t="n">
+        <x:v>Choix MuscuGuide</x:v>
+      </x:c>
+      <x:c r="E40" s="12" t="str">
         <x:f>Produits!E40</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F40" s="12" t="n">
+        <x:v>Vinsguir Ab Roller noir/rouge</x:v>
+      </x:c>
+      <x:c r="F40" s="12" t="str">
         <x:f>Produits!F40</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G40" s="12" t="n">
+        <x:v>Vinsguir</x:v>
+      </x:c>
+      <x:c r="G40" s="12" t="str">
         <x:f>Produits!H40</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H40" s="12" t="n">
+        <x:v>B07RKW5H68</x:v>
+      </x:c>
+      <x:c r="H40" s="12" t="str">
         <x:f>Produits!I40</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B07RKW5H68</x:v>
       </x:c>
       <x:c r="I40" s="12" t="n">
         <x:f>Produits!K40</x:f>
@@ -16966,65 +17141,65 @@
       </x:c>
       <x:c r="K40" s="12" t="n">
         <x:f>Produits!U40</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L40" s="12" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="L40" s="12" t="str">
         <x:f>Produits!V40</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M40" s="12" t="n">
+        <x:v>Excellent</x:v>
+      </x:c>
+      <x:c r="M40" s="12" t="str">
         <x:f>Produits!Z40</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N40" s="12" t="n">
+        <x:v>Une roue abdominale stable, silencieuse et très populaire, adaptée à la majorité des utilisateurs qui souhaitent renforcer leur sangle abdominale à domicile.</x:v>
+      </x:c>
+      <x:c r="N40" s="12" t="str">
         <x:f>Produits!AA40</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O40" s="12" t="n">
+        <x:v>Roue ultra-large de 8 cm | Plus de 22 000 évaluations | Tapis pour genoux inclus | Fonctionnement silencieux | Charge annoncée jusqu’à 200 kg</x:v>
+      </x:c>
+      <x:c r="O40" s="12" t="str">
         <x:f>Produits!AB40</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P40" s="12" t="n">
+        <x:v>Poignées en mousse susceptibles de s’user | Pas de résistance assistée | Le mouvement reste exigeant pour un grand débutant</x:v>
+      </x:c>
+      <x:c r="P40" s="12" t="str">
         <x:f>Produits!AC40</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q40" s="12" t="n">
+        <x:v>Débutant à confirmé recherchant une roue stable et éprouvée</x:v>
+      </x:c>
+      <x:c r="Q40" s="12" t="str">
         <x:f>Produits!AG40</x:f>
-        <x:v>0</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="12" t="n">
+      <x:c r="A41" s="12" t="str">
         <x:f>Produits!A41</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B41" s="12" t="n">
+        <x:v>MG-ROUE-002</x:v>
+      </x:c>
+      <x:c r="B41" s="12" t="str">
         <x:f>Produits!B41</x:f>
-        <x:v>0</x:v>
+        <x:v>Roue à abdos</x:v>
       </x:c>
       <x:c r="C41" s="12" t="n">
         <x:f>Produits!C41</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D41" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D41" s="12" t="str">
         <x:f>Produits!D41</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E41" s="12" t="n">
+        <x:v>Meilleur rapport qualité/prix</x:v>
+      </x:c>
+      <x:c r="E41" s="12" t="str">
         <x:f>Produits!E41</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F41" s="12" t="n">
+        <x:v>adidas Ab Wheel 18 cm</x:v>
+      </x:c>
+      <x:c r="F41" s="12" t="str">
         <x:f>Produits!F41</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G41" s="12" t="n">
+        <x:v>adidas</x:v>
+      </x:c>
+      <x:c r="G41" s="12" t="str">
         <x:f>Produits!H41</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H41" s="12" t="n">
+        <x:v>B00EVNXN6K</x:v>
+      </x:c>
+      <x:c r="H41" s="12" t="str">
         <x:f>Produits!I41</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B00EVNXN6K</x:v>
       </x:c>
       <x:c r="I41" s="12" t="n">
         <x:f>Produits!K41</x:f>
@@ -17036,65 +17211,65 @@
       </x:c>
       <x:c r="K41" s="12" t="n">
         <x:f>Produits!U41</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L41" s="12" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="L41" s="12" t="str">
         <x:f>Produits!V41</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M41" s="12" t="n">
+        <x:v>Excellent</x:v>
+      </x:c>
+      <x:c r="M41" s="12" t="str">
         <x:f>Produits!Z41</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N41" s="12" t="n">
+        <x:v>Une roue simple, solide et accessible, idéale pour s’équiper avec un produit de marque reconnu sans fonctionnalités superflues.</x:v>
+      </x:c>
+      <x:c r="N41" s="12" t="str">
         <x:f>Produits!AA41</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O41" s="12" t="n">
+        <x:v>Excellent rapport qualité/prix | Diamètre de 18 cm | Surface caoutchoutée antidérapante | Poignées rembourrées | Près de 9 000 évaluations</x:v>
+      </x:c>
+      <x:c r="O41" s="12" t="str">
         <x:f>Produits!AB41</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P41" s="12" t="n">
+        <x:v>Montage des poignées parfois difficile | Roue unique moins rassurante au début | Aucun tapis pour genoux inclus</x:v>
+      </x:c>
+      <x:c r="P41" s="12" t="str">
         <x:f>Produits!AC41</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q41" s="12" t="n">
+        <x:v>Débutant à intermédiaire recherchant une roue simple et durable</x:v>
+      </x:c>
+      <x:c r="Q41" s="12" t="str">
         <x:f>Produits!AG41</x:f>
-        <x:v>0</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="12" t="n">
+      <x:c r="A42" s="12" t="str">
         <x:f>Produits!A42</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B42" s="12" t="n">
+        <x:v>MG-ROUE-003</x:v>
+      </x:c>
+      <x:c r="B42" s="12" t="str">
         <x:f>Produits!B42</x:f>
-        <x:v>0</x:v>
+        <x:v>Roue à abdos</x:v>
       </x:c>
       <x:c r="C42" s="12" t="n">
         <x:f>Produits!C42</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D42" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D42" s="12" t="str">
         <x:f>Produits!D42</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E42" s="12" t="n">
+        <x:v>Premium</x:v>
+      </x:c>
+      <x:c r="E42" s="12" t="str">
         <x:f>Produits!E42</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F42" s="12" t="n">
+        <x:v>Perfect Fitness Ab Carver Pro</x:v>
+      </x:c>
+      <x:c r="F42" s="12" t="str">
         <x:f>Produits!F42</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G42" s="12" t="n">
+        <x:v>Perfect Fitness</x:v>
+      </x:c>
+      <x:c r="G42" s="12" t="str">
         <x:f>Produits!H42</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H42" s="12" t="n">
+        <x:v>B07NCBR97K</x:v>
+      </x:c>
+      <x:c r="H42" s="12" t="str">
         <x:f>Produits!I42</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B07NCBR97K</x:v>
       </x:c>
       <x:c r="I42" s="12" t="n">
         <x:f>Produits!K42</x:f>
@@ -17106,31 +17281,31 @@
       </x:c>
       <x:c r="K42" s="12" t="n">
         <x:f>Produits!U42</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L42" s="12" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="L42" s="12" t="str">
         <x:f>Produits!V42</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M42" s="12" t="n">
+        <x:v>Excellent</x:v>
+      </x:c>
+      <x:c r="M42" s="12" t="str">
         <x:f>Produits!Z42</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N42" s="12" t="n">
+        <x:v>Une roue abdominale premium avec résistance intégrée, conçue pour améliorer la stabilité, l’activation musculaire et le contrôle du retour.</x:v>
+      </x:c>
+      <x:c r="N42" s="12" t="str">
         <x:f>Produits!AA42</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O42" s="12" t="n">
+        <x:v>Résistance à ressort intégrée | Assistance au retour | Roue ultra-large | Travail possible des obliques | Poignées ergonomiques et tapis inclus</x:v>
+      </x:c>
+      <x:c r="O42" s="12" t="str">
         <x:f>Produits!AB42</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P42" s="12" t="n">
+        <x:v>Prix nettement supérieur | Plus lourde et encombrante | Amplitude potentiellement limitée pour les utilisateurs très grands</x:v>
+      </x:c>
+      <x:c r="P42" s="12" t="str">
         <x:f>Produits!AC42</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q42" s="12" t="n">
+        <x:v>Intermédiaire à confirmé recherchant davantage de contrôle et de progression</x:v>
+      </x:c>
+      <x:c r="Q42" s="12" t="str">
         <x:f>Produits!AG42</x:f>
-        <x:v>0</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="43">

--- a/data/import/MuscuGuide_Base_Produits.xlsx
+++ b/data/import/MuscuGuide_Base_Produits.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R92adaef9abe946de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produits" sheetId="2" r:id="Rf0202f79178f41e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notation" sheetId="3" r:id="R198a761b2c2b434f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Claude" sheetId="4" r:id="R1eb90a37d9054e81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="5" r:id="R7f9ec2f93cd0444f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="6" r:id="R44ab3857d0d5419d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R334a96ef688c4e85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produits" sheetId="2" r:id="Rb4a760d781224aa6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notation" sheetId="3" r:id="R90805a10dc074995"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Claude" sheetId="4" r:id="R0191e7c5985e4d28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listes" sheetId="5" r:id="R481527d990de4ce4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="6" r:id="R3f19d2b5f82a48ae"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -435,7 +435,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc574ed0a565b42b9"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc556cce810a942f5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -704,7 +704,7 @@
       </x:c>
       <x:c r="G4" s="12" t="n">
         <x:f>COUNTIFS(Produits!B:B,D4,Produits!AG:AG,"Validé")</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H4" s="46" t="n">
         <x:f>IFERROR(F4/E4,0)</x:f>
@@ -747,7 +747,7 @@
       </x:c>
       <x:c r="B6" s="12" t="n">
         <x:f>COUNTIF(Produits!AG4:AG250,"Validé")</x:f>
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C6" s="12"/>
       <x:c r="D6" s="12" t="str">
@@ -777,7 +777,7 @@
       </x:c>
       <x:c r="B7" s="12" t="n">
         <x:f>COUNTIF(Produits!AG4:AG250,"À rechercher")</x:f>
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="12"/>
       <x:c r="D7" s="12" t="str">
@@ -807,7 +807,7 @@
       </x:c>
       <x:c r="B8" s="38" t="n">
         <x:f>IFERROR(AVERAGE(Produits!U4:U250),0)</x:f>
-        <x:v>89.53333333333333</x:v>
+        <x:v>89.60606060606061</x:v>
       </x:c>
       <x:c r="C8" s="12"/>
       <x:c r="D8" s="12" t="str">
@@ -1259,7 +1259,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b151f4f0c374c5c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55ef860175db4921"/>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -1478,14 +1478,20 @@
         <x:v>Choix MuscuGuide</x:v>
       </x:c>
       <x:c r="E4" s="12" t="str">
-        <x:v>Gold Standard 100% Whey</x:v>
+        <x:v>Optimum Nutrition Gold Standard 100% Whey</x:v>
       </x:c>
       <x:c r="F4" s="12" t="str">
         <x:v>Optimum Nutrition</x:v>
       </x:c>
-      <x:c r="G4" s="12" t="str"/>
-      <x:c r="H4" s="12" t="str"/>
-      <x:c r="I4" s="12" t="str"/>
+      <x:c r="G4" s="12" t="str">
+        <x:v>2,26 kg — Double chocolat riche — 73 doses — 24 g de protéines</x:v>
+      </x:c>
+      <x:c r="H4" s="12" t="str">
+        <x:v>B000QSNYGI</x:v>
+      </x:c>
+      <x:c r="I4" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B000QSNYGI</x:v>
+      </x:c>
       <x:c r="J4" s="12" t="str"/>
       <x:c r="K4" s="12" t="str">
         <x:f>IF(OR(H4="",J4=""),"", "https://www.amazon.fr/dp/"&amp;H4&amp;"?tag="&amp;J4)</x:f>
@@ -1495,17 +1501,31 @@
       <x:c r="N4" s="12" t="str">
         <x:v>Performance</x:v>
       </x:c>
-      <x:c r="O4" s="12" t="str"/>
-      <x:c r="P4" s="12" t="str"/>
-      <x:c r="Q4" s="12" t="str"/>
-      <x:c r="R4" s="12" t="str"/>
-      <x:c r="S4" s="12" t="str"/>
-      <x:c r="T4" s="12" t="str"/>
-      <x:c r="U4" s="12" t="str">
+      <x:c r="O4" s="12" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P4" s="12" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="Q4" s="12" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="R4" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="S4" s="12" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="T4" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="U4" s="12" t="n">
         <x:f>IF(COUNTA(O4:T4)=0,"",SUM(O4:T4))</x:f>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="V4" s="12" t="str">
         <x:f>IF(U4="","",IF(U4&gt;=95,"Exceptionnel",IF(U4&gt;=90,"Excellent",IF(U4&gt;=85,"Très bon",IF(U4&gt;=80,"Bon",IF(U4&gt;=70,"Correct","À revoir"))))))</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="W4" s="12" t="str">
         <x:v>Oui</x:v>
@@ -1517,26 +1537,34 @@
         <x:v>Oui</x:v>
       </x:c>
       <x:c r="Z4" s="12" t="str">
-        <x:v>Référence polyvalente pour la majorité des pratiquants.</x:v>
+        <x:v>Une whey de référence, facile à intégrer au quotidien et adaptée à la majorité des pratiquants recherchant une formule éprouvée.</x:v>
       </x:c>
       <x:c r="AA4" s="12" t="str">
-        <x:v>Bonne réputation | Formule connue | Large choix</x:v>
+        <x:v>24 g de protéines par portion | 5,5 g de BCAA | Très forte notoriété | Mélange facile | Large choix de saveurs</x:v>
       </x:c>
       <x:c r="AB4" s="12" t="str">
-        <x:v>Prix parfois élevé | Saveurs variables</x:v>
+        <x:v>Prix souvent supérieur aux alternatives | Goût et texture variables selon le parfum | Contient des édulcorants</x:v>
       </x:c>
       <x:c r="AC4" s="12" t="str">
-        <x:v>Débutant à confirmé</x:v>
-      </x:c>
-      <x:c r="AD4" s="12" t="str"/>
-      <x:c r="AE4" s="38" t="str"/>
-      <x:c r="AF4" s="40" t="str"/>
+        <x:v>Débutant à confirmé recherchant une whey polyvalente et reconnue</x:v>
+      </x:c>
+      <x:c r="AD4" s="12" t="n">
+        <x:v>1676</x:v>
+      </x:c>
+      <x:c r="AE4" s="38" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="AF4" s="55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
       <x:c r="AG4" s="12" t="str">
-        <x:v>À rechercher</x:v>
-      </x:c>
-      <x:c r="AH4" s="12" t="str"/>
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH4" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B000QSNYGI</x:v>
+      </x:c>
       <x:c r="AI4" s="12" t="str">
-        <x:v>Sélection éditoriale initiale — vérifier disponibilité Amazon FR.</x:v>
+        <x:v>ASIN, note Amazon 4,5/5 et 1 676 évaluations vérifiés le 05/08/2026. Format 2,26 kg, 73 doses et 24 g de protéines confirmés sur Amazon FR. Formule officielle : https://www.optimumnutrition.com/en-us/products/gold-standard-100-whey-protein-powder</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1553,14 +1581,20 @@
         <x:v>Meilleur rapport qualité/prix</x:v>
       </x:c>
       <x:c r="E5" s="12" t="str">
-        <x:v>Critical Whey</x:v>
+        <x:v>Applied Nutrition Critical Whey 2 kg</x:v>
       </x:c>
       <x:c r="F5" s="12" t="str">
         <x:v>Applied Nutrition</x:v>
       </x:c>
-      <x:c r="G5" s="12" t="str"/>
-      <x:c r="H5" s="12" t="str"/>
-      <x:c r="I5" s="12" t="str"/>
+      <x:c r="G5" s="12" t="str">
+        <x:v>Chocolate Milkshake — 24 g de protéines — 61 portions — 120 kcal</x:v>
+      </x:c>
+      <x:c r="H5" s="12" t="str">
+        <x:v>B0CN72SD7K</x:v>
+      </x:c>
+      <x:c r="I5" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0CN72SD7K</x:v>
+      </x:c>
       <x:c r="J5" s="12" t="str"/>
       <x:c r="K5" s="12" t="str">
         <x:f>IF(OR(H5="",J5=""),"", "https://www.amazon.fr/dp/"&amp;H5&amp;"?tag="&amp;J5)</x:f>
@@ -1570,17 +1604,31 @@
       <x:c r="N5" s="12" t="str">
         <x:v>Essentials</x:v>
       </x:c>
-      <x:c r="O5" s="12" t="str"/>
-      <x:c r="P5" s="12" t="str"/>
-      <x:c r="Q5" s="12" t="str"/>
-      <x:c r="R5" s="12" t="str"/>
-      <x:c r="S5" s="12" t="str"/>
-      <x:c r="T5" s="12" t="str"/>
-      <x:c r="U5" s="12" t="str">
+      <x:c r="O5" s="12" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="P5" s="12" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="Q5" s="12" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R5" s="12" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="S5" s="12" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="T5" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="U5" s="12" t="n">
         <x:f>IF(COUNTA(O5:T5)=0,"",SUM(O5:T5))</x:f>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="V5" s="12" t="str">
         <x:f>IF(U5="","",IF(U5&gt;=95,"Exceptionnel",IF(U5&gt;=90,"Excellent",IF(U5&gt;=85,"Très bon",IF(U5&gt;=80,"Bon",IF(U5&gt;=70,"Correct","À revoir"))))))</x:f>
+        <x:v>Très bon</x:v>
       </x:c>
       <x:c r="W5" s="12" t="str">
         <x:v>Oui</x:v>
@@ -1590,26 +1638,34 @@
       </x:c>
       <x:c r="Y5" s="12" t="str"/>
       <x:c r="Z5" s="12" t="str">
-        <x:v>Option accessible pour une consommation régulière.</x:v>
+        <x:v>Une whey accessible et bien dosée, intéressante pour une consommation régulière avec un budget maîtrisé.</x:v>
       </x:c>
       <x:c r="AA5" s="12" t="str">
-        <x:v>Tarif compétitif | Marque connue | Polyvalente</x:v>
+        <x:v>24 g de protéines | Bon rapport quantité/prix | 61 portions | 120 kcal par portion | BCAA et glutamine</x:v>
       </x:c>
       <x:c r="AB5" s="12" t="str">
-        <x:v>Composition à comparer selon parfum</x:v>
+        <x:v>Note client plus basse que les références premium | Composition pouvant varier selon le parfum | Texture plus sucrée pour certains utilisateurs</x:v>
       </x:c>
       <x:c r="AC5" s="12" t="str">
-        <x:v>Débutant / intermédiaire</x:v>
-      </x:c>
-      <x:c r="AD5" s="12" t="str"/>
-      <x:c r="AE5" s="38" t="str"/>
-      <x:c r="AF5" s="40" t="str"/>
+        <x:v>Débutant à intermédiaire recherchant une whey économique pour un usage régulier</x:v>
+      </x:c>
+      <x:c r="AD5" s="12" t="n">
+        <x:v>1465</x:v>
+      </x:c>
+      <x:c r="AE5" s="38" t="n">
+        <x:v>4.2</x:v>
+      </x:c>
+      <x:c r="AF5" s="55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
       <x:c r="AG5" s="12" t="str">
-        <x:v>À rechercher</x:v>
-      </x:c>
-      <x:c r="AH5" s="12" t="str"/>
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH5" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B0CN72SD7K</x:v>
+      </x:c>
       <x:c r="AI5" s="12" t="str">
-        <x:v>Sélection éditoriale initiale.</x:v>
+        <x:v>ASIN, note Amazon 4,2/5 et 1 465 évaluations vérifiés le 05/08/2026. La formule actuelle annonce 24 g de protéines, 61 portions et 120 kcal : https://appliednutrition.uk/products/critical-whey</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1626,14 +1682,20 @@
         <x:v>Premium</x:v>
       </x:c>
       <x:c r="E6" s="12" t="str">
-        <x:v>Iso Whey Zero</x:v>
+        <x:v>BioTechUSA Iso Whey Zero 908 g</x:v>
       </x:c>
       <x:c r="F6" s="12" t="str">
         <x:v>BioTechUSA</x:v>
       </x:c>
-      <x:c r="G6" s="12" t="str"/>
-      <x:c r="H6" s="12" t="str"/>
-      <x:c r="I6" s="12" t="str"/>
+      <x:c r="G6" s="12" t="str">
+        <x:v>Black Biscuit — isolat — 21 g de protéines — lactose réduit — sans sucres</x:v>
+      </x:c>
+      <x:c r="H6" s="12" t="str">
+        <x:v>B08TWSPB1F</x:v>
+      </x:c>
+      <x:c r="I6" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B08TWSPB1F</x:v>
+      </x:c>
       <x:c r="J6" s="12" t="str"/>
       <x:c r="K6" s="12" t="str">
         <x:f>IF(OR(H6="",J6=""),"", "https://www.amazon.fr/dp/"&amp;H6&amp;"?tag="&amp;J6)</x:f>
@@ -1643,17 +1705,31 @@
       <x:c r="N6" s="12" t="str">
         <x:v>Elite</x:v>
       </x:c>
-      <x:c r="O6" s="12" t="str"/>
-      <x:c r="P6" s="12" t="str"/>
-      <x:c r="Q6" s="12" t="str"/>
-      <x:c r="R6" s="12" t="str"/>
-      <x:c r="S6" s="12" t="str"/>
-      <x:c r="T6" s="12" t="str"/>
-      <x:c r="U6" s="12" t="str">
+      <x:c r="O6" s="12" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="P6" s="12" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="Q6" s="12" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="R6" s="12" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="S6" s="12" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="T6" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="U6" s="12" t="n">
         <x:f>IF(COUNTA(O6:T6)=0,"",SUM(O6:T6))</x:f>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="V6" s="12" t="str">
         <x:f>IF(U6="","",IF(U6&gt;=95,"Exceptionnel",IF(U6&gt;=90,"Excellent",IF(U6&gt;=85,"Très bon",IF(U6&gt;=80,"Bon",IF(U6&gt;=70,"Correct","À revoir"))))))</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="W6" s="12" t="str"/>
       <x:c r="X6" s="12" t="str">
@@ -1663,26 +1739,34 @@
         <x:v>Oui</x:v>
       </x:c>
       <x:c r="Z6" s="12" t="str">
-        <x:v>Isolat premium pour les utilisateurs exigeants.</x:v>
+        <x:v>Un isolat premium destiné aux utilisateurs qui privilégient une formule riche en protéines, pauvre en sucres et à teneur réduite en lactose.</x:v>
       </x:c>
       <x:c r="AA6" s="12" t="str">
-        <x:v>Faible teneur en sucres | Formule isolat | Image premium</x:v>
+        <x:v>Isolat de whey | 21 g de protéines par portion | Teneur réduite en lactose | Sans sucres et sans gluten | BCAA et glutamine ajoutés</x:v>
       </x:c>
       <x:c r="AB6" s="12" t="str">
-        <x:v>Prix élevé</x:v>
+        <x:v>Prix élevé au kilogramme | Format de 908 g plus petit | Saveurs parfois très marquées</x:v>
       </x:c>
       <x:c r="AC6" s="12" t="str">
-        <x:v>Intermédiaire / confirmé</x:v>
-      </x:c>
-      <x:c r="AD6" s="12" t="str"/>
-      <x:c r="AE6" s="38" t="str"/>
-      <x:c r="AF6" s="40" t="str"/>
+        <x:v>Intermédiaire à confirmé recherchant un isolat premium et une formule allégée en sucres</x:v>
+      </x:c>
+      <x:c r="AD6" s="12" t="n">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="AE6" s="38" t="n">
+        <x:v>4.6</x:v>
+      </x:c>
+      <x:c r="AF6" s="55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
       <x:c r="AG6" s="12" t="str">
-        <x:v>À rechercher</x:v>
-      </x:c>
-      <x:c r="AH6" s="12" t="str"/>
+        <x:v>Validé</x:v>
+      </x:c>
+      <x:c r="AH6" s="12" t="str">
+        <x:v>https://www.amazon.fr/dp/B08TWSPB1F</x:v>
+      </x:c>
       <x:c r="AI6" s="12" t="str">
-        <x:v>Sélection éditoriale initiale.</x:v>
+        <x:v>ASIN, note Amazon 4,6/5 et 171 évaluations vérifiés le 05/08/2026. Amazon FR annonce 21 g de protéines par portion, une teneur réduite en lactose, sans sucres et sans gluten. Source officielle : https://shop.biotechusa.com/products/iso-whey-zero-1816-g</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -14167,7 +14251,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12b0a4b80faf4901"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc30f7ec191d4b86"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14605,19 +14689,19 @@
       </x:c>
       <x:c r="E4" s="12" t="str">
         <x:f>Produits!E4</x:f>
-        <x:v>Gold Standard 100% Whey</x:v>
+        <x:v>Optimum Nutrition Gold Standard 100% Whey</x:v>
       </x:c>
       <x:c r="F4" s="12" t="str">
         <x:f>Produits!F4</x:f>
         <x:v>Optimum Nutrition</x:v>
       </x:c>
-      <x:c r="G4" s="12" t="n">
+      <x:c r="G4" s="12" t="str">
         <x:f>Produits!H4</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H4" s="12" t="n">
+        <x:v>B000QSNYGI</x:v>
+      </x:c>
+      <x:c r="H4" s="12" t="str">
         <x:f>Produits!I4</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B000QSNYGI</x:v>
       </x:c>
       <x:c r="I4" s="12" t="n">
         <x:f>Produits!K4</x:f>
@@ -14629,30 +14713,31 @@
       </x:c>
       <x:c r="K4" s="12" t="n">
         <x:f>Produits!U4</x:f>
-        <x:v>0</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="L4" s="12" t="str">
         <x:f>Produits!V4</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="M4" s="12" t="str">
         <x:f>Produits!Z4</x:f>
-        <x:v>Référence polyvalente pour la majorité des pratiquants.</x:v>
+        <x:v>Une whey de référence, facile à intégrer au quotidien et adaptée à la majorité des pratiquants recherchant une formule éprouvée.</x:v>
       </x:c>
       <x:c r="N4" s="12" t="str">
         <x:f>Produits!AA4</x:f>
-        <x:v>Bonne réputation | Formule connue | Large choix</x:v>
+        <x:v>24 g de protéines par portion | 5,5 g de BCAA | Très forte notoriété | Mélange facile | Large choix de saveurs</x:v>
       </x:c>
       <x:c r="O4" s="12" t="str">
         <x:f>Produits!AB4</x:f>
-        <x:v>Prix parfois élevé | Saveurs variables</x:v>
+        <x:v>Prix souvent supérieur aux alternatives | Goût et texture variables selon le parfum | Contient des édulcorants</x:v>
       </x:c>
       <x:c r="P4" s="12" t="str">
         <x:f>Produits!AC4</x:f>
-        <x:v>Débutant à confirmé</x:v>
+        <x:v>Débutant à confirmé recherchant une whey polyvalente et reconnue</x:v>
       </x:c>
       <x:c r="Q4" s="12" t="str">
         <x:f>Produits!AG4</x:f>
-        <x:v>À rechercher</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -14674,19 +14759,19 @@
       </x:c>
       <x:c r="E5" s="12" t="str">
         <x:f>Produits!E5</x:f>
-        <x:v>Critical Whey</x:v>
+        <x:v>Applied Nutrition Critical Whey 2 kg</x:v>
       </x:c>
       <x:c r="F5" s="12" t="str">
         <x:f>Produits!F5</x:f>
         <x:v>Applied Nutrition</x:v>
       </x:c>
-      <x:c r="G5" s="12" t="n">
+      <x:c r="G5" s="12" t="str">
         <x:f>Produits!H5</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H5" s="12" t="n">
+        <x:v>B0CN72SD7K</x:v>
+      </x:c>
+      <x:c r="H5" s="12" t="str">
         <x:f>Produits!I5</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B0CN72SD7K</x:v>
       </x:c>
       <x:c r="I5" s="12" t="n">
         <x:f>Produits!K5</x:f>
@@ -14698,31 +14783,31 @@
       </x:c>
       <x:c r="K5" s="12" t="n">
         <x:f>Produits!U5</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L5" s="12" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="L5" s="12" t="str">
         <x:f>Produits!V5</x:f>
-        <x:v>0</x:v>
+        <x:v>Très bon</x:v>
       </x:c>
       <x:c r="M5" s="12" t="str">
         <x:f>Produits!Z5</x:f>
-        <x:v>Option accessible pour une consommation régulière.</x:v>
+        <x:v>Une whey accessible et bien dosée, intéressante pour une consommation régulière avec un budget maîtrisé.</x:v>
       </x:c>
       <x:c r="N5" s="12" t="str">
         <x:f>Produits!AA5</x:f>
-        <x:v>Tarif compétitif | Marque connue | Polyvalente</x:v>
+        <x:v>24 g de protéines | Bon rapport quantité/prix | 61 portions | 120 kcal par portion | BCAA et glutamine</x:v>
       </x:c>
       <x:c r="O5" s="12" t="str">
         <x:f>Produits!AB5</x:f>
-        <x:v>Composition à comparer selon parfum</x:v>
+        <x:v>Note client plus basse que les références premium | Composition pouvant varier selon le parfum | Texture plus sucrée pour certains utilisateurs</x:v>
       </x:c>
       <x:c r="P5" s="12" t="str">
         <x:f>Produits!AC5</x:f>
-        <x:v>Débutant / intermédiaire</x:v>
+        <x:v>Débutant à intermédiaire recherchant une whey économique pour un usage régulier</x:v>
       </x:c>
       <x:c r="Q5" s="12" t="str">
         <x:f>Produits!AG5</x:f>
-        <x:v>À rechercher</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -14744,19 +14829,19 @@
       </x:c>
       <x:c r="E6" s="12" t="str">
         <x:f>Produits!E6</x:f>
-        <x:v>Iso Whey Zero</x:v>
+        <x:v>BioTechUSA Iso Whey Zero 908 g</x:v>
       </x:c>
       <x:c r="F6" s="12" t="str">
         <x:f>Produits!F6</x:f>
         <x:v>BioTechUSA</x:v>
       </x:c>
-      <x:c r="G6" s="12" t="n">
+      <x:c r="G6" s="12" t="str">
         <x:f>Produits!H6</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H6" s="12" t="n">
+        <x:v>B08TWSPB1F</x:v>
+      </x:c>
+      <x:c r="H6" s="12" t="str">
         <x:f>Produits!I6</x:f>
-        <x:v>0</x:v>
+        <x:v>https://www.amazon.fr/dp/B08TWSPB1F</x:v>
       </x:c>
       <x:c r="I6" s="12" t="n">
         <x:f>Produits!K6</x:f>
@@ -14768,30 +14853,31 @@
       </x:c>
       <x:c r="K6" s="12" t="n">
         <x:f>Produits!U6</x:f>
-        <x:v>0</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="L6" s="12" t="str">
         <x:f>Produits!V6</x:f>
+        <x:v>Excellent</x:v>
       </x:c>
       <x:c r="M6" s="12" t="str">
         <x:f>Produits!Z6</x:f>
-        <x:v>Isolat premium pour les utilisateurs exigeants.</x:v>
+        <x:v>Un isolat premium destiné aux utilisateurs qui privilégient une formule riche en protéines, pauvre en sucres et à teneur réduite en lactose.</x:v>
       </x:c>
       <x:c r="N6" s="12" t="str">
         <x:f>Produits!AA6</x:f>
-        <x:v>Faible teneur en sucres | Formule isolat | Image premium</x:v>
+        <x:v>Isolat de whey | 21 g de protéines par portion | Teneur réduite en lactose | Sans sucres et sans gluten | BCAA et glutamine ajoutés</x:v>
       </x:c>
       <x:c r="O6" s="12" t="str">
         <x:f>Produits!AB6</x:f>
-        <x:v>Prix élevé</x:v>
+        <x:v>Prix élevé au kilogramme | Format de 908 g plus petit | Saveurs parfois très marquées</x:v>
       </x:c>
       <x:c r="P6" s="12" t="str">
         <x:f>Produits!AC6</x:f>
-        <x:v>Intermédiaire / confirmé</x:v>
+        <x:v>Intermédiaire à confirmé recherchant un isolat premium et une formule allégée en sucres</x:v>
       </x:c>
       <x:c r="Q6" s="12" t="str">
         <x:f>Produits!AG6</x:f>
-        <x:v>À rechercher</x:v>
+        <x:v>Validé</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
